--- a/results/job_matches_2026-04-28.xlsx
+++ b/results/job_matches_2026-04-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G114"/>
+  <dimension ref="A1:G135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,25 +643,25 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Snowflake Architect - Job ID 831</t>
+          <t>Solutions Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Kapitus</t>
+          <t>Cloudera</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>18.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, IAM, RDS, Databricks</t>
+          <t>AWS, Azure, GCP, Hadoop, HDFS, Hive, HBase, YARN, Impala, Spark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30116c3087096b0c</t>
+          <t>https://www.indeed.com/viewjob?jk=6db37997e354b1b6</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Customer Support Developer</t>
+          <t>Snowflake Architect - Job ID 831</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Airbyte</t>
+          <t>Kapitus</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, IAM, RDS, Databricks</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab2390ad9f6c9780</t>
+          <t>https://www.indeed.com/viewjob?jk=30116c3087096b0c</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7fe60e6480b1a64</t>
+          <t>https://www.indeed.com/viewjob?jk=ab2390ad9f6c9780</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Engineer - Data</t>
+          <t>Customer Support Developer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Airbyte</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, NoSQL, dbt</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e96d0ff5e851a0dc</t>
+          <t>https://www.indeed.com/viewjob?jk=a7fe60e6480b1a64</t>
         </is>
       </c>
     </row>
@@ -853,17 +853,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer - Snowflake</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Corebridge</t>
+          <t>Old National Bank</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Lake Elmo, MN, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3afad6ecd5a25a2</t>
+          <t>https://www.indeed.com/viewjob?jk=58d405ceae103971</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AWS API Engineer</t>
+          <t>Data Engineer - Snowflake</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Corebridge</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, MongoDB</t>
+          <t>AWS, Glue, Redshift, RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcce665f3a3b0fee</t>
+          <t>https://www.indeed.com/viewjob?jk=d3afad6ecd5a25a2</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Site Reliability Engineering (SRE) Intern</t>
+          <t>AWS API Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Calix</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,59 +951,59 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b66b9b991f001a00</t>
+          <t>https://www.indeed.com/viewjob?jk=dcce665f3a3b0fee</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Python APIs</t>
+          <t>Senior PS Sales Solutions Architect</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, Azure, GCP, Scala, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f063f9c882ccc12</t>
+          <t>https://www.indeed.com/viewjob?jk=9ed1a2a8d040517b</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Python APIs</t>
+          <t>Site Reliability Engineering (SRE) Intern</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Calix</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, Azure, GCP, Scala, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a00e6d7208f216f0</t>
+          <t>https://www.indeed.com/viewjob?jk=b66b9b991f001a00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Java</t>
+          <t>Senior Software Engineer - Python APIs</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MAERSK</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, Azure, GCP, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a42ffff2f95ecf4</t>
+          <t>https://www.indeed.com/viewjob?jk=0f063f9c882ccc12</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Hybrid)</t>
+          <t>Senior Software Engineer - Python APIs</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MAERSK</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,104 +1081,104 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, Azure, GCP, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83247939112593c0</t>
+          <t>https://www.indeed.com/viewjob?jk=a00e6d7208f216f0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AWS Database Engineer / Cloud DBA</t>
+          <t>Senior Software Engineer - Java</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>MAERSK</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc7b3e2ef98acf25</t>
+          <t>https://www.indeed.com/viewjob?jk=2a42ffff2f95ecf4</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Engineer (Hybrid)</t>
+          <t>Senior Software Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Enova International</t>
+          <t>MAERSK</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f180f27ff7393ac</t>
+          <t>https://www.indeed.com/viewjob?jk=83247939112593c0</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer (remote)</t>
+          <t>AWS Database Engineer / Cloud DBA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Claritev</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, GCP, Hadoop, Spark, Scala, Oracle, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Athena, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de8ee6455a8ca514</t>
+          <t>https://www.indeed.com/viewjob?jk=dc7b3e2ef98acf25</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SF Technology - Software Engineering - Senior Associate</t>
+          <t>Senior Business Intelligence Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Fannie Mae</t>
+          <t>Enova International</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, ECS, IAM, RDS, Spark, Scala</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ba575b133b119eb</t>
+          <t>https://www.indeed.com/viewjob?jk=9f180f27ff7393ac</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Data Engineer (remote)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Claritev</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,42 +1256,42 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, EMR, RDS, Azure, GCP, Hadoop, Spark, Scala, Oracle, Data Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=292c1ae20b051cf4</t>
+          <t>https://www.indeed.com/viewjob?jk=de8ee6455a8ca514</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Versant</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, GCP, Spark, Scala, PostgreSQL, NoSQL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f536b07e93637686</t>
+          <t>https://www.indeed.com/viewjob?jk=292c1ae20b051cf4</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Cloud Governance Engineer</t>
+          <t>SF Technology - Software Engineering - Senior Associate</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Fannie Mae</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, ELT, DataOps</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, ECS, IAM, RDS, Spark, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d20905b5e2faaa0</t>
+          <t>https://www.indeed.com/viewjob?jk=4ba575b133b119eb</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Versant</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, SQL Server, MLOps, CI/CD</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, GCP, Spark, Scala, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba4f4cd3ad0ce6f5</t>
+          <t>https://www.indeed.com/viewjob?jk=f536b07e93637686</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Cloud Governance Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, SQL Server, MLOps, CI/CD</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, ELT, DataOps</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f06821a24e8c6950</t>
+          <t>https://www.indeed.com/viewjob?jk=4d20905b5e2faaa0</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Engineer - Specialist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, SQL Server, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=936f1055bc6513a5</t>
+          <t>https://www.indeed.com/viewjob?jk=ba4f4cd3ad0ce6f5</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sr. Backend Engineer - Integrations</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, SQL Server, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22b8eb7f870c0ec5</t>
+          <t>https://www.indeed.com/viewjob?jk=f06821a24e8c6950</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Software Engineer - Specialist</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, NoSQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d07a1b512d8f6b8e</t>
+          <t>https://www.indeed.com/viewjob?jk=936f1055bc6513a5</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Sr. Backend Engineer - Integrations</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Scala, ETL, ELT, CI/CD, Jenkins</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a00dd6bd18f4d068</t>
+          <t>https://www.indeed.com/viewjob?jk=22b8eb7f870c0ec5</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Kharon</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,42 +1571,42 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, dbt</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Scala, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=429c2128943540c2</t>
+          <t>https://www.indeed.com/viewjob?jk=a00dd6bd18f4d068</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Science Engineer, GenAI Platforms &amp; Data Infrastructure</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, NoSQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,59 +1616,59 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21b925b3e52300cd</t>
+          <t>https://www.indeed.com/viewjob?jk=d07a1b512d8f6b8e</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Easterseals Southern California</t>
+          <t>Kharon</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Oracle, PostgreSQL</t>
+          <t>AWS, Glue, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2241b1872054f42d</t>
+          <t>https://www.indeed.com/viewjob?jk=429c2128943540c2</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>AWS API Engineer</t>
+          <t>Senior Data Science Engineer, GenAI Platforms &amp; Data Infrastructure</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Hive, MapReduce, Impala, Spark, PySpark, Oracle, SQL Server, MySQL</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be902deb0c0cff60</t>
+          <t>https://www.indeed.com/viewjob?jk=21b925b3e52300cd</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>E Source</t>
+          <t>Easterseals Southern California</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, PostgreSQL, ETL, Jenkins, Docker, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc74bb7856780dfe</t>
+          <t>https://www.indeed.com/viewjob?jk=2241b1872054f42d</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Consultant, AI &amp; Data Engineering</t>
+          <t>AWS API Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Castleton Tower</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, dbt</t>
+          <t>AWS, Hadoop, Hive, MapReduce, Impala, Spark, PySpark, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=106bb3c12b0ce283</t>
+          <t>https://www.indeed.com/viewjob?jk=be902deb0c0cff60</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Java SDK / Library Developer</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>E Source</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, PostgreSQL, ETL, Jenkins, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87bcb224d87d1611</t>
+          <t>https://www.indeed.com/viewjob?jk=cc74bb7856780dfe</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior Consultant, AI &amp; Data Engineering</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Castleton Tower</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Jenkins, Maven, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e59f80446549413</t>
+          <t>https://www.indeed.com/viewjob?jk=106bb3c12b0ce283</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Technical Architect - Data &amp; Analytics</t>
+          <t>Java SDK / Library Developer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>WinWire</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Newport Beach, CA, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Medallion Architecture, Snowflake, Oracle, SQL Server, ETL, dbt</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=668b3d9240bad8b3</t>
+          <t>https://www.indeed.com/viewjob?jk=87bcb224d87d1611</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Specialty Software Engineer - Capital Markets Reference Data</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37db4c0b07afe64d</t>
+          <t>https://www.indeed.com/viewjob?jk=2e59f80446549413</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Integration Developer</t>
+          <t>Technical Architect - Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>AlayaCare</t>
+          <t>WinWire</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Newport Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, S3, RDS, Azure, Medallion Architecture, Snowflake, Oracle, SQL Server, ETL, dbt</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e35070e714f42f3c</t>
+          <t>https://www.indeed.com/viewjob?jk=668b3d9240bad8b3</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Integration Developer</t>
+          <t>Senior Specialty Software Engineer - Capital Markets Reference Data</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>AlayaCare</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>API Gateway, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47a751a18a865523</t>
+          <t>https://www.indeed.com/viewjob?jk=37db4c0b07afe64d</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Integration Developer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>AlayaCare</t>
+          <t>HARVEST GROUP</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Scala, Snowflake, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5b72f3e295f2b38</t>
+          <t>https://www.indeed.com/viewjob?jk=d391d4aaecc47ecd</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Founding Engineers</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>HARVEST GROUP</t>
+          <t>Career Mentors</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Scala, Snowflake, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Databricks, GCP, Spark, Kafka, Snowflake, PostgreSQL, dbt, Tableau, MLflow</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d391d4aaecc47ecd</t>
+          <t>https://www.indeed.com/viewjob?jk=004a99e42e1b83ba</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=004a99e42e1b83ba</t>
+          <t>https://www.indeed.com/viewjob?jk=9cbf54fc5208e3a3</t>
         </is>
       </c>
     </row>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cbf54fc5208e3a3</t>
+          <t>https://www.indeed.com/viewjob?jk=3753908732fe77ab</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3753908732fe77ab</t>
+          <t>https://www.indeed.com/viewjob?jk=e30f253b6a8acf18</t>
         </is>
       </c>
     </row>
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e30f253b6a8acf18</t>
+          <t>https://www.indeed.com/viewjob?jk=20194c0f45aa2c81</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Founding Engineers</t>
+          <t>Senior Integration Developer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Career Mentors</t>
+          <t>AlayaCare</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Databricks, GCP, Spark, Kafka, Snowflake, PostgreSQL, dbt, Tableau, MLflow</t>
+          <t>AWS, Lambda, API Gateway, RDS, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20194c0f45aa2c81</t>
+          <t>https://www.indeed.com/viewjob?jk=e35070e714f42f3c</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Escalation Engineer (Python)</t>
+          <t>Senior Integration Developer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Varonis Systems</t>
+          <t>AlayaCare</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Lambda, API Gateway, RDS, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b19ab87ba97422d</t>
+          <t>https://www.indeed.com/viewjob?jk=47a751a18a865523</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Reliability Engineer</t>
+          <t>Senior Integration Developer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Fitch Group</t>
+          <t>AlayaCare</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Docker, Kubernetes, Git</t>
+          <t>AWS, Lambda, API Gateway, RDS, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb104709126cf2da</t>
+          <t>https://www.indeed.com/viewjob?jk=a5b72f3e295f2b38</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Escalation Engineer (Python)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Varonis Systems</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, API Gateway, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccbafc8be264e941</t>
+          <t>https://www.indeed.com/viewjob?jk=3b19ab87ba97422d</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Reliability Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>NRG Energy</t>
+          <t>Fitch Group</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Cloud Storage, Spark, Data Modeling, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=daf356dec855c3b1</t>
+          <t>https://www.indeed.com/viewjob?jk=bb104709126cf2da</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Identity AI / ML Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, Google Cloud Platform, Spark, PySpark, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4d3c4afd567d4dc</t>
+          <t>https://www.indeed.com/viewjob?jk=ccbafc8be264e941</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Engineer - Intermediate</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>NRG Energy</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Maven</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Cloud Storage, Spark, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00328cd20addd95f</t>
+          <t>https://www.indeed.com/viewjob?jk=daf356dec855c3b1</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Engineer - Intermediate</t>
+          <t>Identity AI / ML Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Maven</t>
+          <t>AWS, Kinesis, Azure, Google Cloud Platform, Spark, PySpark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1563bdd8162e56a</t>
+          <t>https://www.indeed.com/viewjob?jk=a4d3c4afd567d4dc</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Solutions Architect | AI</t>
+          <t>Software Engineer - Intermediate</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Trace3</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fba922bb2fd28863</t>
+          <t>https://www.indeed.com/viewjob?jk=00328cd20addd95f</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Solutions Architect | AI</t>
+          <t>Software Engineer - Intermediate</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Trace3</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dae082eb8598575</t>
+          <t>https://www.indeed.com/viewjob?jk=f1563bdd8162e56a</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63486d61003e0a4f</t>
+          <t>https://www.indeed.com/viewjob?jk=fba922bb2fd28863</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d4d0f879560eea6</t>
+          <t>https://www.indeed.com/viewjob?jk=3dae082eb8598575</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Engineer (remote)</t>
+          <t>Data Solutions Architect | AI</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Claritev</t>
+          <t>Trace3</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hive, Impala, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60d533f19b4463da</t>
+          <t>https://www.indeed.com/viewjob?jk=63486d61003e0a4f</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer (remote)</t>
+          <t>Data Solutions Architect | AI</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Claritev</t>
+          <t>Trace3</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,17 +2656,17 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hive, Impala, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa65c57599624378</t>
+          <t>https://www.indeed.com/viewjob?jk=7d4d0f879560eea6</t>
         </is>
       </c>
     </row>
@@ -2696,29 +2696,29 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9230bee4c19c2afb</t>
+          <t>https://www.indeed.com/viewjob?jk=60d533f19b4463da</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>AI Commercial &amp; ML Ops Engineer</t>
+          <t>Data Engineer (remote)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>MGM Resorts International</t>
+          <t>Claritev</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hive, Impala, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e59ac0d5620a4ae</t>
+          <t>https://www.indeed.com/viewjob?jk=aa65c57599624378</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Multi-Cloud Networking Engineer</t>
+          <t>Data Engineer (remote)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Claritev</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Redshift, API Gateway, ECS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hive, Impala, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e048a1fa8803abd</t>
+          <t>https://www.indeed.com/viewjob?jk=9230bee4c19c2afb</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Service Cloud Developer</t>
+          <t>Senior Software Engineer - .NET Developer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>ATG</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, S3, Azure, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2004304d091ff39</t>
+          <t>https://www.indeed.com/viewjob?jk=ac19d93a3fb22200</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Cloud Network Architect</t>
+          <t>Senior Software Engineer - .NET Developer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>ATG</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>North Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, S3, Azure, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a7d02622748f5d3</t>
+          <t>https://www.indeed.com/viewjob?jk=fa7419910a66d6b9</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>SENIOR POWER BI DEVELOPER (HYBRID - REDMOND, WA)</t>
+          <t>AI Commercial &amp; ML Ops Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Eurest</t>
+          <t>MGM Resorts International</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Redmond, WA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,14 +2876,14 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89664cddc02e354c</t>
+          <t>https://www.indeed.com/viewjob?jk=9e59ac0d5620a4ae</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Cloud Migration Engineer</t>
+          <t>Service Cloud Developer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, BigQuery, Snowflake, Data Modeling, Star Schema, dbt, Power BI, Tableau</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d795a30569c6d07</t>
+          <t>https://www.indeed.com/viewjob?jk=e2004304d091ff39</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Cloud Network Architect</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>WEX Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51f550253b36df98</t>
+          <t>https://www.indeed.com/viewjob?jk=0a7d02622748f5d3</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Development Engineer - AI</t>
+          <t>Sr Software Engineer, Fullstack</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Experian</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, SQS, Scala, Kafka, PostgreSQL, Splunk, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, SQL Server, Data Modeling, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,67 +2981,67 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=932a6480f7acd72e</t>
+          <t>https://www.indeed.com/viewjob?jk=4fb90dbd5192ef62</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Platform</t>
+          <t>Multi-Cloud Networking Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Redfin</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, Redshift, API Gateway, ECS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d62543661efd20a8</t>
+          <t>https://www.indeed.com/viewjob?jk=2e048a1fa8803abd</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - AI/ML Engineering Focus - Remote</t>
+          <t>Senior Cloud Migration Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>UnitedHealthcare</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Kafka, Databricks Lakehouse, ELT, MLOps, MLflow</t>
+          <t>Redshift, RDS, Azure, BigQuery, Snowflake, Data Modeling, Star Schema, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b996573f5f8fa39</t>
+          <t>https://www.indeed.com/viewjob?jk=1d795a30569c6d07</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Cloud Database Engineer</t>
+          <t>SENIOR POWER BI DEVELOPER (HYBRID - REDMOND, WA)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Eurest</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Smithfield, RI, US USA</t>
+          <t>Redmond, WA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dff9fd964893cca2</t>
+          <t>https://www.indeed.com/viewjob?jk=89664cddc02e354c</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Cloud Database Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Rosen's Diversified, Inc.</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Green Bay, WI, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd0834fa2eafaef3</t>
+          <t>https://www.indeed.com/viewjob?jk=43e06e046a3009ec</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Cloud Database Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Rosen's Diversified, Inc.</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Eagan, MN, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,19 +3156,19 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46aa6a7b0ccb9c57</t>
+          <t>https://www.indeed.com/viewjob?jk=0d5ed846b77ab548</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>MIS - Analytics Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Phillips &amp; Cohen Associates</t>
+          <t>WEX Inc.</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau, Git, Python</t>
+          <t>AWS, Azure, GCP, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb902b8c2dc0b4e3</t>
+          <t>https://www.indeed.com/viewjob?jk=51f550253b36df98</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>MIS - Analytics Engineer</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Phillips &amp; Cohen Associates</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau, Git, Python</t>
+          <t>AWS, Lambda, Redshift, Athena, S3, SQS, ECS, IAM, RDS, PostgreSQL</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=026772bfd10c6d83</t>
+          <t>https://www.indeed.com/viewjob?jk=c5c87f4d580328bb</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Customer Engineer</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Reltio</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Scala, DynamoDB, Cassandra, NoSQL, ELT</t>
+          <t>AWS, Lambda, Redshift, Athena, S3, SQS, ECS, IAM, RDS, PostgreSQL</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ceebc871c7b716e1</t>
+          <t>https://www.indeed.com/viewjob?jk=7f081e02510ebdea</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Customer Engineer</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Reltio</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,147 +3286,147 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Scala, DynamoDB, Cassandra, NoSQL, ELT</t>
+          <t>AWS, Lambda, Redshift, Athena, S3, SQS, ECS, IAM, RDS, PostgreSQL</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b48f55b509420cd6</t>
+          <t>https://www.indeed.com/viewjob?jk=2a5e445cdfb1f584</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Product Developer Advanced</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Tech Army</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, ETL, Power BI, Python</t>
+          <t>AWS, Lambda, Redshift, Athena, S3, SQS, ECS, IAM, RDS, PostgreSQL</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d958ebf75215c9a</t>
+          <t>https://www.indeed.com/viewjob?jk=bc6e81812acaa849</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Production Engineer</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Placer.ai</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, Redshift, Athena, S3, SQS, ECS, IAM, RDS, PostgreSQL</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad1335920bcdcf1c</t>
+          <t>https://www.indeed.com/viewjob?jk=b9b53627c8bb8781</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Digital Analytics Engineer - Customer Experience</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Sherwin-Williams</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Scala, Snowflake, Power BI, Tableau, Git, SQL</t>
+          <t>AWS, Lambda, Redshift, Athena, S3, SQS, ECS, IAM, RDS, PostgreSQL</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=724311be6474c008</t>
+          <t>https://www.indeed.com/viewjob?jk=0cb9f61bc8ba5e0c</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>MLOps Engineer - Machine Learning Platform</t>
+          <t>Senior Full Stack Software Development Engineer - AI</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Experian</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, IAM, GCP, Scala, NoSQL, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, SQS, Scala, Kafka, PostgreSQL, Splunk, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,102 +3436,102 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29ff9b97d0d69a97</t>
+          <t>https://www.indeed.com/viewjob?jk=932a6480f7acd72e</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Innovien Solutions</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Databricks, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Docker, Kubernetes, pytest</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19b0604cffe8cf9d</t>
+          <t>https://www.indeed.com/viewjob?jk=71acb476a93daa68</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Service Cloud Developer</t>
+          <t>Senior Software Engineer - Platform</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Redfin</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14f7aec210bdd6b1</t>
+          <t>https://www.indeed.com/viewjob?jk=d62543661efd20a8</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Data Scientist - AI/ML Engineering Focus - Remote</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>UnitedHealthcare</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Kafka, Databricks Lakehouse, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,269 +3541,269 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=377a8106189cff56</t>
+          <t>https://www.indeed.com/viewjob?jk=0b996573f5f8fa39</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Data Analytics and AI Senior Consultant</t>
+          <t>Senior Cloud Database Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Citrin Cooperman</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Florham Park, NJ, US USA</t>
+          <t>Smithfield, RI, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab24ee357dc36621</t>
+          <t>https://www.indeed.com/viewjob?jk=dff9fd964893cca2</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Data Analytics and AI Senior Consultant</t>
+          <t>Senior Cloud Database Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Citrin Cooperman</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebeab9493cf52705</t>
+          <t>https://www.indeed.com/viewjob?jk=cd0834fa2eafaef3</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Data Analytics and AI Senior Consultant</t>
+          <t>Senior Cloud Database Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Citrin Cooperman</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Braintree, MA, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd5fb31b5a0e0aed</t>
+          <t>https://www.indeed.com/viewjob?jk=46aa6a7b0ccb9c57</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Data Analytics and AI Senior Consultant</t>
+          <t>MIS - Analytics Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Citrin Cooperman</t>
+          <t>Phillips &amp; Cohen Associates</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
+          <t>RDS, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau, Git, Python</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35945946ef347401</t>
+          <t>https://www.indeed.com/viewjob?jk=fb902b8c2dc0b4e3</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Data Analytics and AI Senior Consultant</t>
+          <t>MIS - Analytics Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Citrin Cooperman</t>
+          <t>Phillips &amp; Cohen Associates</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
+          <t>RDS, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau, Git, Python</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98baf5e0e0e210ab</t>
+          <t>https://www.indeed.com/viewjob?jk=026772bfd10c6d83</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Data Analytics and AI Senior Consultant</t>
+          <t>Customer Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Citrin Cooperman</t>
+          <t>Reltio</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Scala, DynamoDB, Cassandra, NoSQL, ELT</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=619ef2ef0698f1fd</t>
+          <t>https://www.indeed.com/viewjob?jk=ceebc871c7b716e1</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Data Analytics and AI Senior Consultant</t>
+          <t>Customer Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Citrin Cooperman</t>
+          <t>Reltio</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Scala, DynamoDB, Cassandra, NoSQL, ELT</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16af3b0c4f8842cc</t>
+          <t>https://www.indeed.com/viewjob?jk=b48f55b509420cd6</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>AI/ML Software Engineer</t>
+          <t>Product Developer Advanced</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Numa Management Associates</t>
+          <t>Tech Army</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, MLOps, Docker</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, ETL, Power BI, Python</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b8199552143ed2c</t>
+          <t>https://www.indeed.com/viewjob?jk=8d958ebf75215c9a</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>AWS API Engineer</t>
+          <t>Production Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Placer.ai</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Hadoop, Spark, Scala, Kafka, MongoDB, NoSQL, Docker, Kubernetes</t>
+          <t>RDS, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd06c562a0dd4e4d</t>
+          <t>https://www.indeed.com/viewjob?jk=ad1335920bcdcf1c</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>AWS API Engineer</t>
+          <t>Senior Digital Analytics Engineer - Customer Experience</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Sherwin-Williams</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Hadoop, Spark, Scala, Kafka, MongoDB, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Databricks, Scala, Snowflake, Power BI, Tableau, Git, SQL</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7837b5aefbcb5351</t>
+          <t>https://www.indeed.com/viewjob?jk=724311be6474c008</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>AWS API Engineer</t>
+          <t>MLOps Engineer - Machine Learning Platform</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Hadoop, Spark, Scala, Kafka, MongoDB, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, IAM, GCP, Scala, NoSQL, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5edebdec5daaa4e1</t>
+          <t>https://www.indeed.com/viewjob?jk=29ff9b97d0d69a97</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Data Engineer (remote)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Claritev</t>
+          <t>Innovien Solutions</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, BigQuery, Spark, PySpark, Scala, ETL, ELT, DataOps</t>
+          <t>AWS, Lambda, Redshift, Databricks, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c836f48c3d814cb7</t>
+          <t>https://www.indeed.com/viewjob?jk=19b0604cffe8cf9d</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Service Cloud Developer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Total Quality Logistics (TQL)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Data Modeling, ELT, MLOps, MLflow, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16ea6e485299a08c</t>
+          <t>https://www.indeed.com/viewjob?jk=14f7aec210bdd6b1</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Total Quality Logistics (TQL)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Data Modeling, ELT, MLOps, MLflow, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, ECS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b999917838878a9</t>
+          <t>https://www.indeed.com/viewjob?jk=377a8106189cff56</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Data Analytics and AI Senior Consultant</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Total Quality Logistics (TQL)</t>
+          <t>Citrin Cooperman</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Florham Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Data Modeling, ELT, MLOps, MLflow, CI/CD, Azure DevOps, Docker</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d71435c6a86e8b64</t>
+          <t>https://www.indeed.com/viewjob?jk=ab24ee357dc36621</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Data Analytics and AI Senior Consultant</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>S.S. White Technologies</t>
+          <t>Citrin Cooperman</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,34 +4091,34 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc670920196ab795</t>
+          <t>https://www.indeed.com/viewjob?jk=ebeab9493cf52705</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Mid Level Software Engineer</t>
+          <t>Data Analytics and AI Senior Consultant</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Harvestaff</t>
+          <t>Citrin Cooperman</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Chesterfield, MO, US USA</t>
+          <t>Braintree, MA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,34 +4126,34 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>RDS, Azure, Oracle, SQL Server, PostgreSQL, MongoDB, Cassandra, NoSQL, Jenkins, Azure DevOps</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee62f5b48244cf04</t>
+          <t>https://www.indeed.com/viewjob?jk=bd5fb31b5a0e0aed</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Data Analytics and AI Senior Consultant</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Citrin Cooperman</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,34 +4161,34 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Terraform, Kubernetes, SonarQube</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8aca26123e673da7</t>
+          <t>https://www.indeed.com/viewjob?jk=35945946ef347401</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>OpenAM</t>
+          <t>Data Analytics and AI Senior Consultant</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Citrin Cooperman</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,34 +4196,34 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Azure, Scala, Kafka, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdf8975ebf0eb43f</t>
+          <t>https://www.indeed.com/viewjob?jk=98baf5e0e0e210ab</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Data Analytics and AI Senior Consultant</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>L&amp;T Technology Services Ltd.</t>
+          <t>Citrin Cooperman</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Novi, MI, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,34 +4231,34 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Hadoop, Spark, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8bace0705a89432</t>
+          <t>https://www.indeed.com/viewjob?jk=619ef2ef0698f1fd</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Solutions Engineer</t>
+          <t>Data Analytics and AI Senior Consultant</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Cellular Sales, Verizon Authorized Retailer</t>
+          <t>Citrin Cooperman</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,34 +4266,34 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, ETL, CI/CD, Docker</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9313901bc5ac9da</t>
+          <t>https://www.indeed.com/viewjob?jk=16af3b0c4f8842cc</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist, Programmatic Algorithms</t>
+          <t>AI/ML Software Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Impact.Com</t>
+          <t>Numa Management Associates</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>RDS, Databricks, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Kafka, MLOps</t>
+          <t>AWS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, MLOps, Docker</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e86578384aa4b6f</t>
+          <t>https://www.indeed.com/viewjob?jk=3b8199552143ed2c</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist, Programmatic Algorithms</t>
+          <t>AWS API Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Impact.Com</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>RDS, Databricks, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Kafka, MLOps</t>
+          <t>AWS, Databricks, Hadoop, Spark, Scala, Kafka, MongoDB, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0db61ba5b16e71bf</t>
+          <t>https://www.indeed.com/viewjob?jk=bd06c562a0dd4e4d</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Software Engineer - Core Platform</t>
+          <t>AWS API Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Unacast</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Snowflake, MySQL, DynamoDB, NoSQL, GitHub Actions, Git</t>
+          <t>AWS, Databricks, Hadoop, Spark, Scala, Kafka, MongoDB, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=868f8c4ef1ebde56</t>
+          <t>https://www.indeed.com/viewjob?jk=7837b5aefbcb5351</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>IT Business Analyst II</t>
+          <t>AWS API Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>NFI Industries</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,17 +4406,752 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
+          <t>AWS, Databricks, Hadoop, Spark, Scala, Kafka, MongoDB, NoSQL, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5edebdec5daaa4e1</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Data Engineer (remote)</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Claritev</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, BigQuery, Spark, PySpark, Scala, ETL, ELT, DataOps</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c836f48c3d814cb7</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>DevOps Prime</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f2c9a4c0d1556c3d</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>DevOps Prime</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Wichita, KS, US USA</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bdda93ad98da9aec</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>DevOps Prime</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e5d0a6d38e25b0a0</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>DevOps Prime</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Orlando, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d02c7ff4534ba5bd</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>DevOps Prime</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fd8abfee5fbd9116</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>AI Architect</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Total Quality Logistics (TQL)</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Data Modeling, ELT, MLOps, MLflow, CI/CD, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=16ea6e485299a08c</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>AI Architect</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Total Quality Logistics (TQL)</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Data Modeling, ELT, MLOps, MLflow, CI/CD, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7b999917838878a9</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>AI Architect</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Total Quality Logistics (TQL)</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Data Modeling, ELT, MLOps, MLflow, CI/CD, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d71435c6a86e8b64</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Software Developer</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>S.S. White Technologies</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Saint Petersburg, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>AWS, ECS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dc670920196ab795</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Django/Python</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>ATG</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>North Little Rock, AR, US USA</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e959c5c2ece017ba</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Django/Python</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>ATG</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=df9a48331ce93c56</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Mid Level Software Engineer</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Harvestaff</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Chesterfield, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Oracle, SQL Server, PostgreSQL, MongoDB, Cassandra, NoSQL, Jenkins, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ee62f5b48244cf04</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Engineer/Sr Engineer, IT Software</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>American Airlines</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Terraform, Kubernetes, SonarQube</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8aca26123e673da7</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>OpenAM</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Azure, Scala, Kafka, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fdf8975ebf0eb43f</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Software Developer</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>L&amp;T Technology Services Ltd.</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Novi, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Azure, Databricks, Hadoop, Spark, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b8bace0705a89432</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Sr. Data Scientist, Programmatic Algorithms</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Impact.Com</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>RDS, Databricks, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Kafka, MLOps</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4e86578384aa4b6f</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Sr. Data Scientist, Programmatic Algorithms</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Impact.Com</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>RDS, Databricks, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Kafka, MLOps</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0db61ba5b16e71bf</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Software Engineer - Core Platform</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Unacast</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Ashburn, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Spark, Scala, Snowflake, MySQL, DynamoDB, NoSQL, GitHub Actions, Git</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=868f8c4ef1ebde56</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>IT Business Analyst II</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>NFI Industries</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Camden, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
           <t>AWS, ECS, RDS, Azure, Spark, PySpark, Snowflake, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
-      <c r="F114" t="inlineStr">
+      <c r="F134" t="inlineStr">
         <is>
           <t>2026-04-24</t>
         </is>
       </c>
-      <c r="G114" t="inlineStr">
+      <c r="G134" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=b12be44615688132</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Solutions Engineer</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Cellular Sales, Verizon Authorized Retailer</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Knoxville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, ETL, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f9313901bc5ac9da</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-28.xlsx
+++ b/results/job_matches_2026-04-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G135"/>
+  <dimension ref="A1:G138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,25 +643,25 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Solutions Engineer</t>
+          <t>Snowflake Architect - Job ID 831</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Cloudera</t>
+          <t>Kapitus</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, HDFS, Hive, HBase, YARN, Impala, Spark</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, IAM, RDS, Databricks</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6db37997e354b1b6</t>
+          <t>https://www.indeed.com/viewjob?jk=30116c3087096b0c</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Snowflake Architect - Job ID 831</t>
+          <t>Customer Support Developer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Kapitus</t>
+          <t>Airbyte</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, IAM, RDS, Databricks</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30116c3087096b0c</t>
+          <t>https://www.indeed.com/viewjob?jk=ab2390ad9f6c9780</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab2390ad9f6c9780</t>
+          <t>https://www.indeed.com/viewjob?jk=a7fe60e6480b1a64</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Customer Support Developer</t>
+          <t>API Security IAM</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Airbyte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,14 +776,14 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7fe60e6480b1a64</t>
+          <t>https://www.indeed.com/viewjob?jk=0585ca531cf89a02</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>API Security IAM</t>
+          <t>AWS API Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, S3, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0585ca531cf89a02</t>
+          <t>https://www.indeed.com/viewjob?jk=8e2967a40f711a6e</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AWS API Engineer</t>
+          <t>Data Engineer - Snowflake</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Corebridge</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Glue, Redshift, RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e2967a40f711a6e</t>
+          <t>https://www.indeed.com/viewjob?jk=d3afad6ecd5a25a2</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AWS API Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Old National Bank</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Lake Elmo, MN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58d405ceae103971</t>
+          <t>https://www.indeed.com/viewjob?jk=dcce665f3a3b0fee</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer - Snowflake</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Corebridge</t>
+          <t>Old National Bank</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Lake Elmo, MN, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3afad6ecd5a25a2</t>
+          <t>https://www.indeed.com/viewjob?jk=58d405ceae103971</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AWS API Engineer</t>
+          <t>Senior PS Sales Solutions Architect</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,69 +941,69 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, MongoDB</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcce665f3a3b0fee</t>
+          <t>https://www.indeed.com/viewjob?jk=9ed1a2a8d040517b</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior PS Sales Solutions Architect</t>
+          <t>Site Reliability Engineering (SRE) Intern</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Calix</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ed1a2a8d040517b</t>
+          <t>https://www.indeed.com/viewjob?jk=b66b9b991f001a00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Site Reliability Engineering (SRE) Intern</t>
+          <t>Senior Software Engineer - Python APIs</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Calix</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, Azure, GCP, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b66b9b991f001a00</t>
+          <t>https://www.indeed.com/viewjob?jk=0f063f9c882ccc12</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f063f9c882ccc12</t>
+          <t>https://www.indeed.com/viewjob?jk=a00e6d7208f216f0</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Python APIs</t>
+          <t>Senior Software Engineer - Java</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>MAERSK</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,24 +1081,24 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, Azure, GCP, Scala, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a00e6d7208f216f0</t>
+          <t>https://www.indeed.com/viewjob?jk=2a42ffff2f95ecf4</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Java</t>
+          <t>Senior Software Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1121,64 +1121,64 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a42ffff2f95ecf4</t>
+          <t>https://www.indeed.com/viewjob?jk=83247939112593c0</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Hybrid)</t>
+          <t>Senior Business Intelligence Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MAERSK</t>
+          <t>Enova International</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83247939112593c0</t>
+          <t>https://www.indeed.com/viewjob?jk=9f180f27ff7393ac</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AWS Database Engineer / Cloud DBA</t>
+          <t>Data Engineer (remote)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Claritev</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, EMR, RDS, Azure, GCP, Hadoop, Spark, Scala, Oracle, Data Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc7b3e2ef98acf25</t>
+          <t>https://www.indeed.com/viewjob?jk=de8ee6455a8ca514</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Engineer (Hybrid)</t>
+          <t>AWS Database Engineer / Cloud DBA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Enova International</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, Glue, Lambda, Athena, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f180f27ff7393ac</t>
+          <t>https://www.indeed.com/viewjob?jk=dc7b3e2ef98acf25</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer (remote)</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Claritev</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, GCP, Hadoop, Spark, Scala, Oracle, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de8ee6455a8ca514</t>
+          <t>https://www.indeed.com/viewjob?jk=292c1ae20b051cf4</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>SF Technology - Software Engineering - Senior Associate</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Fannie Mae</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, ECS, IAM, RDS, Spark, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=292c1ae20b051cf4</t>
+          <t>https://www.indeed.com/viewjob?jk=4ba575b133b119eb</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SF Technology - Software Engineering - Senior Associate</t>
+          <t>Software Engineer - Specialist</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Fannie Mae</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, ECS, IAM, RDS, Spark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ba575b133b119eb</t>
+          <t>https://www.indeed.com/viewjob?jk=936f1055bc6513a5</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Versant</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, GCP, Spark, Scala, PostgreSQL, NoSQL</t>
+          <t>AWS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, SQL Server, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f536b07e93637686</t>
+          <t>https://www.indeed.com/viewjob?jk=ba4f4cd3ad0ce6f5</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Cloud Governance Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, ELT, DataOps</t>
+          <t>AWS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, SQL Server, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d20905b5e2faaa0</t>
+          <t>https://www.indeed.com/viewjob?jk=f06821a24e8c6950</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Versant</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, SQL Server, MLOps, CI/CD</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, GCP, Spark, Scala, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba4f4cd3ad0ce6f5</t>
+          <t>https://www.indeed.com/viewjob?jk=f536b07e93637686</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Cloud Governance Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, SQL Server, MLOps, CI/CD</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, ELT, DataOps</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f06821a24e8c6950</t>
+          <t>https://www.indeed.com/viewjob?jk=4d20905b5e2faaa0</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Engineer - Specialist</t>
+          <t>Sr. Backend Engineer - Integrations</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=936f1055bc6513a5</t>
+          <t>https://www.indeed.com/viewjob?jk=22b8eb7f870c0ec5</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sr. Backend Engineer - Integrations</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Aroha Technologies</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, Glue, S3, IAM, Azure, Databricks, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22b8eb7f870c0ec5</t>
+          <t>https://www.indeed.com/viewjob?jk=7f7113fe3fafcf1f</t>
         </is>
       </c>
     </row>
@@ -1868,17 +1868,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Founding Engineers</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Career Mentors</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Jenkins, Maven, Docker</t>
+          <t>AWS, Databricks, GCP, Spark, Kafka, Snowflake, PostgreSQL, dbt, Tableau, MLflow</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e59f80446549413</t>
+          <t>https://www.indeed.com/viewjob?jk=004a99e42e1b83ba</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Technical Architect - Data &amp; Analytics</t>
+          <t>Founding Engineers</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>WinWire</t>
+          <t>Career Mentors</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Newport Beach, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Medallion Architecture, Snowflake, Oracle, SQL Server, ETL, dbt</t>
+          <t>AWS, Databricks, GCP, Spark, Kafka, Snowflake, PostgreSQL, dbt, Tableau, MLflow</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=668b3d9240bad8b3</t>
+          <t>https://www.indeed.com/viewjob?jk=9cbf54fc5208e3a3</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Specialty Software Engineer - Capital Markets Reference Data</t>
+          <t>Founding Engineers</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Career Mentors</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, CI/CD, GitHub Actions</t>
+          <t>AWS, Databricks, GCP, Spark, Kafka, Snowflake, PostgreSQL, dbt, Tableau, MLflow</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37db4c0b07afe64d</t>
+          <t>https://www.indeed.com/viewjob?jk=3753908732fe77ab</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Founding Engineers</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>HARVEST GROUP</t>
+          <t>Career Mentors</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Scala, Snowflake, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Databricks, GCP, Spark, Kafka, Snowflake, PostgreSQL, dbt, Tableau, MLflow</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d391d4aaecc47ecd</t>
+          <t>https://www.indeed.com/viewjob?jk=e30f253b6a8acf18</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=004a99e42e1b83ba</t>
+          <t>https://www.indeed.com/viewjob?jk=20194c0f45aa2c81</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Founding Engineers</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Career Mentors</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Databricks, GCP, Spark, Kafka, Snowflake, PostgreSQL, dbt, Tableau, MLflow</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cbf54fc5208e3a3</t>
+          <t>https://www.indeed.com/viewjob?jk=2e59f80446549413</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Founding Engineers</t>
+          <t>Technical Architect - Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Career Mentors</t>
+          <t>WinWire</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Newport Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Databricks, GCP, Spark, Kafka, Snowflake, PostgreSQL, dbt, Tableau, MLflow</t>
+          <t>AWS, S3, RDS, Azure, Medallion Architecture, Snowflake, Oracle, SQL Server, ETL, dbt</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3753908732fe77ab</t>
+          <t>https://www.indeed.com/viewjob?jk=668b3d9240bad8b3</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Founding Engineers</t>
+          <t>Senior Specialty Software Engineer - Capital Markets Reference Data</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Career Mentors</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Databricks, GCP, Spark, Kafka, Snowflake, PostgreSQL, dbt, Tableau, MLflow</t>
+          <t>API Gateway, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e30f253b6a8acf18</t>
+          <t>https://www.indeed.com/viewjob?jk=37db4c0b07afe64d</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Founding Engineers</t>
+          <t>Senior Integration Developer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Career Mentors</t>
+          <t>AlayaCare</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Databricks, GCP, Spark, Kafka, Snowflake, PostgreSQL, dbt, Tableau, MLflow</t>
+          <t>AWS, Lambda, API Gateway, RDS, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20194c0f45aa2c81</t>
+          <t>https://www.indeed.com/viewjob?jk=e35070e714f42f3c</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e35070e714f42f3c</t>
+          <t>https://www.indeed.com/viewjob?jk=47a751a18a865523</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47a751a18a865523</t>
+          <t>https://www.indeed.com/viewjob?jk=a5b72f3e295f2b38</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Integration Developer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>AlayaCare</t>
+          <t>HARVEST GROUP</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Scala, Snowflake, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5b72f3e295f2b38</t>
+          <t>https://www.indeed.com/viewjob?jk=d391d4aaecc47ecd</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Reliability Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Fitch Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb104709126cf2da</t>
+          <t>https://www.indeed.com/viewjob?jk=ccbafc8be264e941</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer - Intermediate</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccbafc8be264e941</t>
+          <t>https://www.indeed.com/viewjob?jk=00328cd20addd95f</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer - Intermediate</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>NRG Energy</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Cloud Storage, Spark, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=daf356dec855c3b1</t>
+          <t>https://www.indeed.com/viewjob?jk=f1563bdd8162e56a</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Identity AI / ML Engineer</t>
+          <t>Data Solutions Architect | AI</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Trace3</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, Google Cloud Platform, Spark, PySpark, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4d3c4afd567d4dc</t>
+          <t>https://www.indeed.com/viewjob?jk=fba922bb2fd28863</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Engineer - Intermediate</t>
+          <t>Data Solutions Architect | AI</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Trace3</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Maven</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00328cd20addd95f</t>
+          <t>https://www.indeed.com/viewjob?jk=3dae082eb8598575</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Software Engineer - Intermediate</t>
+          <t>Data Solutions Architect | AI</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Trace3</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Maven</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1563bdd8162e56a</t>
+          <t>https://www.indeed.com/viewjob?jk=63486d61003e0a4f</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fba922bb2fd28863</t>
+          <t>https://www.indeed.com/viewjob?jk=7d4d0f879560eea6</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Solutions Architect | AI</t>
+          <t>Data Engineer (remote)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Trace3</t>
+          <t>Claritev</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hive, Impala, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dae082eb8598575</t>
+          <t>https://www.indeed.com/viewjob?jk=60d533f19b4463da</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Solutions Architect | AI</t>
+          <t>Data Engineer (remote)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Trace3</t>
+          <t>Claritev</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hive, Impala, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63486d61003e0a4f</t>
+          <t>https://www.indeed.com/viewjob?jk=aa65c57599624378</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Solutions Architect | AI</t>
+          <t>Data Engineer (remote)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Trace3</t>
+          <t>Claritev</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hive, Impala, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d4d0f879560eea6</t>
+          <t>https://www.indeed.com/viewjob?jk=9230bee4c19c2afb</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer (remote)</t>
+          <t>Senior Reliability Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Claritev</t>
+          <t>Fitch Group</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hive, Impala, Spark, PySpark, Scala</t>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60d533f19b4463da</t>
+          <t>https://www.indeed.com/viewjob?jk=bb104709126cf2da</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer (remote)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Claritev</t>
+          <t>NRG Energy</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hive, Impala, Spark, PySpark, Scala</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Cloud Storage, Spark, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa65c57599624378</t>
+          <t>https://www.indeed.com/viewjob?jk=daf356dec855c3b1</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer (remote)</t>
+          <t>Identity AI / ML Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Claritev</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hive, Impala, Spark, PySpark, Scala</t>
+          <t>AWS, Kinesis, Azure, Google Cloud Platform, Spark, PySpark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9230bee4c19c2afb</t>
+          <t>https://www.indeed.com/viewjob?jk=a4d3c4afd567d4dc</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - .NET Developer</t>
+          <t>AI Commercial &amp; ML Ops Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>ATG</t>
+          <t>MGM Resorts International</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac19d93a3fb22200</t>
+          <t>https://www.indeed.com/viewjob?jk=9e59ac0d5620a4ae</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - .NET Developer</t>
+          <t>Backend Developer- Dallas, TX</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>ATG</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>North Little Rock, AR, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, S3, IAM, Scala, Kafka, PostgreSQL, MongoDB, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa7419910a66d6b9</t>
+          <t>https://www.indeed.com/viewjob?jk=c6cf88579d0b139b</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>AI Commercial &amp; ML Ops Engineer</t>
+          <t>Backend Developer- Dallas, TX</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>MGM Resorts International</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLflow, CI/CD</t>
+          <t>AWS, S3, IAM, Scala, Kafka, PostgreSQL, MongoDB, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e59ac0d5620a4ae</t>
+          <t>https://www.indeed.com/viewjob?jk=9d29f0c0f97c6ad9</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Service Cloud Developer</t>
+          <t>Implementation Consultant - Solutions Architect</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>New Relic</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,14 +2911,14 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2004304d091ff39</t>
+          <t>https://www.indeed.com/viewjob?jk=73dc903c92ca8eb2</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Cloud Network Architect</t>
+          <t>Multi-Cloud Networking Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, Redshift, API Gateway, ECS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a7d02622748f5d3</t>
+          <t>https://www.indeed.com/viewjob?jk=2e048a1fa8803abd</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sr Software Engineer, Fullstack</t>
+          <t>BackEnd Developer- Dallas, TX</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, SQL Server, Data Modeling, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, Scala, PostgreSQL, DynamoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fb90dbd5192ef62</t>
+          <t>https://www.indeed.com/viewjob?jk=eaf41f1dcd53eba3</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Multi-Cloud Networking Engineer</t>
+          <t>BackEnd Developer- Dallas, TX</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,24 +3006,24 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Redshift, API Gateway, ECS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, Scala, PostgreSQL, DynamoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e048a1fa8803abd</t>
+          <t>https://www.indeed.com/viewjob?jk=f4936cea15fb6fab</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Cloud Migration Engineer</t>
+          <t>Service Cloud Developer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, BigQuery, Snowflake, Data Modeling, Star Schema, dbt, Power BI, Tableau</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d795a30569c6d07</t>
+          <t>https://www.indeed.com/viewjob?jk=e2004304d091ff39</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>SENIOR POWER BI DEVELOPER (HYBRID - REDMOND, WA)</t>
+          <t>Cloud Network Architect</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Eurest</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Redmond, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89664cddc02e354c</t>
+          <t>https://www.indeed.com/viewjob?jk=0a7d02622748f5d3</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Sr Software Engineer, Fullstack</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Rosen's Diversified, Inc.</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Green Bay, WI, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, SQL Server, Data Modeling, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43e06e046a3009ec</t>
+          <t>https://www.indeed.com/viewjob?jk=4fb90dbd5192ef62</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>SENIOR POWER BI DEVELOPER (HYBRID - REDMOND, WA)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Rosen's Diversified, Inc.</t>
+          <t>Eurest</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Eagan, MN, US USA</t>
+          <t>Redmond, WA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d5ed846b77ab548</t>
+          <t>https://www.indeed.com/viewjob?jk=89664cddc02e354c</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Cloud Migration Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>WEX Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>Redshift, RDS, Azure, BigQuery, Snowflake, Data Modeling, Star Schema, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51f550253b36df98</t>
+          <t>https://www.indeed.com/viewjob?jk=1d795a30569c6d07</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Rosen's Diversified, Inc.</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Green Bay, WI, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Athena, S3, SQS, ECS, IAM, RDS, PostgreSQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5c87f4d580328bb</t>
+          <t>https://www.indeed.com/viewjob?jk=43e06e046a3009ec</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Rosen's Diversified, Inc.</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Eagan, MN, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Athena, S3, SQS, ECS, IAM, RDS, PostgreSQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f081e02510ebdea</t>
+          <t>https://www.indeed.com/viewjob?jk=0d5ed846b77ab548</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>WEX Inc.</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,24 +3286,24 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Athena, S3, SQS, ECS, IAM, RDS, PostgreSQL</t>
+          <t>AWS, Azure, GCP, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a5e445cdfb1f584</t>
+          <t>https://www.indeed.com/viewjob?jk=51f550253b36df98</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Athena, S3, SQS, ECS, IAM, RDS, PostgreSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Docker, Kubernetes, pytest</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc6e81812acaa849</t>
+          <t>https://www.indeed.com/viewjob?jk=71acb476a93daa68</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9b53627c8bb8781</t>
+          <t>https://www.indeed.com/viewjob?jk=c5c87f4d580328bb</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cb9f61bc8ba5e0c</t>
+          <t>https://www.indeed.com/viewjob?jk=7f081e02510ebdea</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Development Engineer - AI</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Experian</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,24 +3426,24 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, SQS, Scala, Kafka, PostgreSQL, Splunk, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Redshift, Athena, S3, SQS, ECS, IAM, RDS, PostgreSQL</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=932a6480f7acd72e</t>
+          <t>https://www.indeed.com/viewjob?jk=2a5e445cdfb1f584</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Docker, Kubernetes, pytest</t>
+          <t>AWS, Lambda, Redshift, Athena, S3, SQS, ECS, IAM, RDS, PostgreSQL</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71acb476a93daa68</t>
+          <t>https://www.indeed.com/viewjob?jk=bc6e81812acaa849</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Platform</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Redfin</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, Lambda, Redshift, Athena, S3, SQS, ECS, IAM, RDS, PostgreSQL</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d62543661efd20a8</t>
+          <t>https://www.indeed.com/viewjob?jk=b9b53627c8bb8781</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - AI/ML Engineering Focus - Remote</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>UnitedHealthcare</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Kafka, Databricks Lakehouse, ELT, MLOps, MLflow</t>
+          <t>AWS, Lambda, Redshift, Athena, S3, SQS, ECS, IAM, RDS, PostgreSQL</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b996573f5f8fa39</t>
+          <t>https://www.indeed.com/viewjob?jk=0cb9f61bc8ba5e0c</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Cloud Database Engineer</t>
+          <t>Senior Full Stack Software Development Engineer - AI</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Experian</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Smithfield, RI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, SQS, Scala, Kafka, PostgreSQL, Splunk, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dff9fd964893cca2</t>
+          <t>https://www.indeed.com/viewjob?jk=932a6480f7acd72e</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Cloud Database Engineer</t>
+          <t>Senior Software Engineer - Platform</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Redfin</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd0834fa2eafaef3</t>
+          <t>https://www.indeed.com/viewjob?jk=d62543661efd20a8</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Cloud Database Engineer</t>
+          <t>Senior Data Scientist - AI/ML Engineering Focus - Remote</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>UnitedHealthcare</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Kafka, Databricks Lakehouse, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46aa6a7b0ccb9c57</t>
+          <t>https://www.indeed.com/viewjob?jk=0b996573f5f8fa39</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>MIS - Analytics Engineer</t>
+          <t>Senior Cloud Database Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Phillips &amp; Cohen Associates</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Smithfield, RI, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau, Git, Python</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb902b8c2dc0b4e3</t>
+          <t>https://www.indeed.com/viewjob?jk=dff9fd964893cca2</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>MIS - Analytics Engineer</t>
+          <t>Senior Cloud Database Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Phillips &amp; Cohen Associates</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RDS, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau, Git, Python</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=026772bfd10c6d83</t>
+          <t>https://www.indeed.com/viewjob?jk=cd0834fa2eafaef3</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Customer Engineer</t>
+          <t>Senior Cloud Database Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Reltio</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Scala, DynamoDB, Cassandra, NoSQL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ceebc871c7b716e1</t>
+          <t>https://www.indeed.com/viewjob?jk=46aa6a7b0ccb9c57</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Customer Engineer</t>
+          <t>MIS - Analytics Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Reltio</t>
+          <t>Phillips &amp; Cohen Associates</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Scala, DynamoDB, Cassandra, NoSQL, ELT</t>
+          <t>RDS, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau, Git, Python</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,32 +3786,32 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b48f55b509420cd6</t>
+          <t>https://www.indeed.com/viewjob?jk=fb902b8c2dc0b4e3</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Product Developer Advanced</t>
+          <t>MIS - Analytics Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Tech Army</t>
+          <t>Phillips &amp; Cohen Associates</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, ETL, Power BI, Python</t>
+          <t>RDS, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau, Git, Python</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,32 +3821,32 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d958ebf75215c9a</t>
+          <t>https://www.indeed.com/viewjob?jk=026772bfd10c6d83</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Production Engineer</t>
+          <t>Customer Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Placer.ai</t>
+          <t>Reltio</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>RDS, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Scala, DynamoDB, Cassandra, NoSQL, ELT</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,32 +3856,32 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad1335920bcdcf1c</t>
+          <t>https://www.indeed.com/viewjob?jk=ceebc871c7b716e1</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Digital Analytics Engineer - Customer Experience</t>
+          <t>Customer Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Sherwin-Williams</t>
+          <t>Reltio</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Scala, Snowflake, Power BI, Tableau, Git, SQL</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Scala, DynamoDB, Cassandra, NoSQL, ELT</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=724311be6474c008</t>
+          <t>https://www.indeed.com/viewjob?jk=b48f55b509420cd6</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>MLOps Engineer - Machine Learning Platform</t>
+          <t>AI/ML Software Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Numa Management Associates</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, IAM, GCP, Scala, NoSQL, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, MLOps, Docker</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29ff9b97d0d69a97</t>
+          <t>https://www.indeed.com/viewjob?jk=3b8199552143ed2c</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AWS API Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Innovien Solutions</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Databricks, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Databricks, Hadoop, Spark, Scala, Kafka, MongoDB, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,14 +3961,14 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19b0604cffe8cf9d</t>
+          <t>https://www.indeed.com/viewjob?jk=bd06c562a0dd4e4d</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Service Cloud Developer</t>
+          <t>AWS API Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
+          <t>AWS, Databricks, Hadoop, Spark, Scala, Kafka, MongoDB, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14f7aec210bdd6b1</t>
+          <t>https://www.indeed.com/viewjob?jk=7837b5aefbcb5351</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>AWS API Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Databricks, Hadoop, Spark, Scala, Kafka, MongoDB, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=377a8106189cff56</t>
+          <t>https://www.indeed.com/viewjob?jk=5edebdec5daaa4e1</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Data Analytics and AI Senior Consultant</t>
+          <t>Data Engineer (remote)</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Citrin Cooperman</t>
+          <t>Claritev</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Florham Park, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
+          <t>AWS, RDS, Databricks, BigQuery, Spark, PySpark, Scala, ETL, ELT, DataOps</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab24ee357dc36621</t>
+          <t>https://www.indeed.com/viewjob?jk=c836f48c3d814cb7</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Data Analytics and AI Senior Consultant</t>
+          <t>Product Developer Advanced</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Citrin Cooperman</t>
+          <t>Tech Army</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,34 +4091,34 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, ETL, Power BI, Python</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebeab9493cf52705</t>
+          <t>https://www.indeed.com/viewjob?jk=8d958ebf75215c9a</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Data Analytics and AI Senior Consultant</t>
+          <t>Production Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Citrin Cooperman</t>
+          <t>Placer.ai</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Braintree, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,34 +4126,34 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
+          <t>RDS, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd5fb31b5a0e0aed</t>
+          <t>https://www.indeed.com/viewjob?jk=ad1335920bcdcf1c</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Data Analytics and AI Senior Consultant</t>
+          <t>Senior Digital Analytics Engineer - Customer Experience</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Citrin Cooperman</t>
+          <t>Sherwin-Williams</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,34 +4161,34 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
+          <t>AWS, IAM, RDS, Databricks, Scala, Snowflake, Power BI, Tableau, Git, SQL</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35945946ef347401</t>
+          <t>https://www.indeed.com/viewjob?jk=724311be6474c008</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Data Analytics and AI Senior Consultant</t>
+          <t>MLOps Engineer - Machine Learning Platform</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Citrin Cooperman</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,34 +4196,34 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
+          <t>AWS, IAM, GCP, Scala, NoSQL, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98baf5e0e0e210ab</t>
+          <t>https://www.indeed.com/viewjob?jk=29ff9b97d0d69a97</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Data Analytics and AI Senior Consultant</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Citrin Cooperman</t>
+          <t>Innovien Solutions</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,34 +4231,34 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
+          <t>AWS, Lambda, Redshift, Databricks, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=619ef2ef0698f1fd</t>
+          <t>https://www.indeed.com/viewjob?jk=19b0604cffe8cf9d</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Data Analytics and AI Senior Consultant</t>
+          <t>Service Cloud Developer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Citrin Cooperman</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,34 +4266,34 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
+          <t>AWS, RDS, Azure, Data Factory, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16af3b0c4f8842cc</t>
+          <t>https://www.indeed.com/viewjob?jk=14f7aec210bdd6b1</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>AI/ML Software Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Numa Management Associates</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, MLOps, Docker</t>
+          <t>AWS, ECS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b8199552143ed2c</t>
+          <t>https://www.indeed.com/viewjob?jk=377a8106189cff56</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>AWS API Engineer</t>
+          <t>Data Analytics and AI Senior Consultant</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Citrin Cooperman</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Florham Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,34 +4336,34 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Hadoop, Spark, Scala, Kafka, MongoDB, NoSQL, Docker, Kubernetes</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd06c562a0dd4e4d</t>
+          <t>https://www.indeed.com/viewjob?jk=ab24ee357dc36621</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>AWS API Engineer</t>
+          <t>Data Analytics and AI Senior Consultant</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Citrin Cooperman</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,34 +4371,34 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Hadoop, Spark, Scala, Kafka, MongoDB, NoSQL, Docker, Kubernetes</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7837b5aefbcb5351</t>
+          <t>https://www.indeed.com/viewjob?jk=ebeab9493cf52705</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>AWS API Engineer</t>
+          <t>Data Analytics and AI Senior Consultant</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Citrin Cooperman</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Braintree, MA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,34 +4406,34 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Hadoop, Spark, Scala, Kafka, MongoDB, NoSQL, Docker, Kubernetes</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5edebdec5daaa4e1</t>
+          <t>https://www.indeed.com/viewjob?jk=bd5fb31b5a0e0aed</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Data Engineer (remote)</t>
+          <t>Data Analytics and AI Senior Consultant</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Claritev</t>
+          <t>Citrin Cooperman</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,34 +4441,34 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, BigQuery, Spark, PySpark, Scala, ETL, ELT, DataOps</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c836f48c3d814cb7</t>
+          <t>https://www.indeed.com/viewjob?jk=35945946ef347401</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>DevOps Prime</t>
+          <t>Data Analytics and AI Senior Consultant</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Citrin Cooperman</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,34 +4476,34 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2c9a4c0d1556c3d</t>
+          <t>https://www.indeed.com/viewjob?jk=98baf5e0e0e210ab</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>DevOps Prime</t>
+          <t>Data Analytics and AI Senior Consultant</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Citrin Cooperman</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,34 +4511,34 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdda93ad98da9aec</t>
+          <t>https://www.indeed.com/viewjob?jk=619ef2ef0698f1fd</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>DevOps Prime</t>
+          <t>Data Analytics and AI Senior Consultant</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Citrin Cooperman</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,17 +4546,17 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5d0a6d38e25b0a0</t>
+          <t>https://www.indeed.com/viewjob?jk=16af3b0c4f8842cc</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d02c7ff4534ba5bd</t>
+          <t>https://www.indeed.com/viewjob?jk=f2c9a4c0d1556c3d</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd8abfee5fbd9116</t>
+          <t>https://www.indeed.com/viewjob?jk=bdda93ad98da9aec</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>DevOps Prime</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Total Quality Logistics (TQL)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,34 +4651,34 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Data Modeling, ELT, MLOps, MLflow, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, Lambda, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16ea6e485299a08c</t>
+          <t>https://www.indeed.com/viewjob?jk=e5d0a6d38e25b0a0</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>DevOps Prime</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Total Quality Logistics (TQL)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,34 +4686,34 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Data Modeling, ELT, MLOps, MLflow, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, Lambda, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b999917838878a9</t>
+          <t>https://www.indeed.com/viewjob?jk=d02c7ff4534ba5bd</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>DevOps Prime</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Total Quality Logistics (TQL)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,34 +4721,34 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Data Modeling, ELT, MLOps, MLflow, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, Lambda, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d71435c6a86e8b64</t>
+          <t>https://www.indeed.com/viewjob?jk=fd8abfee5fbd9116</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Senior Software Engineer - Django/Python</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>S.S. White Technologies</t>
+          <t>ATG</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>North Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,17 +4756,17 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, S3, Azure, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc670920196ab795</t>
+          <t>https://www.indeed.com/viewjob?jk=e959c5c2ece017ba</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>North Little Rock, AR, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e959c5c2ece017ba</t>
+          <t>https://www.indeed.com/viewjob?jk=df9a48331ce93c56</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Django/Python</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>ATG</t>
+          <t>Total Quality Logistics (TQL)</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
+          <t>RDS, Azure, Scala, Data Modeling, ELT, MLOps, MLflow, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df9a48331ce93c56</t>
+          <t>https://www.indeed.com/viewjob?jk=16ea6e485299a08c</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Mid Level Software Engineer</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Harvestaff</t>
+          <t>Total Quality Logistics (TQL)</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Chesterfield, MO, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>RDS, Azure, Oracle, SQL Server, PostgreSQL, MongoDB, Cassandra, NoSQL, Jenkins, Azure DevOps</t>
+          <t>RDS, Azure, Scala, Data Modeling, ELT, MLOps, MLflow, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee62f5b48244cf04</t>
+          <t>https://www.indeed.com/viewjob?jk=7b999917838878a9</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Total Quality Logistics (TQL)</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Terraform, Kubernetes, SonarQube</t>
+          <t>RDS, Azure, Scala, Data Modeling, ELT, MLOps, MLflow, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8aca26123e673da7</t>
+          <t>https://www.indeed.com/viewjob?jk=d71435c6a86e8b64</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>OpenAM</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>S.S. White Technologies</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,34 +4931,34 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Azure, Scala, Kafka, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, ECS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdf8975ebf0eb43f</t>
+          <t>https://www.indeed.com/viewjob?jk=dc670920196ab795</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Mid Level Software Engineer</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>L&amp;T Technology Services Ltd.</t>
+          <t>Harvestaff</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Novi, MI, US USA</t>
+          <t>Chesterfield, MO, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,34 +4966,34 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Hadoop, Spark, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
+          <t>RDS, Azure, Oracle, SQL Server, PostgreSQL, MongoDB, Cassandra, NoSQL, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8bace0705a89432</t>
+          <t>https://www.indeed.com/viewjob?jk=ee62f5b48244cf04</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist, Programmatic Algorithms</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Impact.Com</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>RDS, Databricks, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Kafka, MLOps</t>
+          <t>AWS, RDS, Azure, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Terraform, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,24 +5011,24 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e86578384aa4b6f</t>
+          <t>https://www.indeed.com/viewjob?jk=8aca26123e673da7</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist, Programmatic Algorithms</t>
+          <t>OpenAM</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Impact.Com</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>RDS, Databricks, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Kafka, MLOps</t>
+          <t>Azure, Scala, Kafka, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,24 +5046,24 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0db61ba5b16e71bf</t>
+          <t>https://www.indeed.com/viewjob?jk=fdf8975ebf0eb43f</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Software Engineer - Core Platform</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Unacast</t>
+          <t>L&amp;T Technology Services Ltd.</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Novi, MI, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,34 +5071,34 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Snowflake, MySQL, DynamoDB, NoSQL, GitHub Actions, Git</t>
+          <t>Azure, Databricks, Hadoop, Spark, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=868f8c4ef1ebde56</t>
+          <t>https://www.indeed.com/viewjob?jk=b8bace0705a89432</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>IT Business Analyst II</t>
+          <t>Sr. Data Scientist, Programmatic Algorithms</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>NFI Industries</t>
+          <t>Impact.Com</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,34 +5106,34 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Spark, PySpark, Snowflake, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>RDS, Databricks, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Kafka, MLOps</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b12be44615688132</t>
+          <t>https://www.indeed.com/viewjob?jk=4e86578384aa4b6f</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Solutions Engineer</t>
+          <t>Sr. Data Scientist, Programmatic Algorithms</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Cellular Sales, Verizon Authorized Retailer</t>
+          <t>Impact.Com</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,17 +5141,122 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
+          <t>RDS, Databricks, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Kafka, MLOps</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0db61ba5b16e71bf</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Solutions Engineer</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Cellular Sales, Verizon Authorized Retailer</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Knoxville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
           <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, ETL, CI/CD, Docker</t>
         </is>
       </c>
-      <c r="F135" t="inlineStr">
+      <c r="F136" t="inlineStr">
         <is>
           <t>2026-04-23</t>
         </is>
       </c>
-      <c r="G135" t="inlineStr">
+      <c r="G136" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=f9313901bc5ac9da</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Software Engineer - Core Platform</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Unacast</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Ashburn, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Spark, Scala, Snowflake, MySQL, DynamoDB, NoSQL, GitHub Actions, Git</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=868f8c4ef1ebde56</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>IT Business Analyst II</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>NFI Industries</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Camden, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>AWS, ECS, RDS, Azure, Spark, PySpark, Snowflake, Data Modeling, Dimensional Modeling, Star Schema</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b12be44615688132</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-28.xlsx
+++ b/results/job_matches_2026-04-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G138"/>
+  <dimension ref="A1:G102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -513,7 +513,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -853,17 +853,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AWS API Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Old National Bank</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Lake Elmo, MN, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcce665f3a3b0fee</t>
+          <t>https://www.indeed.com/viewjob?jk=58d405ceae103971</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior PS Sales Solutions Architect</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Old National Bank</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Lake Elmo, MN, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,69 +906,69 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58d405ceae103971</t>
+          <t>https://www.indeed.com/viewjob?jk=9ed1a2a8d040517b</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior PS Sales Solutions Architect</t>
+          <t>Senior Software Engineer - Java</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>MAERSK</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ed1a2a8d040517b</t>
+          <t>https://www.indeed.com/viewjob?jk=2a42ffff2f95ecf4</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Site Reliability Engineering (SRE) Intern</t>
+          <t>Senior Software Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Calix</t>
+          <t>MAERSK</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,42 +976,42 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b66b9b991f001a00</t>
+          <t>https://www.indeed.com/viewjob?jk=83247939112593c0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Python APIs</t>
+          <t>Senior Business Intelligence Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Enova International</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, Azure, GCP, Scala, CI/CD</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,137 +1021,137 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f063f9c882ccc12</t>
+          <t>https://www.indeed.com/viewjob?jk=9f180f27ff7393ac</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Python APIs</t>
+          <t>Data Engineer (remote)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Claritev</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, Azure, GCP, Scala, CI/CD</t>
+          <t>AWS, EMR, RDS, Azure, GCP, Hadoop, Spark, Scala, Oracle, Data Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a00e6d7208f216f0</t>
+          <t>https://www.indeed.com/viewjob?jk=de8ee6455a8ca514</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Java</t>
+          <t>AWS Database Engineer / Cloud DBA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MAERSK</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, Glue, Lambda, Athena, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a42ffff2f95ecf4</t>
+          <t>https://www.indeed.com/viewjob?jk=dc7b3e2ef98acf25</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Hybrid)</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MAERSK</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83247939112593c0</t>
+          <t>https://www.indeed.com/viewjob?jk=292c1ae20b051cf4</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Engineer (Hybrid)</t>
+          <t>Software Engineer - Specialist</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Enova International</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,49 +1161,49 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f180f27ff7393ac</t>
+          <t>https://www.indeed.com/viewjob?jk=936f1055bc6513a5</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer (remote)</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Claritev</t>
+          <t>Versant</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, GCP, Hadoop, Spark, Scala, Oracle, Data Modeling</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, GCP, Spark, Scala, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de8ee6455a8ca514</t>
+          <t>https://www.indeed.com/viewjob?jk=f536b07e93637686</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AWS Database Engineer / Cloud DBA</t>
+          <t>Senior Cloud Governance Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1213,15 +1213,15 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, ELT, DataOps</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc7b3e2ef98acf25</t>
+          <t>https://www.indeed.com/viewjob?jk=4d20905b5e2faaa0</t>
         </is>
       </c>
     </row>
@@ -1252,11 +1252,11 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Scala, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=292c1ae20b051cf4</t>
+          <t>https://www.indeed.com/viewjob?jk=a00dd6bd18f4d068</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SF Technology - Software Engineering - Senior Associate</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Fannie Mae</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, ECS, IAM, RDS, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, NoSQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ba575b133b119eb</t>
+          <t>https://www.indeed.com/viewjob?jk=d07a1b512d8f6b8e</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Engineer - Specialist</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Kharon</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=936f1055bc6513a5</t>
+          <t>https://www.indeed.com/viewjob?jk=429c2128943540c2</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Backend Engineer - Integrations</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,77 +1361,77 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, SQL Server, MLOps, CI/CD</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba4f4cd3ad0ce6f5</t>
+          <t>https://www.indeed.com/viewjob?jk=22b8eb7f870c0ec5</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Science Engineer, GenAI Platforms &amp; Data Infrastructure</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, SQL Server, MLOps, CI/CD</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f06821a24e8c6950</t>
+          <t>https://www.indeed.com/viewjob?jk=21b925b3e52300cd</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Versant</t>
+          <t>Easterseals Southern California</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, GCP, Spark, Scala, PostgreSQL, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,14 +1441,14 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f536b07e93637686</t>
+          <t>https://www.indeed.com/viewjob?jk=2241b1872054f42d</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Cloud Governance Engineer</t>
+          <t>AWS API Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1458,15 +1458,15 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, ELT, DataOps</t>
+          <t>AWS, Hadoop, Hive, MapReduce, Impala, Spark, PySpark, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d20905b5e2faaa0</t>
+          <t>https://www.indeed.com/viewjob?jk=be902deb0c0cff60</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Sr. Backend Engineer - Integrations</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>E Source</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, PostgreSQL, ETL, Jenkins, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22b8eb7f870c0ec5</t>
+          <t>https://www.indeed.com/viewjob?jk=cc74bb7856780dfe</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Senior Consultant, AI &amp; Data Engineering</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Aroha Technologies</t>
+          <t>Castleton Tower</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, Azure, Databricks, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,67 +1546,67 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f7113fe3fafcf1f</t>
+          <t>https://www.indeed.com/viewjob?jk=106bb3c12b0ce283</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior Specialty Software Engineer - Capital Markets Reference Data</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Scala, ETL, ELT, CI/CD, Jenkins</t>
+          <t>API Gateway, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a00dd6bd18f4d068</t>
+          <t>https://www.indeed.com/viewjob?jk=f0e85b21f1fb3187</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Implementation Consultant</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, NoSQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, Glue, ECS, RDS, Azure, Oracle, SQL Server, Data Modeling, ETL, Talend</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,59 +1616,59 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d07a1b512d8f6b8e</t>
+          <t>https://www.indeed.com/viewjob?jk=443bc56bd18ac3c1</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Kharon</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, dbt</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=429c2128943540c2</t>
+          <t>https://www.indeed.com/viewjob?jk=2e59f80446549413</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Science Engineer, GenAI Platforms &amp; Data Infrastructure</t>
+          <t>Technical Architect - Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>WinWire</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Newport Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, S3, RDS, Azure, Medallion Architecture, Snowflake, Oracle, SQL Server, ETL, dbt</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21b925b3e52300cd</t>
+          <t>https://www.indeed.com/viewjob?jk=668b3d9240bad8b3</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Integration Developer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Easterseals Southern California</t>
+          <t>AlayaCare</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Oracle, PostgreSQL</t>
+          <t>AWS, Lambda, API Gateway, RDS, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2241b1872054f42d</t>
+          <t>https://www.indeed.com/viewjob?jk=e35070e714f42f3c</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AWS API Engineer</t>
+          <t>Senior Integration Developer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>AlayaCare</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Hive, MapReduce, Impala, Spark, PySpark, Oracle, SQL Server, MySQL</t>
+          <t>AWS, Lambda, API Gateway, RDS, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be902deb0c0cff60</t>
+          <t>https://www.indeed.com/viewjob?jk=47a751a18a865523</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Senior Integration Developer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>E Source</t>
+          <t>AlayaCare</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, PostgreSQL, ETL, Jenkins, Docker, Jenkins</t>
+          <t>AWS, Lambda, API Gateway, RDS, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc74bb7856780dfe</t>
+          <t>https://www.indeed.com/viewjob?jk=a5b72f3e295f2b38</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Consultant, AI &amp; Data Engineering</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Castleton Tower</t>
+          <t>HARVEST GROUP</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, dbt</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Scala, Snowflake, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=106bb3c12b0ce283</t>
+          <t>https://www.indeed.com/viewjob?jk=d391d4aaecc47ecd</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Java SDK / Library Developer</t>
+          <t>Founding Engineers</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Career Mentors</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Databricks, GCP, Spark, Kafka, Snowflake, PostgreSQL, dbt, Tableau, MLflow</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87bcb224d87d1611</t>
+          <t>https://www.indeed.com/viewjob?jk=004a99e42e1b83ba</t>
         </is>
       </c>
     </row>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=004a99e42e1b83ba</t>
+          <t>https://www.indeed.com/viewjob?jk=9cbf54fc5208e3a3</t>
         </is>
       </c>
     </row>
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cbf54fc5208e3a3</t>
+          <t>https://www.indeed.com/viewjob?jk=3753908732fe77ab</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3753908732fe77ab</t>
+          <t>https://www.indeed.com/viewjob?jk=e30f253b6a8acf18</t>
         </is>
       </c>
     </row>
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e30f253b6a8acf18</t>
+          <t>https://www.indeed.com/viewjob?jk=20194c0f45aa2c81</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Founding Engineers</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Career Mentors</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Databricks, GCP, Spark, Kafka, Snowflake, PostgreSQL, dbt, Tableau, MLflow</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20194c0f45aa2c81</t>
+          <t>https://www.indeed.com/viewjob?jk=ccbafc8be264e941</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Software Engineer - Intermediate</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Jenkins, Maven, Docker</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e59f80446549413</t>
+          <t>https://www.indeed.com/viewjob?jk=00328cd20addd95f</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Technical Architect - Data &amp; Analytics</t>
+          <t>Software Engineer - Intermediate</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>WinWire</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Newport Beach, CA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Medallion Architecture, Snowflake, Oracle, SQL Server, ETL, dbt</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=668b3d9240bad8b3</t>
+          <t>https://www.indeed.com/viewjob?jk=f1563bdd8162e56a</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Specialty Software Engineer - Capital Markets Reference Data</t>
+          <t>Data Solutions Architect | AI</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Trace3</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37db4c0b07afe64d</t>
+          <t>https://www.indeed.com/viewjob?jk=fba922bb2fd28863</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Integration Developer</t>
+          <t>Data Solutions Architect | AI</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>AlayaCare</t>
+          <t>Trace3</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e35070e714f42f3c</t>
+          <t>https://www.indeed.com/viewjob?jk=3dae082eb8598575</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Integration Developer</t>
+          <t>Data Solutions Architect | AI</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>AlayaCare</t>
+          <t>Trace3</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47a751a18a865523</t>
+          <t>https://www.indeed.com/viewjob?jk=63486d61003e0a4f</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Integration Developer</t>
+          <t>Data Solutions Architect | AI</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>AlayaCare</t>
+          <t>Trace3</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,94 +2246,94 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5b72f3e295f2b38</t>
+          <t>https://www.indeed.com/viewjob?jk=7d4d0f879560eea6</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Data Engineer (remote)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>HARVEST GROUP</t>
+          <t>Claritev</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Scala, Snowflake, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hive, Impala, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d391d4aaecc47ecd</t>
+          <t>https://www.indeed.com/viewjob?jk=60d533f19b4463da</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software Escalation Engineer (Python)</t>
+          <t>Data Engineer (remote)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Varonis Systems</t>
+          <t>Claritev</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hive, Impala, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b19ab87ba97422d</t>
+          <t>https://www.indeed.com/viewjob?jk=aa65c57599624378</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer (remote)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Claritev</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hive, Impala, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccbafc8be264e941</t>
+          <t>https://www.indeed.com/viewjob?jk=9230bee4c19c2afb</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Engineer - Intermediate</t>
+          <t>Senior Reliability Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Fitch Group</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Maven</t>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00328cd20addd95f</t>
+          <t>https://www.indeed.com/viewjob?jk=bb104709126cf2da</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Engineer - Intermediate</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>NRG Energy</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Maven</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Cloud Storage, Spark, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1563bdd8162e56a</t>
+          <t>https://www.indeed.com/viewjob?jk=daf356dec855c3b1</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Solutions Architect | AI</t>
+          <t>Senior Software Engineer - Platform &amp; Integrations</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Trace3</t>
+          <t>Seismic</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fba922bb2fd28863</t>
+          <t>https://www.indeed.com/viewjob?jk=cca2fb47a24092c1</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Solutions Architect | AI</t>
+          <t>AI Commercial &amp; ML Ops Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Trace3</t>
+          <t>MGM Resorts International</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dae082eb8598575</t>
+          <t>https://www.indeed.com/viewjob?jk=9e59ac0d5620a4ae</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Solutions Architect | AI</t>
+          <t>Service Cloud Developer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Trace3</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63486d61003e0a4f</t>
+          <t>https://www.indeed.com/viewjob?jk=e2004304d091ff39</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Solutions Architect | AI</t>
+          <t>Cloud Network Architect</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Trace3</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d4d0f879560eea6</t>
+          <t>https://www.indeed.com/viewjob?jk=0a7d02622748f5d3</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer (remote)</t>
+          <t>Sr Software Engineer, Fullstack</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Claritev</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hive, Impala, Spark, PySpark, Scala</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, SQL Server, Data Modeling, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60d533f19b4463da</t>
+          <t>https://www.indeed.com/viewjob?jk=4fb90dbd5192ef62</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Engineer (remote)</t>
+          <t>Multi-Cloud Networking Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Claritev</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hive, Impala, Spark, PySpark, Scala</t>
+          <t>AWS, Redshift, API Gateway, ECS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa65c57599624378</t>
+          <t>https://www.indeed.com/viewjob?jk=2e048a1fa8803abd</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer (remote)</t>
+          <t>SENIOR POWER BI DEVELOPER (HYBRID - REDMOND, WA)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Claritev</t>
+          <t>Eurest</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Redmond, WA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hive, Impala, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9230bee4c19c2afb</t>
+          <t>https://www.indeed.com/viewjob?jk=89664cddc02e354c</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Reliability Engineer</t>
+          <t>Senior Cloud Migration Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Fitch Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Docker, Kubernetes, Git</t>
+          <t>Redshift, RDS, Azure, BigQuery, Snowflake, Data Modeling, Star Schema, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,67 +2701,67 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb104709126cf2da</t>
+          <t>https://www.indeed.com/viewjob?jk=1d795a30569c6d07</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Consultant - Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>NRG Energy</t>
+          <t>Insygnum</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Cloud Storage, Spark, Data Modeling, ETL, ELT</t>
+          <t>Glue, RDS, Hadoop, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=daf356dec855c3b1</t>
+          <t>https://www.indeed.com/viewjob?jk=add721e79e9d7463</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Identity AI / ML Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Rosen's Diversified, Inc.</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Green Bay, WI, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, Google Cloud Platform, Spark, PySpark, Scala, Kafka, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4d3c4afd567d4dc</t>
+          <t>https://www.indeed.com/viewjob?jk=43e06e046a3009ec</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>AI Commercial &amp; ML Ops Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>MGM Resorts International</t>
+          <t>Rosen's Diversified, Inc.</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Eagan, MN, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLflow, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,67 +2806,67 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e59ac0d5620a4ae</t>
+          <t>https://www.indeed.com/viewjob?jk=0d5ed846b77ab548</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Backend Developer- Dallas, TX</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>WEX Inc.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Scala, Kafka, PostgreSQL, MongoDB, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, Azure, GCP, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6cf88579d0b139b</t>
+          <t>https://www.indeed.com/viewjob?jk=51f550253b36df98</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Backend Developer- Dallas, TX</t>
+          <t>Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Scala, Kafka, PostgreSQL, MongoDB, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Docker, Kubernetes, pytest</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,67 +2876,67 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d29f0c0f97c6ad9</t>
+          <t>https://www.indeed.com/viewjob?jk=71acb476a93daa68</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Implementation Consultant - Solutions Architect</t>
+          <t>Senior Software Engineer - Platform</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>New Relic</t>
+          <t>Redfin</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73dc903c92ca8eb2</t>
+          <t>https://www.indeed.com/viewjob?jk=d62543661efd20a8</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Multi-Cloud Networking Engineer</t>
+          <t>Senior Data Scientist - AI/ML Engineering Focus - Remote</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>UnitedHealthcare</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Redshift, API Gateway, ECS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Kafka, Databricks Lakehouse, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,84 +2946,84 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e048a1fa8803abd</t>
+          <t>https://www.indeed.com/viewjob?jk=0b996573f5f8fa39</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>BackEnd Developer- Dallas, TX</t>
+          <t>AI/ML Software Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Numa Management Associates</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Scala, PostgreSQL, DynamoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, MLOps, Docker</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaf41f1dcd53eba3</t>
+          <t>https://www.indeed.com/viewjob?jk=3b8199552143ed2c</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>BackEnd Developer- Dallas, TX</t>
+          <t>AWS API Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Scala, PostgreSQL, DynamoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Databricks, Hadoop, Spark, Scala, Kafka, MongoDB, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4936cea15fb6fab</t>
+          <t>https://www.indeed.com/viewjob?jk=bd06c562a0dd4e4d</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Service Cloud Developer</t>
+          <t>AWS API Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3037,11 +3037,11 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, Databricks, Hadoop, Spark, Scala, Kafka, MongoDB, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,67 +3051,67 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2004304d091ff39</t>
+          <t>https://www.indeed.com/viewjob?jk=7837b5aefbcb5351</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Cloud Network Architect</t>
+          <t>Data Engineer (remote)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Claritev</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, BigQuery, Spark, PySpark, Scala, ETL, ELT, DataOps</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a7d02622748f5d3</t>
+          <t>https://www.indeed.com/viewjob?jk=c836f48c3d814cb7</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Sr Software Engineer, Fullstack</t>
+          <t>Product Developer Advanced</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>Tech Army</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, SQL Server, Data Modeling, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, ETL, Power BI, Python</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fb90dbd5192ef62</t>
+          <t>https://www.indeed.com/viewjob?jk=8d958ebf75215c9a</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>SENIOR POWER BI DEVELOPER (HYBRID - REDMOND, WA)</t>
+          <t>Production Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Eurest</t>
+          <t>Placer.ai</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Redmond, WA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>RDS, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89664cddc02e354c</t>
+          <t>https://www.indeed.com/viewjob?jk=ad1335920bcdcf1c</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Cloud Migration Engineer</t>
+          <t>Senior Digital Analytics Engineer - Customer Experience</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Sherwin-Williams</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, BigQuery, Snowflake, Data Modeling, Star Schema, dbt, Power BI, Tableau</t>
+          <t>AWS, IAM, RDS, Databricks, Scala, Snowflake, Power BI, Tableau, Git, SQL</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d795a30569c6d07</t>
+          <t>https://www.indeed.com/viewjob?jk=724311be6474c008</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>MLOps Engineer - Machine Learning Platform</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Rosen's Diversified, Inc.</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Green Bay, WI, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>AWS, IAM, GCP, Scala, NoSQL, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,32 +3226,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43e06e046a3009ec</t>
+          <t>https://www.indeed.com/viewjob?jk=29ff9b97d0d69a97</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Rosen's Diversified, Inc.</t>
+          <t>Innovien Solutions</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Eagan, MN, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, Redshift, Databricks, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,32 +3261,32 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d5ed846b77ab548</t>
+          <t>https://www.indeed.com/viewjob?jk=19b0604cffe8cf9d</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Service Cloud Developer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>WEX Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,14 +3296,14 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51f550253b36df98</t>
+          <t>https://www.indeed.com/viewjob?jk=14f7aec210bdd6b1</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3313,72 +3313,72 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Docker, Kubernetes, pytest</t>
+          <t>AWS, ECS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71acb476a93daa68</t>
+          <t>https://www.indeed.com/viewjob?jk=377a8106189cff56</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Data Analytics and AI Senior Consultant</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Citrin Cooperman</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Florham Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Athena, S3, SQS, ECS, IAM, RDS, PostgreSQL</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5c87f4d580328bb</t>
+          <t>https://www.indeed.com/viewjob?jk=ab24ee357dc36621</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Data Analytics and AI Senior Consultant</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Citrin Cooperman</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3387,256 +3387,256 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Athena, S3, SQS, ECS, IAM, RDS, PostgreSQL</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f081e02510ebdea</t>
+          <t>https://www.indeed.com/viewjob?jk=ebeab9493cf52705</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Data Analytics and AI Senior Consultant</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Citrin Cooperman</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Braintree, MA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Athena, S3, SQS, ECS, IAM, RDS, PostgreSQL</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a5e445cdfb1f584</t>
+          <t>https://www.indeed.com/viewjob?jk=bd5fb31b5a0e0aed</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Data Analytics and AI Senior Consultant</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Citrin Cooperman</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Athena, S3, SQS, ECS, IAM, RDS, PostgreSQL</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc6e81812acaa849</t>
+          <t>https://www.indeed.com/viewjob?jk=35945946ef347401</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Data Analytics and AI Senior Consultant</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Citrin Cooperman</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Athena, S3, SQS, ECS, IAM, RDS, PostgreSQL</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9b53627c8bb8781</t>
+          <t>https://www.indeed.com/viewjob?jk=98baf5e0e0e210ab</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Data Analytics and AI Senior Consultant</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Citrin Cooperman</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Athena, S3, SQS, ECS, IAM, RDS, PostgreSQL</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cb9f61bc8ba5e0c</t>
+          <t>https://www.indeed.com/viewjob?jk=619ef2ef0698f1fd</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Development Engineer - AI</t>
+          <t>Data Analytics and AI Senior Consultant</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Experian</t>
+          <t>Citrin Cooperman</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, SQS, Scala, Kafka, PostgreSQL, Splunk, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=932a6480f7acd72e</t>
+          <t>https://www.indeed.com/viewjob?jk=16af3b0c4f8842cc</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Platform</t>
+          <t>Senior Software Engineer - Django/Python</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Redfin</t>
+          <t>ATG</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>North Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, S3, Azure, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d62543661efd20a8</t>
+          <t>https://www.indeed.com/viewjob?jk=e959c5c2ece017ba</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - AI/ML Engineering Focus - Remote</t>
+          <t>Senior Software Engineer - Django/Python</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>UnitedHealthcare</t>
+          <t>ATG</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Kafka, Databricks Lakehouse, ELT, MLOps, MLflow</t>
+          <t>AWS, S3, Azure, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,32 +3646,32 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b996573f5f8fa39</t>
+          <t>https://www.indeed.com/viewjob?jk=df9a48331ce93c56</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Cloud Database Engineer</t>
+          <t>Mid Level Software Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Harvestaff</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Smithfield, RI, US USA</t>
+          <t>Chesterfield, MO, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
+          <t>RDS, Azure, Oracle, SQL Server, PostgreSQL, MongoDB, Cassandra, NoSQL, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,32 +3681,32 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dff9fd964893cca2</t>
+          <t>https://www.indeed.com/viewjob?jk=ee62f5b48244cf04</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Cloud Database Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Terraform, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,32 +3716,32 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd0834fa2eafaef3</t>
+          <t>https://www.indeed.com/viewjob?jk=8aca26123e673da7</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Cloud Database Engineer</t>
+          <t>OpenAM</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
+          <t>Azure, Scala, Kafka, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,102 +3751,102 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46aa6a7b0ccb9c57</t>
+          <t>https://www.indeed.com/viewjob?jk=fdf8975ebf0eb43f</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>MIS - Analytics Engineer</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Phillips &amp; Cohen Associates</t>
+          <t>L&amp;T Technology Services Ltd.</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Novi, MI, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RDS, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau, Git, Python</t>
+          <t>Azure, Databricks, Hadoop, Spark, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb902b8c2dc0b4e3</t>
+          <t>https://www.indeed.com/viewjob?jk=b8bace0705a89432</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>MIS - Analytics Engineer</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Phillips &amp; Cohen Associates</t>
+          <t>S.S. White Technologies</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>RDS, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau, Git, Python</t>
+          <t>AWS, ECS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=026772bfd10c6d83</t>
+          <t>https://www.indeed.com/viewjob?jk=dc670920196ab795</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Customer Engineer</t>
+          <t>Sr. Data Scientist, Programmatic Algorithms</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Reltio</t>
+          <t>Impact.Com</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Scala, DynamoDB, Cassandra, NoSQL, ELT</t>
+          <t>RDS, Databricks, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Kafka, MLOps</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,32 +3856,32 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ceebc871c7b716e1</t>
+          <t>https://www.indeed.com/viewjob?jk=4e86578384aa4b6f</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Customer Engineer</t>
+          <t>Sr. Data Scientist, Programmatic Algorithms</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Reltio</t>
+          <t>Impact.Com</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Scala, DynamoDB, Cassandra, NoSQL, ELT</t>
+          <t>RDS, Databricks, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Kafka, MLOps</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b48f55b509420cd6</t>
+          <t>https://www.indeed.com/viewjob?jk=0db61ba5b16e71bf</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>AI/ML Software Engineer</t>
+          <t>Solutions Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Numa Management Associates</t>
+          <t>Cellular Sales, Verizon Authorized Retailer</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, MLOps, Docker</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b8199552143ed2c</t>
+          <t>https://www.indeed.com/viewjob?jk=f9313901bc5ac9da</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>AWS API Engineer</t>
+          <t>Software Engineer - Core Platform</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Unacast</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Hadoop, Spark, Scala, Kafka, MongoDB, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, RDS, Spark, Scala, Snowflake, MySQL, DynamoDB, NoSQL, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd06c562a0dd4e4d</t>
+          <t>https://www.indeed.com/viewjob?jk=868f8c4ef1ebde56</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>AWS API Engineer</t>
+          <t>IT Business Analyst II</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NFI Industries</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,1275 +3986,15 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Hadoop, Spark, Scala, Kafka, MongoDB, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, ECS, RDS, Azure, Spark, PySpark, Snowflake, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7837b5aefbcb5351</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>AWS API Engineer</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>AWS, Databricks, Hadoop, Spark, Scala, Kafka, MongoDB, NoSQL, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5edebdec5daaa4e1</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Data Engineer (remote)</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Claritev</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, BigQuery, Spark, PySpark, Scala, ETL, ELT, DataOps</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c836f48c3d814cb7</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Product Developer Advanced</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Tech Army</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Tallahassee, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, ETL, Power BI, Python</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8d958ebf75215c9a</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Production Engineer</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Placer.ai</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>RDS, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ad1335920bcdcf1c</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Senior Digital Analytics Engineer - Customer Experience</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Sherwin-Williams</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Cleveland, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Databricks, Scala, Snowflake, Power BI, Tableau, Git, SQL</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=724311be6474c008</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>MLOps Engineer - Machine Learning Platform</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Goldman Sachs</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>AWS, IAM, GCP, Scala, NoSQL, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=29ff9b97d0d69a97</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>Innovien Solutions</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Cincinnati, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Redshift, Databricks, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=19b0604cffe8cf9d</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Service Cloud Developer</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=14f7aec210bdd6b1</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Senior Cloud Engineer</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>AWS, ECS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=377a8106189cff56</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>Data Analytics and AI Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Citrin Cooperman</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Florham Park, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ab24ee357dc36621</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Data Analytics and AI Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Citrin Cooperman</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Philadelphia, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ebeab9493cf52705</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>Data Analytics and AI Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>Citrin Cooperman</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Braintree, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bd5fb31b5a0e0aed</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Data Analytics and AI Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>Citrin Cooperman</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Worcester, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D115" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=35945946ef347401</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>Data Analytics and AI Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>Citrin Cooperman</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D116" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=98baf5e0e0e210ab</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>Data Analytics and AI Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>Citrin Cooperman</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D117" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=619ef2ef0698f1fd</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>Data Analytics and AI Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>Citrin Cooperman</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D118" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=16af3b0c4f8842cc</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>DevOps Prime</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D119" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f2c9a4c0d1556c3d</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>DevOps Prime</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>Wichita, KS, US USA</t>
-        </is>
-      </c>
-      <c r="D120" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bdda93ad98da9aec</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>DevOps Prime</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Philadelphia, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D121" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e5d0a6d38e25b0a0</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>DevOps Prime</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>Orlando, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D122" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d02c7ff4534ba5bd</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>DevOps Prime</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D123" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fd8abfee5fbd9116</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Django/Python</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>ATG</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>North Little Rock, AR, US USA</t>
-        </is>
-      </c>
-      <c r="D124" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>AWS, S3, Azure, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e959c5c2ece017ba</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Django/Python</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>ATG</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D125" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>AWS, S3, Azure, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=df9a48331ce93c56</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>AI Architect</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>Total Quality Logistics (TQL)</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Tampa, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D126" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Data Modeling, ELT, MLOps, MLflow, CI/CD, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=16ea6e485299a08c</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>AI Architect</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Total Quality Logistics (TQL)</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>Cincinnati, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D127" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Data Modeling, ELT, MLOps, MLflow, CI/CD, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7b999917838878a9</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>AI Architect</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>Total Quality Logistics (TQL)</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D128" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Data Modeling, ELT, MLOps, MLflow, CI/CD, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d71435c6a86e8b64</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>Software Developer</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>S.S. White Technologies</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Saint Petersburg, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D129" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>AWS, ECS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dc670920196ab795</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>Mid Level Software Engineer</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>Harvestaff</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>Chesterfield, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D130" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Oracle, SQL Server, PostgreSQL, MongoDB, Cassandra, NoSQL, Jenkins, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ee62f5b48244cf04</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>American Airlines</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D131" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Terraform, Kubernetes, SonarQube</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8aca26123e673da7</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>OpenAM</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D132" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>Azure, Scala, Kafka, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fdf8975ebf0eb43f</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>Software Developer</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>L&amp;T Technology Services Ltd.</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>Novi, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D133" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>Azure, Databricks, Hadoop, Spark, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b8bace0705a89432</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>Sr. Data Scientist, Programmatic Algorithms</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>Impact.Com</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D134" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Kafka, MLOps</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4e86578384aa4b6f</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>Sr. Data Scientist, Programmatic Algorithms</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>Impact.Com</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D135" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Kafka, MLOps</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0db61ba5b16e71bf</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>Solutions Engineer</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>Cellular Sales, Verizon Authorized Retailer</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>Knoxville, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D136" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, ETL, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f9313901bc5ac9da</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>Software Engineer - Core Platform</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>Unacast</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>Ashburn, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D137" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Spark, Scala, Snowflake, MySQL, DynamoDB, NoSQL, GitHub Actions, Git</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=868f8c4ef1ebde56</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>IT Business Analyst II</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>NFI Industries</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>Camden, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D138" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>AWS, ECS, RDS, Azure, Spark, PySpark, Snowflake, Data Modeling, Dimensional Modeling, Star Schema</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=b12be44615688132</t>
         </is>

--- a/results/job_matches_2026-04-28.xlsx
+++ b/results/job_matches_2026-04-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G102"/>
+  <dimension ref="A1:G101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -818,17 +818,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer - Snowflake</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Corebridge</t>
+          <t>Old National Bank</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Lake Elmo, MN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3afad6ecd5a25a2</t>
+          <t>https://www.indeed.com/viewjob?jk=58d405ceae103971</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior PS Sales Solutions Architect</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Old National Bank</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Lake Elmo, MN, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,59 +871,59 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58d405ceae103971</t>
+          <t>https://www.indeed.com/viewjob?jk=9ed1a2a8d040517b</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior PS Sales Solutions Architect</t>
+          <t>Senior Software Engineer - Java</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>MAERSK</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ed1a2a8d040517b</t>
+          <t>https://www.indeed.com/viewjob?jk=2a42ffff2f95ecf4</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Java</t>
+          <t>Senior Software Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -946,64 +946,64 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a42ffff2f95ecf4</t>
+          <t>https://www.indeed.com/viewjob?jk=83247939112593c0</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Hybrid)</t>
+          <t>Senior Business Intelligence Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MAERSK</t>
+          <t>Enova International</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83247939112593c0</t>
+          <t>https://www.indeed.com/viewjob?jk=9f180f27ff7393ac</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Engineer (Hybrid)</t>
+          <t>Data Engineer (remote)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Enova International</t>
+          <t>Claritev</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, EMR, RDS, Azure, GCP, Hadoop, Spark, Scala, Oracle, Data Modeling</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f180f27ff7393ac</t>
+          <t>https://www.indeed.com/viewjob?jk=de8ee6455a8ca514</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer (remote)</t>
+          <t>AWS Database Engineer / Cloud DBA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Claritev</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,24 +1046,24 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, GCP, Hadoop, Spark, Scala, Oracle, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Athena, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de8ee6455a8ca514</t>
+          <t>https://www.indeed.com/viewjob?jk=dc7b3e2ef98acf25</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AWS Database Engineer / Cloud DBA</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc7b3e2ef98acf25</t>
+          <t>https://www.indeed.com/viewjob?jk=292c1ae20b051cf4</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Software Engineer - Specialist</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=292c1ae20b051cf4</t>
+          <t>https://www.indeed.com/viewjob?jk=936f1055bc6513a5</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer - Specialist</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Versant</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, GCP, Spark, Scala, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=936f1055bc6513a5</t>
+          <t>https://www.indeed.com/viewjob?jk=f536b07e93637686</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Cloud Governance Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Versant</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, GCP, Spark, Scala, PostgreSQL, NoSQL</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, ELT, DataOps</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,14 +1196,14 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f536b07e93637686</t>
+          <t>https://www.indeed.com/viewjob?jk=4d20905b5e2faaa0</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Cloud Governance Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, ELT, DataOps</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Scala, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d20905b5e2faaa0</t>
+          <t>https://www.indeed.com/viewjob?jk=a00dd6bd18f4d068</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Scala, ETL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, NoSQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a00dd6bd18f4d068</t>
+          <t>https://www.indeed.com/viewjob?jk=d07a1b512d8f6b8e</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Kharon</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, NoSQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, Glue, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d07a1b512d8f6b8e</t>
+          <t>https://www.indeed.com/viewjob?jk=429c2128943540c2</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Backend Engineer - Integrations</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Kharon</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,42 +1326,42 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, dbt</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=429c2128943540c2</t>
+          <t>https://www.indeed.com/viewjob?jk=22b8eb7f870c0ec5</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr. Backend Engineer - Integrations</t>
+          <t>Senior Data Science Engineer, GenAI Platforms &amp; Data Infrastructure</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22b8eb7f870c0ec5</t>
+          <t>https://www.indeed.com/viewjob?jk=21b925b3e52300cd</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Science Engineer, GenAI Platforms &amp; Data Infrastructure</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Easterseals Southern California</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21b925b3e52300cd</t>
+          <t>https://www.indeed.com/viewjob?jk=2241b1872054f42d</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AWS API Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Easterseals Southern California</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Oracle, PostgreSQL</t>
+          <t>AWS, Hadoop, Hive, MapReduce, Impala, Spark, PySpark, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2241b1872054f42d</t>
+          <t>https://www.indeed.com/viewjob?jk=be902deb0c0cff60</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AWS API Engineer</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>E Source</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Hive, MapReduce, Impala, Spark, PySpark, Oracle, SQL Server, MySQL</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, PostgreSQL, ETL, Jenkins, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be902deb0c0cff60</t>
+          <t>https://www.indeed.com/viewjob?jk=cc74bb7856780dfe</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Senior Consultant, AI &amp; Data Engineering</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>E Source</t>
+          <t>Castleton Tower</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, PostgreSQL, ETL, Jenkins, Docker, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc74bb7856780dfe</t>
+          <t>https://www.indeed.com/viewjob?jk=106bb3c12b0ce283</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Consultant, AI &amp; Data Engineering</t>
+          <t>Implementation Consultant</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Castleton Tower</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, dbt</t>
+          <t>AWS, Glue, ECS, RDS, Azure, Oracle, SQL Server, Data Modeling, ETL, Talend</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=106bb3c12b0ce283</t>
+          <t>https://www.indeed.com/viewjob?jk=443bc56bd18ac3c1</t>
         </is>
       </c>
     </row>
@@ -1588,17 +1588,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Implementation Consultant</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, ECS, RDS, Azure, Oracle, SQL Server, Data Modeling, ETL, Talend</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=443bc56bd18ac3c1</t>
+          <t>https://www.indeed.com/viewjob?jk=2e59f80446549413</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Technical Architect - Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>WinWire</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Newport Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Jenkins, Maven, Docker</t>
+          <t>AWS, S3, RDS, Azure, Medallion Architecture, Snowflake, Oracle, SQL Server, ETL, dbt</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e59f80446549413</t>
+          <t>https://www.indeed.com/viewjob?jk=668b3d9240bad8b3</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Technical Architect - Data &amp; Analytics</t>
+          <t>Senior Integration Developer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>WinWire</t>
+          <t>AlayaCare</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Newport Beach, CA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Medallion Architecture, Snowflake, Oracle, SQL Server, ETL, dbt</t>
+          <t>AWS, Lambda, API Gateway, RDS, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=668b3d9240bad8b3</t>
+          <t>https://www.indeed.com/viewjob?jk=e35070e714f42f3c</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e35070e714f42f3c</t>
+          <t>https://www.indeed.com/viewjob?jk=47a751a18a865523</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47a751a18a865523</t>
+          <t>https://www.indeed.com/viewjob?jk=a5b72f3e295f2b38</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Integration Developer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>AlayaCare</t>
+          <t>HARVEST GROUP</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Scala, Snowflake, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5b72f3e295f2b38</t>
+          <t>https://www.indeed.com/viewjob?jk=d391d4aaecc47ecd</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Founding Engineers</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>HARVEST GROUP</t>
+          <t>Career Mentors</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Scala, Snowflake, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Databricks, GCP, Spark, Kafka, Snowflake, PostgreSQL, dbt, Tableau, MLflow</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d391d4aaecc47ecd</t>
+          <t>https://www.indeed.com/viewjob?jk=004a99e42e1b83ba</t>
         </is>
       </c>
     </row>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=004a99e42e1b83ba</t>
+          <t>https://www.indeed.com/viewjob?jk=9cbf54fc5208e3a3</t>
         </is>
       </c>
     </row>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cbf54fc5208e3a3</t>
+          <t>https://www.indeed.com/viewjob?jk=3753908732fe77ab</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3753908732fe77ab</t>
+          <t>https://www.indeed.com/viewjob?jk=e30f253b6a8acf18</t>
         </is>
       </c>
     </row>
@@ -1966,59 +1966,59 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e30f253b6a8acf18</t>
+          <t>https://www.indeed.com/viewjob?jk=20194c0f45aa2c81</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Founding Engineers</t>
+          <t>System Architect IV (ATL)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Career Mentors</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Databricks, GCP, Spark, Kafka, Snowflake, PostgreSQL, dbt, Tableau, MLflow</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20194c0f45aa2c81</t>
+          <t>https://www.indeed.com/viewjob?jk=562c3953d5d4cf9e</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer - Intermediate</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccbafc8be264e941</t>
+          <t>https://www.indeed.com/viewjob?jk=00328cd20addd95f</t>
         </is>
       </c>
     </row>
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00328cd20addd95f</t>
+          <t>https://www.indeed.com/viewjob?jk=f1563bdd8162e56a</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Engineer - Intermediate</t>
+          <t>Data Solutions Architect | AI</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Trace3</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Maven</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1563bdd8162e56a</t>
+          <t>https://www.indeed.com/viewjob?jk=fba922bb2fd28863</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fba922bb2fd28863</t>
+          <t>https://www.indeed.com/viewjob?jk=3dae082eb8598575</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dae082eb8598575</t>
+          <t>https://www.indeed.com/viewjob?jk=63486d61003e0a4f</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63486d61003e0a4f</t>
+          <t>https://www.indeed.com/viewjob?jk=7d4d0f879560eea6</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Solutions Architect | AI</t>
+          <t>Data Engineer (remote)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Trace3</t>
+          <t>Claritev</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,17 +2236,17 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hive, Impala, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d4d0f879560eea6</t>
+          <t>https://www.indeed.com/viewjob?jk=60d533f19b4463da</t>
         </is>
       </c>
     </row>
@@ -2276,12 +2276,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60d533f19b4463da</t>
+          <t>https://www.indeed.com/viewjob?jk=aa65c57599624378</t>
         </is>
       </c>
     </row>
@@ -2311,29 +2311,29 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa65c57599624378</t>
+          <t>https://www.indeed.com/viewjob?jk=9230bee4c19c2afb</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer (remote)</t>
+          <t>Senior Reliability Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Claritev</t>
+          <t>Fitch Group</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hive, Impala, Spark, PySpark, Scala</t>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9230bee4c19c2afb</t>
+          <t>https://www.indeed.com/viewjob?jk=bb104709126cf2da</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Reliability Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Fitch Group</t>
+          <t>NRG Energy</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Docker, Kubernetes, Git</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Cloud Storage, Spark, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb104709126cf2da</t>
+          <t>https://www.indeed.com/viewjob?jk=daf356dec855c3b1</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer - Platform &amp; Integrations</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>NRG Energy</t>
+          <t>Seismic</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Cloud Storage, Spark, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=daf356dec855c3b1</t>
+          <t>https://www.indeed.com/viewjob?jk=cca2fb47a24092c1</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Platform &amp; Integrations</t>
+          <t>AI Commercial &amp; ML Ops Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Seismic</t>
+          <t>MGM Resorts International</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cca2fb47a24092c1</t>
+          <t>https://www.indeed.com/viewjob?jk=9e59ac0d5620a4ae</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AI Commercial &amp; ML Ops Engineer</t>
+          <t>Service Cloud Developer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>MGM Resorts International</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLflow, CI/CD</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,14 +2491,14 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e59ac0d5620a4ae</t>
+          <t>https://www.indeed.com/viewjob?jk=e2004304d091ff39</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Service Cloud Developer</t>
+          <t>Cloud Network Architect</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2004304d091ff39</t>
+          <t>https://www.indeed.com/viewjob?jk=0a7d02622748f5d3</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Cloud Network Architect</t>
+          <t>Sr Software Engineer, Fullstack</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, SQL Server, Data Modeling, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a7d02622748f5d3</t>
+          <t>https://www.indeed.com/viewjob?jk=4fb90dbd5192ef62</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Sr Software Engineer, Fullstack</t>
+          <t>Multi-Cloud Networking Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, SQL Server, Data Modeling, CI/CD, GitHub Actions</t>
+          <t>AWS, Redshift, API Gateway, ECS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fb90dbd5192ef62</t>
+          <t>https://www.indeed.com/viewjob?jk=2e048a1fa8803abd</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Multi-Cloud Networking Engineer</t>
+          <t>SENIOR POWER BI DEVELOPER (HYBRID - REDMOND, WA)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Eurest</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Redmond, WA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Redshift, API Gateway, ECS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e048a1fa8803abd</t>
+          <t>https://www.indeed.com/viewjob?jk=89664cddc02e354c</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>SENIOR POWER BI DEVELOPER (HYBRID - REDMOND, WA)</t>
+          <t>Senior Cloud Migration Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Eurest</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Redmond, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>Redshift, RDS, Azure, BigQuery, Snowflake, Data Modeling, Star Schema, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,59 +2666,59 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89664cddc02e354c</t>
+          <t>https://www.indeed.com/viewjob?jk=1d795a30569c6d07</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Cloud Migration Engineer</t>
+          <t>Sr. Consultant - Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Insygnum</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, BigQuery, Snowflake, Data Modeling, Star Schema, dbt, Power BI, Tableau</t>
+          <t>Glue, RDS, Hadoop, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d795a30569c6d07</t>
+          <t>https://www.indeed.com/viewjob?jk=add721e79e9d7463</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sr. Consultant - Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Insygnum</t>
+          <t>Rosen's Diversified, Inc.</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Green Bay, WI, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,17 +2726,17 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Glue, RDS, Hadoop, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=add721e79e9d7463</t>
+          <t>https://www.indeed.com/viewjob?jk=43e06e046a3009ec</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Green Bay, WI, US USA</t>
+          <t>Eagan, MN, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43e06e046a3009ec</t>
+          <t>https://www.indeed.com/viewjob?jk=0d5ed846b77ab548</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Rosen's Diversified, Inc.</t>
+          <t>WEX Inc.</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Eagan, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>AWS, Azure, GCP, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d5ed846b77ab548</t>
+          <t>https://www.indeed.com/viewjob?jk=51f550253b36df98</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>WEX Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Docker, Kubernetes, pytest</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51f550253b36df98</t>
+          <t>https://www.indeed.com/viewjob?jk=71acb476a93daa68</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack</t>
+          <t>Senior Software Engineer - Platform</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Redfin</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Docker, Kubernetes, pytest</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71acb476a93daa68</t>
+          <t>https://www.indeed.com/viewjob?jk=d62543661efd20a8</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Platform</t>
+          <t>Senior Data Scientist - AI/ML Engineering Focus - Remote</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Redfin</t>
+          <t>UnitedHealthcare</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,42 +2901,42 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Kafka, Databricks Lakehouse, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d62543661efd20a8</t>
+          <t>https://www.indeed.com/viewjob?jk=0b996573f5f8fa39</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - AI/ML Engineering Focus - Remote</t>
+          <t>AI/ML Software Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>UnitedHealthcare</t>
+          <t>Numa Management Associates</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Kafka, Databricks Lakehouse, ELT, MLOps, MLflow</t>
+          <t>AWS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, MLOps, Docker</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b996573f5f8fa39</t>
+          <t>https://www.indeed.com/viewjob?jk=3b8199552143ed2c</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>AI/ML Software Engineer</t>
+          <t>AWS API Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Numa Management Associates</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, MLOps, Docker</t>
+          <t>AWS, Databricks, Hadoop, Spark, Scala, Kafka, MongoDB, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b8199552143ed2c</t>
+          <t>https://www.indeed.com/viewjob?jk=bd06c562a0dd4e4d</t>
         </is>
       </c>
     </row>
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd06c562a0dd4e4d</t>
+          <t>https://www.indeed.com/viewjob?jk=7837b5aefbcb5351</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>AWS API Engineer</t>
+          <t>Data Engineer (remote)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Claritev</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Hadoop, Spark, Scala, Kafka, MongoDB, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, BigQuery, Spark, PySpark, Scala, ETL, ELT, DataOps</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7837b5aefbcb5351</t>
+          <t>https://www.indeed.com/viewjob?jk=c836f48c3d814cb7</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Engineer (remote)</t>
+          <t>Product Developer Advanced</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Claritev</t>
+          <t>Tech Army</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, BigQuery, Spark, PySpark, Scala, ETL, ELT, DataOps</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, ETL, Power BI, Python</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c836f48c3d814cb7</t>
+          <t>https://www.indeed.com/viewjob?jk=8d958ebf75215c9a</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Product Developer Advanced</t>
+          <t>Production Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Tech Army</t>
+          <t>Placer.ai</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, ETL, Power BI, Python</t>
+          <t>RDS, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d958ebf75215c9a</t>
+          <t>https://www.indeed.com/viewjob?jk=ad1335920bcdcf1c</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Production Engineer</t>
+          <t>Senior Digital Analytics Engineer - Customer Experience</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Placer.ai</t>
+          <t>Sherwin-Williams</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, IAM, RDS, Databricks, Scala, Snowflake, Power BI, Tableau, Git, SQL</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad1335920bcdcf1c</t>
+          <t>https://www.indeed.com/viewjob?jk=724311be6474c008</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Digital Analytics Engineer - Customer Experience</t>
+          <t>MLOps Engineer - Machine Learning Platform</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Sherwin-Williams</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Scala, Snowflake, Power BI, Tableau, Git, SQL</t>
+          <t>AWS, IAM, GCP, Scala, NoSQL, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=724311be6474c008</t>
+          <t>https://www.indeed.com/viewjob?jk=29ff9b97d0d69a97</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>MLOps Engineer - Machine Learning Platform</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Innovien Solutions</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, IAM, GCP, Scala, NoSQL, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Redshift, Databricks, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29ff9b97d0d69a97</t>
+          <t>https://www.indeed.com/viewjob?jk=19b0604cffe8cf9d</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Service Cloud Developer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Innovien Solutions</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Databricks, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19b0604cffe8cf9d</t>
+          <t>https://www.indeed.com/viewjob?jk=14f7aec210bdd6b1</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Service Cloud Developer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
+          <t>AWS, ECS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14f7aec210bdd6b1</t>
+          <t>https://www.indeed.com/viewjob?jk=377a8106189cff56</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Data Analytics and AI Senior Consultant</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Citrin Cooperman</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Florham Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,17 +3321,17 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=377a8106189cff56</t>
+          <t>https://www.indeed.com/viewjob?jk=ab24ee357dc36621</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Florham Park, NJ, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab24ee357dc36621</t>
+          <t>https://www.indeed.com/viewjob?jk=ebeab9493cf52705</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Braintree, MA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebeab9493cf52705</t>
+          <t>https://www.indeed.com/viewjob?jk=bd5fb31b5a0e0aed</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Braintree, MA, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd5fb31b5a0e0aed</t>
+          <t>https://www.indeed.com/viewjob?jk=35945946ef347401</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35945946ef347401</t>
+          <t>https://www.indeed.com/viewjob?jk=98baf5e0e0e210ab</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98baf5e0e0e210ab</t>
+          <t>https://www.indeed.com/viewjob?jk=619ef2ef0698f1fd</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=619ef2ef0698f1fd</t>
+          <t>https://www.indeed.com/viewjob?jk=16af3b0c4f8842cc</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Data Analytics and AI Senior Consultant</t>
+          <t>Senior Software Engineer - Django/Python</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Citrin Cooperman</t>
+          <t>ATG</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>North Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,17 +3566,17 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
+          <t>AWS, S3, Azure, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16af3b0c4f8842cc</t>
+          <t>https://www.indeed.com/viewjob?jk=e959c5c2ece017ba</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>North Little Rock, AR, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e959c5c2ece017ba</t>
+          <t>https://www.indeed.com/viewjob?jk=df9a48331ce93c56</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Django/Python</t>
+          <t>Mid Level Software Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>ATG</t>
+          <t>Harvestaff</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Chesterfield, MO, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
+          <t>RDS, Azure, Oracle, SQL Server, PostgreSQL, MongoDB, Cassandra, NoSQL, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df9a48331ce93c56</t>
+          <t>https://www.indeed.com/viewjob?jk=ee62f5b48244cf04</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Mid Level Software Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Harvestaff</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Chesterfield, MO, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Azure, Oracle, SQL Server, PostgreSQL, MongoDB, Cassandra, NoSQL, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Terraform, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee62f5b48244cf04</t>
+          <t>https://www.indeed.com/viewjob?jk=8aca26123e673da7</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>OpenAM</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Terraform, Kubernetes, SonarQube</t>
+          <t>Azure, Scala, Kafka, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8aca26123e673da7</t>
+          <t>https://www.indeed.com/viewjob?jk=fdf8975ebf0eb43f</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>OpenAM</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>L&amp;T Technology Services Ltd.</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Novi, MI, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,17 +3741,17 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Azure, Scala, Kafka, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>Azure, Databricks, Hadoop, Spark, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdf8975ebf0eb43f</t>
+          <t>https://www.indeed.com/viewjob?jk=b8bace0705a89432</t>
         </is>
       </c>
     </row>
@@ -3763,12 +3763,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>L&amp;T Technology Services Ltd.</t>
+          <t>S.S. White Technologies</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Novi, MI, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Hadoop, Spark, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
+          <t>AWS, ECS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8bace0705a89432</t>
+          <t>https://www.indeed.com/viewjob?jk=dc670920196ab795</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Sr. Data Scientist, Programmatic Algorithms</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>S.S. White Technologies</t>
+          <t>Impact.Com</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,17 +3811,17 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>RDS, Databricks, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Kafka, MLOps</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc670920196ab795</t>
+          <t>https://www.indeed.com/viewjob?jk=4e86578384aa4b6f</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e86578384aa4b6f</t>
+          <t>https://www.indeed.com/viewjob?jk=0db61ba5b16e71bf</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist, Programmatic Algorithms</t>
+          <t>Solutions Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Impact.Com</t>
+          <t>Cellular Sales, Verizon Authorized Retailer</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>RDS, Databricks, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Kafka, MLOps</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0db61ba5b16e71bf</t>
+          <t>https://www.indeed.com/viewjob?jk=f9313901bc5ac9da</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Solutions Engineer</t>
+          <t>Software Engineer - Core Platform</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Cellular Sales, Verizon Authorized Retailer</t>
+          <t>Unacast</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, ETL, CI/CD, Docker</t>
+          <t>AWS, RDS, Spark, Scala, Snowflake, MySQL, DynamoDB, NoSQL, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9313901bc5ac9da</t>
+          <t>https://www.indeed.com/viewjob?jk=868f8c4ef1ebde56</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Software Engineer - Core Platform</t>
+          <t>IT Business Analyst II</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Unacast</t>
+          <t>NFI Industries</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,50 +3951,15 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Snowflake, MySQL, DynamoDB, NoSQL, GitHub Actions, Git</t>
+          <t>AWS, ECS, RDS, Azure, Spark, PySpark, Snowflake, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=868f8c4ef1ebde56</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>IT Business Analyst II</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>NFI Industries</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Camden, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>AWS, ECS, RDS, Azure, Spark, PySpark, Snowflake, Data Modeling, Dimensional Modeling, Star Schema</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=b12be44615688132</t>
         </is>

--- a/results/job_matches_2026-04-28.xlsx
+++ b/results/job_matches_2026-04-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G101"/>
+  <dimension ref="A1:G96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,60 +573,60 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI &amp; Data Solution Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Carrier</t>
+          <t>Quilt</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Provo, UT, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>22.2</v>
+        <v>18.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Medallion Architecture, Google Cloud Platform, GCP</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b75279cc7e23ce8</t>
+          <t>https://www.indeed.com/viewjob?jk=2f1b4cd21f275b79</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Customer Support Developer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Quilt</t>
+          <t>Airbyte</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Provo, UT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f1b4cd21f275b79</t>
+          <t>https://www.indeed.com/viewjob?jk=ab2390ad9f6c9780</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Snowflake Architect - Job ID 831</t>
+          <t>Customer Support Developer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Kapitus</t>
+          <t>Airbyte</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, IAM, RDS, Databricks</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30116c3087096b0c</t>
+          <t>https://www.indeed.com/viewjob?jk=a7fe60e6480b1a64</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Customer Support Developer</t>
+          <t>Snowflake Architect - Job ID 831</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Airbyte</t>
+          <t>Kapitus</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, IAM, RDS, Databricks</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab2390ad9f6c9780</t>
+          <t>https://www.indeed.com/viewjob?jk=30116c3087096b0c</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Customer Support Developer</t>
+          <t>API Security IAM</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Airbyte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,14 +741,14 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7fe60e6480b1a64</t>
+          <t>https://www.indeed.com/viewjob?jk=0585ca531cf89a02</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>API Security IAM</t>
+          <t>AWS API Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, S3, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0585ca531cf89a02</t>
+          <t>https://www.indeed.com/viewjob?jk=8e2967a40f711a6e</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AWS API Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Old National Bank</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Lake Elmo, MN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e2967a40f711a6e</t>
+          <t>https://www.indeed.com/viewjob?jk=58d405ceae103971</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior PS Sales Solutions Architect</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Old National Bank</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Lake Elmo, MN, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,139 +836,139 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58d405ceae103971</t>
+          <t>https://www.indeed.com/viewjob?jk=9ed1a2a8d040517b</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior PS Sales Solutions Architect</t>
+          <t>Senior Business Intelligence Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Enova International</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ed1a2a8d040517b</t>
+          <t>https://www.indeed.com/viewjob?jk=9f180f27ff7393ac</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Java</t>
+          <t>Data Engineer (remote)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MAERSK</t>
+          <t>Claritev</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, EMR, RDS, Azure, GCP, Hadoop, Spark, Scala, Oracle, Data Modeling</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a42ffff2f95ecf4</t>
+          <t>https://www.indeed.com/viewjob?jk=de8ee6455a8ca514</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Hybrid)</t>
+          <t>AWS Database Engineer / Cloud DBA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>MAERSK</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, Glue, Lambda, Athena, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83247939112593c0</t>
+          <t>https://www.indeed.com/viewjob?jk=dc7b3e2ef98acf25</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Engineer (Hybrid)</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Enova International</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,67 +986,67 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f180f27ff7393ac</t>
+          <t>https://www.indeed.com/viewjob?jk=292c1ae20b051cf4</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer (remote)</t>
+          <t>Software Engineer - Specialist</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Claritev</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, GCP, Hadoop, Spark, Scala, Oracle, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de8ee6455a8ca514</t>
+          <t>https://www.indeed.com/viewjob?jk=936f1055bc6513a5</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AWS Database Engineer / Cloud DBA</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Versant</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, GCP, Spark, Scala, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,14 +1056,14 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc7b3e2ef98acf25</t>
+          <t>https://www.indeed.com/viewjob?jk=f536b07e93637686</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior Cloud Governance Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1073,15 +1073,15 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, ELT, CI/CD</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, ELT, DataOps</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=292c1ae20b051cf4</t>
+          <t>https://www.indeed.com/viewjob?jk=4d20905b5e2faaa0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer - Specialist</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Scala, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=936f1055bc6513a5</t>
+          <t>https://www.indeed.com/viewjob?jk=a00dd6bd18f4d068</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Versant</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, GCP, Spark, Scala, PostgreSQL, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, NoSQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f536b07e93637686</t>
+          <t>https://www.indeed.com/viewjob?jk=d07a1b512d8f6b8e</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Cloud Governance Engineer</t>
+          <t>Sr. Backend Engineer - Integrations</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, ELT, DataOps</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d20905b5e2faaa0</t>
+          <t>https://www.indeed.com/viewjob?jk=22b8eb7f870c0ec5</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Kharon</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,42 +1221,42 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Scala, ETL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, Glue, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a00dd6bd18f4d068</t>
+          <t>https://www.indeed.com/viewjob?jk=429c2128943540c2</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior Data Science Engineer, GenAI Platforms &amp; Data Infrastructure</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, NoSQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,67 +1266,67 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d07a1b512d8f6b8e</t>
+          <t>https://www.indeed.com/viewjob?jk=21b925b3e52300cd</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Kharon</t>
+          <t>Easterseals Southern California</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=429c2128943540c2</t>
+          <t>https://www.indeed.com/viewjob?jk=2241b1872054f42d</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sr. Backend Engineer - Integrations</t>
+          <t>AWS API Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, Hadoop, Hive, MapReduce, Impala, Spark, PySpark, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22b8eb7f870c0ec5</t>
+          <t>https://www.indeed.com/viewjob?jk=be902deb0c0cff60</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Science Engineer, GenAI Platforms &amp; Data Infrastructure</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>E Source</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, PostgreSQL, ETL, Jenkins, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21b925b3e52300cd</t>
+          <t>https://www.indeed.com/viewjob?jk=cc74bb7856780dfe</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Consultant, AI &amp; Data Engineering</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Easterseals Southern California</t>
+          <t>Castleton Tower</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2241b1872054f42d</t>
+          <t>https://www.indeed.com/viewjob?jk=106bb3c12b0ce283</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AWS API Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Aureon</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>West Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Hive, MapReduce, Impala, Spark, PySpark, Oracle, SQL Server, MySQL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be902deb0c0cff60</t>
+          <t>https://www.indeed.com/viewjob?jk=2f774c4618ca5806</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Senior Specialty Software Engineer - Capital Markets Reference Data</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>E Source</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, PostgreSQL, ETL, Jenkins, Docker, Jenkins</t>
+          <t>API Gateway, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc74bb7856780dfe</t>
+          <t>https://www.indeed.com/viewjob?jk=f0e85b21f1fb3187</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Consultant, AI &amp; Data Engineering</t>
+          <t>Founding Engineers</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Castleton Tower</t>
+          <t>Career Mentors</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, dbt</t>
+          <t>AWS, Databricks, GCP, Spark, Kafka, Snowflake, PostgreSQL, dbt, Tableau, MLflow</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=106bb3c12b0ce283</t>
+          <t>https://www.indeed.com/viewjob?jk=004a99e42e1b83ba</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Implementation Consultant</t>
+          <t>Founding Engineers</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>Career Mentors</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, ECS, RDS, Azure, Oracle, SQL Server, Data Modeling, ETL, Talend</t>
+          <t>AWS, Databricks, GCP, Spark, Kafka, Snowflake, PostgreSQL, dbt, Tableau, MLflow</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=443bc56bd18ac3c1</t>
+          <t>https://www.indeed.com/viewjob?jk=9cbf54fc5208e3a3</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Specialty Software Engineer - Capital Markets Reference Data</t>
+          <t>Founding Engineers</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Career Mentors</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, CI/CD, GitHub Actions</t>
+          <t>AWS, Databricks, GCP, Spark, Kafka, Snowflake, PostgreSQL, dbt, Tableau, MLflow</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0e85b21f1fb3187</t>
+          <t>https://www.indeed.com/viewjob?jk=3753908732fe77ab</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Founding Engineers</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Career Mentors</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Jenkins, Maven, Docker</t>
+          <t>AWS, Databricks, GCP, Spark, Kafka, Snowflake, PostgreSQL, dbt, Tableau, MLflow</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e59f80446549413</t>
+          <t>https://www.indeed.com/viewjob?jk=e30f253b6a8acf18</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Technical Architect - Data &amp; Analytics</t>
+          <t>Founding Engineers</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>WinWire</t>
+          <t>Career Mentors</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Newport Beach, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Medallion Architecture, Snowflake, Oracle, SQL Server, ETL, dbt</t>
+          <t>AWS, Databricks, GCP, Spark, Kafka, Snowflake, PostgreSQL, dbt, Tableau, MLflow</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=668b3d9240bad8b3</t>
+          <t>https://www.indeed.com/viewjob?jk=20194c0f45aa2c81</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Integration Developer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>AlayaCare</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e35070e714f42f3c</t>
+          <t>https://www.indeed.com/viewjob?jk=2e59f80446549413</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47a751a18a865523</t>
+          <t>https://www.indeed.com/viewjob?jk=e35070e714f42f3c</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5b72f3e295f2b38</t>
+          <t>https://www.indeed.com/viewjob?jk=47a751a18a865523</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior Integration Developer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>HARVEST GROUP</t>
+          <t>AlayaCare</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Scala, Snowflake, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, API Gateway, RDS, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d391d4aaecc47ecd</t>
+          <t>https://www.indeed.com/viewjob?jk=a5b72f3e295f2b38</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Founding Engineers</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Career Mentors</t>
+          <t>HARVEST GROUP</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Databricks, GCP, Spark, Kafka, Snowflake, PostgreSQL, dbt, Tableau, MLflow</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Scala, Snowflake, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,67 +1826,67 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=004a99e42e1b83ba</t>
+          <t>https://www.indeed.com/viewjob?jk=d391d4aaecc47ecd</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Founding Engineers</t>
+          <t>System Architect IV (ATL)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Career Mentors</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Databricks, GCP, Spark, Kafka, Snowflake, PostgreSQL, dbt, Tableau, MLflow</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cbf54fc5208e3a3</t>
+          <t>https://www.indeed.com/viewjob?jk=562c3953d5d4cf9e</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Founding Engineers</t>
+          <t>Software Engineer - Intermediate</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Career Mentors</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Databricks, GCP, Spark, Kafka, Snowflake, PostgreSQL, dbt, Tableau, MLflow</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3753908732fe77ab</t>
+          <t>https://www.indeed.com/viewjob?jk=00328cd20addd95f</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Founding Engineers</t>
+          <t>Software Engineer - Intermediate</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Career Mentors</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Databricks, GCP, Spark, Kafka, Snowflake, PostgreSQL, dbt, Tableau, MLflow</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e30f253b6a8acf18</t>
+          <t>https://www.indeed.com/viewjob?jk=f1563bdd8162e56a</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Founding Engineers</t>
+          <t>Data Solutions Architect | AI</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Career Mentors</t>
+          <t>Trace3</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Databricks, GCP, Spark, Kafka, Snowflake, PostgreSQL, dbt, Tableau, MLflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20194c0f45aa2c81</t>
+          <t>https://www.indeed.com/viewjob?jk=fba922bb2fd28863</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>System Architect IV (ATL)</t>
+          <t>Data Solutions Architect | AI</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Trace3</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=562c3953d5d4cf9e</t>
+          <t>https://www.indeed.com/viewjob?jk=3dae082eb8598575</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Software Engineer - Intermediate</t>
+          <t>Data Solutions Architect | AI</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Trace3</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Maven</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00328cd20addd95f</t>
+          <t>https://www.indeed.com/viewjob?jk=63486d61003e0a4f</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Engineer - Intermediate</t>
+          <t>Data Solutions Architect | AI</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Trace3</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Maven</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1563bdd8162e56a</t>
+          <t>https://www.indeed.com/viewjob?jk=7d4d0f879560eea6</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Solutions Architect | AI</t>
+          <t>Data Engineer (remote)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Trace3</t>
+          <t>Claritev</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hive, Impala, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fba922bb2fd28863</t>
+          <t>https://www.indeed.com/viewjob?jk=60d533f19b4463da</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Solutions Architect | AI</t>
+          <t>Data Engineer (remote)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Trace3</t>
+          <t>Claritev</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hive, Impala, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dae082eb8598575</t>
+          <t>https://www.indeed.com/viewjob?jk=aa65c57599624378</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Solutions Architect | AI</t>
+          <t>Data Engineer (remote)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Trace3</t>
+          <t>Claritev</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hive, Impala, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63486d61003e0a4f</t>
+          <t>https://www.indeed.com/viewjob?jk=9230bee4c19c2afb</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Solutions Architect | AI</t>
+          <t>Senior Reliability Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Trace3</t>
+          <t>Fitch Group</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d4d0f879560eea6</t>
+          <t>https://www.indeed.com/viewjob?jk=bb104709126cf2da</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer (remote)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Claritev</t>
+          <t>NRG Energy</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hive, Impala, Spark, PySpark, Scala</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Cloud Storage, Spark, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60d533f19b4463da</t>
+          <t>https://www.indeed.com/viewjob?jk=daf356dec855c3b1</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer (remote)</t>
+          <t>Senior Software Engineer - Platform &amp; Integrations</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Claritev</t>
+          <t>Seismic</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hive, Impala, Spark, PySpark, Scala</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa65c57599624378</t>
+          <t>https://www.indeed.com/viewjob?jk=cca2fb47a24092c1</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer (remote)</t>
+          <t>Multi-Cloud Networking Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Claritev</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hive, Impala, Spark, PySpark, Scala</t>
+          <t>AWS, Redshift, API Gateway, ECS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9230bee4c19c2afb</t>
+          <t>https://www.indeed.com/viewjob?jk=2e048a1fa8803abd</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Reliability Engineer</t>
+          <t>AI Commercial &amp; ML Ops Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Fitch Group</t>
+          <t>MGM Resorts International</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb104709126cf2da</t>
+          <t>https://www.indeed.com/viewjob?jk=9e59ac0d5620a4ae</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Service Cloud Developer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>NRG Energy</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Cloud Storage, Spark, Data Modeling, ETL, ELT</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=daf356dec855c3b1</t>
+          <t>https://www.indeed.com/viewjob?jk=e2004304d091ff39</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Platform &amp; Integrations</t>
+          <t>Cloud Network Architect</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Seismic</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Terraform</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cca2fb47a24092c1</t>
+          <t>https://www.indeed.com/viewjob?jk=0a7d02622748f5d3</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AI Commercial &amp; ML Ops Engineer</t>
+          <t>Sr Software Engineer, Fullstack</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>MGM Resorts International</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLflow, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, SQL Server, Data Modeling, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,14 +2456,14 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e59ac0d5620a4ae</t>
+          <t>https://www.indeed.com/viewjob?jk=4fb90dbd5192ef62</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Service Cloud Developer</t>
+          <t>Senior Cloud Migration Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>Redshift, RDS, Azure, BigQuery, Snowflake, Data Modeling, Star Schema, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2004304d091ff39</t>
+          <t>https://www.indeed.com/viewjob?jk=1d795a30569c6d07</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Cloud Network Architect</t>
+          <t>Backend Developer- Dallas, TX</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, S3, IAM, Scala, Kafka, PostgreSQL, MongoDB, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a7d02622748f5d3</t>
+          <t>https://www.indeed.com/viewjob?jk=c6cf88579d0b139b</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sr Software Engineer, Fullstack</t>
+          <t>Backend Developer- Dallas, TX</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,77 +2551,77 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, SQL Server, Data Modeling, CI/CD, GitHub Actions</t>
+          <t>AWS, S3, IAM, Scala, Kafka, PostgreSQL, MongoDB, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fb90dbd5192ef62</t>
+          <t>https://www.indeed.com/viewjob?jk=9d29f0c0f97c6ad9</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Multi-Cloud Networking Engineer</t>
+          <t>Sr. Consultant - Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Insygnum</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Redshift, API Gateway, ECS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins</t>
+          <t>Glue, RDS, Hadoop, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e048a1fa8803abd</t>
+          <t>https://www.indeed.com/viewjob?jk=add721e79e9d7463</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>SENIOR POWER BI DEVELOPER (HYBRID - REDMOND, WA)</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Eurest</t>
+          <t>Rosen's Diversified, Inc.</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Redmond, WA, US USA</t>
+          <t>Green Bay, WI, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89664cddc02e354c</t>
+          <t>https://www.indeed.com/viewjob?jk=43e06e046a3009ec</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Cloud Migration Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Rosen's Diversified, Inc.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Eagan, MN, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, BigQuery, Snowflake, Data Modeling, Star Schema, dbt, Power BI, Tableau</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d795a30569c6d07</t>
+          <t>https://www.indeed.com/viewjob?jk=0d5ed846b77ab548</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sr. Consultant - Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Insygnum</t>
+          <t>WEX Inc.</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Glue, RDS, Hadoop, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Azure, GCP, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=add721e79e9d7463</t>
+          <t>https://www.indeed.com/viewjob?jk=51f550253b36df98</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Rosen's Diversified, Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Green Bay, WI, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Docker, Kubernetes, pytest</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43e06e046a3009ec</t>
+          <t>https://www.indeed.com/viewjob?jk=71acb476a93daa68</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Software Engineer - Platform</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Rosen's Diversified, Inc.</t>
+          <t>Redfin</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Eagan, MN, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d5ed846b77ab548</t>
+          <t>https://www.indeed.com/viewjob?jk=d62543661efd20a8</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Scientist - AI/ML Engineering Focus - Remote</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>WEX Inc.</t>
+          <t>UnitedHealthcare</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Kafka, Databricks Lakehouse, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,102 +2806,102 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51f550253b36df98</t>
+          <t>https://www.indeed.com/viewjob?jk=0b996573f5f8fa39</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack</t>
+          <t>AI/ML Software Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Numa Management Associates</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Docker, Kubernetes, pytest</t>
+          <t>AWS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, MLOps, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71acb476a93daa68</t>
+          <t>https://www.indeed.com/viewjob?jk=3b8199552143ed2c</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Platform</t>
+          <t>AWS API Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Redfin</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, Databricks, Hadoop, Spark, Scala, Kafka, MongoDB, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d62543661efd20a8</t>
+          <t>https://www.indeed.com/viewjob?jk=bd06c562a0dd4e4d</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - AI/ML Engineering Focus - Remote</t>
+          <t>AWS API Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>UnitedHealthcare</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Kafka, Databricks Lakehouse, ELT, MLOps, MLflow</t>
+          <t>AWS, Databricks, Hadoop, Spark, Scala, Kafka, MongoDB, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,19 +2911,19 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b996573f5f8fa39</t>
+          <t>https://www.indeed.com/viewjob?jk=7837b5aefbcb5351</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>AI/ML Software Engineer</t>
+          <t>Data Engineer (remote)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Numa Management Associates</t>
+          <t>Claritev</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, MLOps, Docker</t>
+          <t>AWS, RDS, Databricks, BigQuery, Spark, PySpark, Scala, ETL, ELT, DataOps</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b8199552143ed2c</t>
+          <t>https://www.indeed.com/viewjob?jk=c836f48c3d814cb7</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>AWS API Engineer</t>
+          <t>Product Developer Advanced</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tech Army</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Hadoop, Spark, Scala, Kafka, MongoDB, NoSQL, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, ETL, Power BI, Python</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd06c562a0dd4e4d</t>
+          <t>https://www.indeed.com/viewjob?jk=8d958ebf75215c9a</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>AWS API Engineer</t>
+          <t>Production Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Placer.ai</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Hadoop, Spark, Scala, Kafka, MongoDB, NoSQL, Docker, Kubernetes</t>
+          <t>RDS, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7837b5aefbcb5351</t>
+          <t>https://www.indeed.com/viewjob?jk=ad1335920bcdcf1c</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Engineer (remote)</t>
+          <t>Senior Digital Analytics Engineer - Customer Experience</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Claritev</t>
+          <t>Sherwin-Williams</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, BigQuery, Spark, PySpark, Scala, ETL, ELT, DataOps</t>
+          <t>AWS, IAM, RDS, Databricks, Scala, Snowflake, Power BI, Tableau, Git, SQL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c836f48c3d814cb7</t>
+          <t>https://www.indeed.com/viewjob?jk=724311be6474c008</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Product Developer Advanced</t>
+          <t>MLOps Engineer - Machine Learning Platform</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Tech Army</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, ETL, Power BI, Python</t>
+          <t>AWS, IAM, GCP, Scala, NoSQL, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d958ebf75215c9a</t>
+          <t>https://www.indeed.com/viewjob?jk=29ff9b97d0d69a97</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Production Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Placer.ai</t>
+          <t>Innovien Solutions</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, Redshift, Databricks, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad1335920bcdcf1c</t>
+          <t>https://www.indeed.com/viewjob?jk=19b0604cffe8cf9d</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Digital Analytics Engineer - Customer Experience</t>
+          <t>Service Cloud Developer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Sherwin-Williams</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Scala, Snowflake, Power BI, Tableau, Git, SQL</t>
+          <t>AWS, RDS, Azure, Data Factory, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=724311be6474c008</t>
+          <t>https://www.indeed.com/viewjob?jk=14f7aec210bdd6b1</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>MLOps Engineer - Machine Learning Platform</t>
+          <t>Data Analytics and AI Senior Consultant</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Citrin Cooperman</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Florham Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, IAM, GCP, Scala, NoSQL, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29ff9b97d0d69a97</t>
+          <t>https://www.indeed.com/viewjob?jk=ab24ee357dc36621</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Analytics and AI Senior Consultant</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Innovien Solutions</t>
+          <t>Citrin Cooperman</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Databricks, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19b0604cffe8cf9d</t>
+          <t>https://www.indeed.com/viewjob?jk=ebeab9493cf52705</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Service Cloud Developer</t>
+          <t>Data Analytics and AI Senior Consultant</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Citrin Cooperman</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Braintree, MA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14f7aec210bdd6b1</t>
+          <t>https://www.indeed.com/viewjob?jk=bd5fb31b5a0e0aed</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Data Analytics and AI Senior Consultant</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Citrin Cooperman</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,17 +3286,17 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=377a8106189cff56</t>
+          <t>https://www.indeed.com/viewjob?jk=35945946ef347401</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Florham Park, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab24ee357dc36621</t>
+          <t>https://www.indeed.com/viewjob?jk=98baf5e0e0e210ab</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebeab9493cf52705</t>
+          <t>https://www.indeed.com/viewjob?jk=619ef2ef0698f1fd</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Braintree, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd5fb31b5a0e0aed</t>
+          <t>https://www.indeed.com/viewjob?jk=16af3b0c4f8842cc</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Analytics and AI Senior Consultant</t>
+          <t>Senior Software Engineer - Django/Python</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Citrin Cooperman</t>
+          <t>ATG</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>North Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
+          <t>AWS, S3, Azure, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35945946ef347401</t>
+          <t>https://www.indeed.com/viewjob?jk=e959c5c2ece017ba</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data Analytics and AI Senior Consultant</t>
+          <t>Senior Software Engineer - Django/Python</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Citrin Cooperman</t>
+          <t>ATG</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
+          <t>AWS, S3, Azure, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98baf5e0e0e210ab</t>
+          <t>https://www.indeed.com/viewjob?jk=df9a48331ce93c56</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Analytics and AI Senior Consultant</t>
+          <t>Mid Level Software Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Citrin Cooperman</t>
+          <t>Harvestaff</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Chesterfield, MO, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
+          <t>RDS, Azure, Oracle, SQL Server, PostgreSQL, MongoDB, Cassandra, NoSQL, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=619ef2ef0698f1fd</t>
+          <t>https://www.indeed.com/viewjob?jk=ee62f5b48244cf04</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data Analytics and AI Senior Consultant</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Citrin Cooperman</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
+          <t>AWS, RDS, Azure, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Terraform, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16af3b0c4f8842cc</t>
+          <t>https://www.indeed.com/viewjob?jk=8aca26123e673da7</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Django/Python</t>
+          <t>OpenAM</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>ATG</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>North Little Rock, AR, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
+          <t>Azure, Scala, Kafka, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e959c5c2ece017ba</t>
+          <t>https://www.indeed.com/viewjob?jk=fdf8975ebf0eb43f</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Django/Python</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>ATG</t>
+          <t>L&amp;T Technology Services Ltd.</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Novi, MI, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
+          <t>Azure, Databricks, Hadoop, Spark, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df9a48331ce93c56</t>
+          <t>https://www.indeed.com/viewjob?jk=b8bace0705a89432</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Mid Level Software Engineer</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Harvestaff</t>
+          <t>S.S. White Technologies</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Chesterfield, MO, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RDS, Azure, Oracle, SQL Server, PostgreSQL, MongoDB, Cassandra, NoSQL, Jenkins, Azure DevOps</t>
+          <t>AWS, ECS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee62f5b48244cf04</t>
+          <t>https://www.indeed.com/viewjob?jk=dc670920196ab795</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Solutions Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Cellular Sales, Verizon Authorized Retailer</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Terraform, Kubernetes, SonarQube</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8aca26123e673da7</t>
+          <t>https://www.indeed.com/viewjob?jk=f9313901bc5ac9da</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>OpenAM</t>
+          <t>Software Engineer - Core Platform</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Unacast</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Azure, Scala, Kafka, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Spark, Scala, Snowflake, MySQL, DynamoDB, NoSQL, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdf8975ebf0eb43f</t>
+          <t>https://www.indeed.com/viewjob?jk=868f8c4ef1ebde56</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Sr. Data Scientist, Programmatic Algorithms</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>L&amp;T Technology Services Ltd.</t>
+          <t>Impact.Com</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Novi, MI, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Hadoop, Spark, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
+          <t>RDS, Databricks, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Kafka, MLOps</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8bace0705a89432</t>
+          <t>https://www.indeed.com/viewjob?jk=4e86578384aa4b6f</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Sr. Data Scientist, Programmatic Algorithms</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>S.S. White Technologies</t>
+          <t>Impact.Com</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,192 +3776,17 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>RDS, Databricks, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Kafka, MLOps</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc670920196ab795</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Sr. Data Scientist, Programmatic Algorithms</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Impact.Com</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Kafka, MLOps</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4e86578384aa4b6f</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Sr. Data Scientist, Programmatic Algorithms</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Impact.Com</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Kafka, MLOps</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=0db61ba5b16e71bf</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Solutions Engineer</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Cellular Sales, Verizon Authorized Retailer</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Knoxville, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, ETL, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f9313901bc5ac9da</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Software Engineer - Core Platform</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Unacast</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Ashburn, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Spark, Scala, Snowflake, MySQL, DynamoDB, NoSQL, GitHub Actions, Git</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=868f8c4ef1ebde56</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>IT Business Analyst II</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>NFI Industries</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Camden, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>AWS, ECS, RDS, Azure, Spark, PySpark, Snowflake, Data Modeling, Dimensional Modeling, Star Schema</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b12be44615688132</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-28.xlsx
+++ b/results/job_matches_2026-04-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G96"/>
+  <dimension ref="A1:G77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Salesforce Financial Services Cloud Consultant</t>
+          <t>Senior Software Developer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>27.8</v>
+        <v>25.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, Azure, Google Cloud Platform, BigQuery</t>
+          <t>AWS, Lambda, Kinesis, Redshift, S3, SQS, SNS, API Gateway, ECS, RDS</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=452ad96763321f8b</t>
+          <t>https://www.indeed.com/viewjob?jk=0e7c40f9e99ad12f</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Cloud IAM Engineer (AWS, Azure, GCP)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Quilt</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Provo, UT, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>27.1</v>
+        <v>18.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, Azure, Google Cloud Platform, GCP</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,67 +531,67 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4824fb9c6cc39b44</t>
+          <t>https://www.indeed.com/viewjob?jk=2f1b4cd21f275b79</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Software Developer</t>
+          <t>Senior Software Engineer, Full-Stack (DIT)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>NerdWallet</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>25.7</v>
+        <v>17.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Redshift, S3, SQS, SNS, API Gateway, ECS, RDS</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e7c40f9e99ad12f</t>
+          <t>https://www.indeed.com/viewjob?jk=997500b178b6daa0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Customer Support Developer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Quilt</t>
+          <t>Airbyte</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Provo, UT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f1b4cd21f275b79</t>
+          <t>https://www.indeed.com/viewjob?jk=ab2390ad9f6c9780</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab2390ad9f6c9780</t>
+          <t>https://www.indeed.com/viewjob?jk=a7fe60e6480b1a64</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Customer Support Developer</t>
+          <t>Snowflake Architect - Job ID 831</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Airbyte</t>
+          <t>Kapitus</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, IAM, RDS, Databricks</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7fe60e6480b1a64</t>
+          <t>https://www.indeed.com/viewjob?jk=30116c3087096b0c</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Snowflake Architect - Job ID 831</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Kapitus</t>
+          <t>Old National Bank</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Lake Elmo, MN, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, IAM, RDS, Databricks</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,172 +706,172 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30116c3087096b0c</t>
+          <t>https://www.indeed.com/viewjob?jk=58d405ceae103971</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>API Security IAM</t>
+          <t>Senior Associate - Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0585ca531cf89a02</t>
+          <t>https://www.indeed.com/viewjob?jk=cadb0e669ca658a7</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AWS API Engineer</t>
+          <t>Senior PS Sales Solutions Architect</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e2967a40f711a6e</t>
+          <t>https://www.indeed.com/viewjob?jk=9ed1a2a8d040517b</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Consultant SW Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Old National Bank</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Lake Elmo, MN, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58d405ceae103971</t>
+          <t>https://www.indeed.com/viewjob?jk=f9ca5a09e7cef446</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior PS Sales Solutions Architect</t>
+          <t>Data Engineer (remote)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Claritev</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
+          <t>AWS, EMR, RDS, Azure, GCP, Hadoop, Spark, Scala, Oracle, Data Modeling</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ed1a2a8d040517b</t>
+          <t>https://www.indeed.com/viewjob?jk=de8ee6455a8ca514</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Engineer (Hybrid)</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Enova International</t>
+          <t>Versant</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, GCP, Spark, Scala, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,67 +881,67 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f180f27ff7393ac</t>
+          <t>https://www.indeed.com/viewjob?jk=f536b07e93637686</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer (remote)</t>
+          <t>Software Engineer - Specialist</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Claritev</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, GCP, Hadoop, Spark, Scala, Oracle, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de8ee6455a8ca514</t>
+          <t>https://www.indeed.com/viewjob?jk=936f1055bc6513a5</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AWS Database Engineer / Cloud DBA</t>
+          <t>IT Applications Engineer V - Data Science, Data &amp; AI Engineering, Application Engineering</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Kaiser Permanente</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, ELT, MLflow, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc7b3e2ef98acf25</t>
+          <t>https://www.indeed.com/viewjob?jk=6453e30c37711925</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, NoSQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=292c1ae20b051cf4</t>
+          <t>https://www.indeed.com/viewjob?jk=d07a1b512d8f6b8e</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer - Specialist</t>
+          <t>Sr. Backend Engineer - Integrations</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=936f1055bc6513a5</t>
+          <t>https://www.indeed.com/viewjob?jk=22b8eb7f870c0ec5</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Versant</t>
+          <t>Kharon</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,112 +1046,112 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, GCP, Spark, Scala, PostgreSQL, NoSQL</t>
+          <t>AWS, Glue, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f536b07e93637686</t>
+          <t>https://www.indeed.com/viewjob?jk=429c2128943540c2</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Cloud Governance Engineer</t>
+          <t>Senior DevOps Engineer - Atlanta, GA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Cortland</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, ELT, DataOps</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Git</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d20905b5e2faaa0</t>
+          <t>https://www.indeed.com/viewjob?jk=75a9d9f16c1afffa</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Platform Engineer (Remote / Contract)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>VERVE GROUP</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Scala, ETL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, ECS, RDS, GCP, Dataflow, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a00dd6bd18f4d068</t>
+          <t>https://www.indeed.com/viewjob?jk=ca697f45b6290281</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior Data Science Engineer, GenAI Platforms &amp; Data Infrastructure</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, NoSQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d07a1b512d8f6b8e</t>
+          <t>https://www.indeed.com/viewjob?jk=21b925b3e52300cd</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr. Backend Engineer - Integrations</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Easterseals Southern California</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,59 +1196,59 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22b8eb7f870c0ec5</t>
+          <t>https://www.indeed.com/viewjob?jk=2241b1872054f42d</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Kharon</t>
+          <t>Klaviyo</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, dbt</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=429c2128943540c2</t>
+          <t>https://www.indeed.com/viewjob?jk=c14b5f2f1affd1a2</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Science Engineer, GenAI Platforms &amp; Data Infrastructure</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Aureon</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>West Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21b925b3e52300cd</t>
+          <t>https://www.indeed.com/viewjob?jk=2f774c4618ca5806</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Specialty Software Engineer - Capital Markets Reference Data</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Easterseals Southern California</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Oracle, PostgreSQL</t>
+          <t>API Gateway, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2241b1872054f42d</t>
+          <t>https://www.indeed.com/viewjob?jk=f0e85b21f1fb3187</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AWS API Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Hive, MapReduce, Impala, Spark, PySpark, Oracle, SQL Server, MySQL</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be902deb0c0cff60</t>
+          <t>https://www.indeed.com/viewjob?jk=2e59f80446549413</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Senior Integration Developer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>E Source</t>
+          <t>AlayaCare</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, PostgreSQL, ETL, Jenkins, Docker, Jenkins</t>
+          <t>AWS, Lambda, API Gateway, RDS, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc74bb7856780dfe</t>
+          <t>https://www.indeed.com/viewjob?jk=e35070e714f42f3c</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Consultant, AI &amp; Data Engineering</t>
+          <t>Senior Integration Developer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Castleton Tower</t>
+          <t>AlayaCare</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, dbt</t>
+          <t>AWS, Lambda, API Gateway, RDS, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=106bb3c12b0ce283</t>
+          <t>https://www.indeed.com/viewjob?jk=47a751a18a865523</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Senior Integration Developer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Aureon</t>
+          <t>AlayaCare</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>West Des Moines, IA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, API Gateway, RDS, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f774c4618ca5806</t>
+          <t>https://www.indeed.com/viewjob?jk=a5b72f3e295f2b38</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Specialty Software Engineer - Capital Markets Reference Data</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>HARVEST GROUP</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,17 +1466,17 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Scala, Snowflake, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0e85b21f1fb3187</t>
+          <t>https://www.indeed.com/viewjob?jk=d391d4aaecc47ecd</t>
         </is>
       </c>
     </row>
@@ -1658,25 +1658,25 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior Reliability Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Fitch Group</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Jenkins, Maven, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e59f80446549413</t>
+          <t>https://www.indeed.com/viewjob?jk=bb104709126cf2da</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Integration Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>AlayaCare</t>
+          <t>NRG Energy</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Cloud Storage, Spark, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,67 +1721,67 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e35070e714f42f3c</t>
+          <t>https://www.indeed.com/viewjob?jk=daf356dec855c3b1</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Integration Developer</t>
+          <t>System Architect IV (ATL)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>AlayaCare</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47a751a18a865523</t>
+          <t>https://www.indeed.com/viewjob?jk=562c3953d5d4cf9e</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Integration Developer</t>
+          <t>Software Engineer - Intermediate</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>AlayaCare</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5b72f3e295f2b38</t>
+          <t>https://www.indeed.com/viewjob?jk=00328cd20addd95f</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Software Engineer - Intermediate</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>HARVEST GROUP</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Scala, Snowflake, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d391d4aaecc47ecd</t>
+          <t>https://www.indeed.com/viewjob?jk=f1563bdd8162e56a</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>System Architect IV (ATL)</t>
+          <t>Data Engineer (remote)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Claritev</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hive, Impala, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=562c3953d5d4cf9e</t>
+          <t>https://www.indeed.com/viewjob?jk=60d533f19b4463da</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Engineer - Intermediate</t>
+          <t>Data Engineer (remote)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Claritev</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Maven</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hive, Impala, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00328cd20addd95f</t>
+          <t>https://www.indeed.com/viewjob?jk=aa65c57599624378</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Software Engineer - Intermediate</t>
+          <t>Data Engineer (remote)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Claritev</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Maven</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hive, Impala, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1563bdd8162e56a</t>
+          <t>https://www.indeed.com/viewjob?jk=9230bee4c19c2afb</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Solutions Architect | AI</t>
+          <t>Senior Software Engineer - Platform &amp; Integrations</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Trace3</t>
+          <t>Seismic</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fba922bb2fd28863</t>
+          <t>https://www.indeed.com/viewjob?jk=cca2fb47a24092c1</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Solutions Architect | AI</t>
+          <t>AI Commercial &amp; ML Ops Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Trace3</t>
+          <t>MGM Resorts International</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dae082eb8598575</t>
+          <t>https://www.indeed.com/viewjob?jk=9e59ac0d5620a4ae</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Solutions Architect | AI</t>
+          <t>Sr Software Engineer, Fullstack</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Trace3</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, SQL Server, Data Modeling, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,124 +2036,124 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63486d61003e0a4f</t>
+          <t>https://www.indeed.com/viewjob?jk=4fb90dbd5192ef62</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Solutions Architect | AI</t>
+          <t>Sr. Consultant - Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Trace3</t>
+          <t>Insygnum</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
+          <t>Glue, RDS, Hadoop, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d4d0f879560eea6</t>
+          <t>https://www.indeed.com/viewjob?jk=add721e79e9d7463</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer (remote)</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Claritev</t>
+          <t>Rosen's Diversified, Inc.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Green Bay, WI, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hive, Impala, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60d533f19b4463da</t>
+          <t>https://www.indeed.com/viewjob?jk=43e06e046a3009ec</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer (remote)</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Claritev</t>
+          <t>Rosen's Diversified, Inc.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Eagan, MN, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hive, Impala, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa65c57599624378</t>
+          <t>https://www.indeed.com/viewjob?jk=0d5ed846b77ab548</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer (remote)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Claritev</t>
+          <t>WEX Inc.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2162,151 +2162,151 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hive, Impala, Spark, PySpark, Scala</t>
+          <t>AWS, Azure, GCP, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9230bee4c19c2afb</t>
+          <t>https://www.indeed.com/viewjob?jk=51f550253b36df98</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Reliability Engineer</t>
+          <t>Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Fitch Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Docker, Kubernetes, pytest</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb104709126cf2da</t>
+          <t>https://www.indeed.com/viewjob?jk=71acb476a93daa68</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer - Platform</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>NRG Energy</t>
+          <t>Redfin</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Cloud Storage, Spark, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=daf356dec855c3b1</t>
+          <t>https://www.indeed.com/viewjob?jk=d62543661efd20a8</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Platform &amp; Integrations</t>
+          <t>TM1 Developer IBM Planning Analytics Solution</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Seismic</t>
+          <t xml:space="preserve">KPRMT Global solutions </t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Delaware, NJ, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cca2fb47a24092c1</t>
+          <t>https://www.indeed.com/viewjob?jk=5ba25f8dea0287eb</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Multi-Cloud Networking Engineer</t>
+          <t>Product Developer Advanced</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tech Army</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Redshift, API Gateway, ECS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, ETL, Power BI, Python</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e048a1fa8803abd</t>
+          <t>https://www.indeed.com/viewjob?jk=8d958ebf75215c9a</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>AI Commercial &amp; ML Ops Engineer</t>
+          <t>Production Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>MGM Resorts International</t>
+          <t>Placer.ai</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLflow, CI/CD</t>
+          <t>RDS, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e59ac0d5620a4ae</t>
+          <t>https://www.indeed.com/viewjob?jk=ad1335920bcdcf1c</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Service Cloud Developer</t>
+          <t>Senior Digital Analytics Engineer - Customer Experience</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Sherwin-Williams</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Databricks, Scala, Snowflake, Power BI, Tableau, Git, SQL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2004304d091ff39</t>
+          <t>https://www.indeed.com/viewjob?jk=724311be6474c008</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Cloud Network Architect</t>
+          <t>MLOps Engineer - Machine Learning Platform</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, IAM, GCP, Scala, NoSQL, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a7d02622748f5d3</t>
+          <t>https://www.indeed.com/viewjob?jk=29ff9b97d0d69a97</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sr Software Engineer, Fullstack</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>Innovien Solutions</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, SQL Server, Data Modeling, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, Redshift, Databricks, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,374 +2456,374 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fb90dbd5192ef62</t>
+          <t>https://www.indeed.com/viewjob?jk=19b0604cffe8cf9d</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Cloud Migration Engineer</t>
+          <t>Data Analytics and AI Senior Consultant</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Citrin Cooperman</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Florham Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, BigQuery, Snowflake, Data Modeling, Star Schema, dbt, Power BI, Tableau</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d795a30569c6d07</t>
+          <t>https://www.indeed.com/viewjob?jk=ab24ee357dc36621</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Backend Developer- Dallas, TX</t>
+          <t>Data Analytics and AI Senior Consultant</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Citrin Cooperman</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Scala, Kafka, PostgreSQL, MongoDB, DynamoDB, NoSQL, CI/CD</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6cf88579d0b139b</t>
+          <t>https://www.indeed.com/viewjob?jk=ebeab9493cf52705</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Backend Developer- Dallas, TX</t>
+          <t>Data Analytics and AI Senior Consultant</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Citrin Cooperman</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Braintree, MA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Scala, Kafka, PostgreSQL, MongoDB, DynamoDB, NoSQL, CI/CD</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d29f0c0f97c6ad9</t>
+          <t>https://www.indeed.com/viewjob?jk=bd5fb31b5a0e0aed</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Sr. Consultant - Data Engineer</t>
+          <t>Data Analytics and AI Senior Consultant</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Insygnum</t>
+          <t>Citrin Cooperman</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Glue, RDS, Hadoop, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, Data Modeling, ETL</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=add721e79e9d7463</t>
+          <t>https://www.indeed.com/viewjob?jk=35945946ef347401</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Analytics and AI Senior Consultant</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Rosen's Diversified, Inc.</t>
+          <t>Citrin Cooperman</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Green Bay, WI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43e06e046a3009ec</t>
+          <t>https://www.indeed.com/viewjob?jk=98baf5e0e0e210ab</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Analytics and AI Senior Consultant</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Rosen's Diversified, Inc.</t>
+          <t>Citrin Cooperman</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Eagan, MN, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d5ed846b77ab548</t>
+          <t>https://www.indeed.com/viewjob?jk=619ef2ef0698f1fd</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Analytics and AI Senior Consultant</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>WEX Inc.</t>
+          <t>Citrin Cooperman</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51f550253b36df98</t>
+          <t>https://www.indeed.com/viewjob?jk=16af3b0c4f8842cc</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack</t>
+          <t>AI/ML Software Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Numa Management Associates</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Docker, Kubernetes, pytest</t>
+          <t>AWS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, MLOps, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71acb476a93daa68</t>
+          <t>https://www.indeed.com/viewjob?jk=3b8199552143ed2c</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Platform</t>
+          <t>Data Engineer (remote)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Redfin</t>
+          <t>Claritev</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Databricks, BigQuery, Spark, PySpark, Scala, ETL, ELT, DataOps</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d62543661efd20a8</t>
+          <t>https://www.indeed.com/viewjob?jk=c836f48c3d814cb7</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - AI/ML Engineering Focus - Remote</t>
+          <t>.Net Developer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>UnitedHealthcare</t>
+          <t>Cloud and Things</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Kafka, Databricks Lakehouse, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, Azure DevOps, Docker, SonarQube, Git</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b996573f5f8fa39</t>
+          <t>https://www.indeed.com/viewjob?jk=a9e68a2fc7798ac9</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>AI/ML Software Engineer</t>
+          <t>Senior Software Engineer - Django/Python</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Numa Management Associates</t>
+          <t>ATG</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>North Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, MLOps, Docker</t>
+          <t>AWS, S3, Azure, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b8199552143ed2c</t>
+          <t>https://www.indeed.com/viewjob?jk=e959c5c2ece017ba</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>AWS API Engineer</t>
+          <t>Mid Level Software Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Harvestaff</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chesterfield, MO, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Hadoop, Spark, Scala, Kafka, MongoDB, NoSQL, Docker, Kubernetes</t>
+          <t>RDS, Azure, Oracle, SQL Server, PostgreSQL, MongoDB, Cassandra, NoSQL, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd06c562a0dd4e4d</t>
+          <t>https://www.indeed.com/viewjob?jk=ee62f5b48244cf04</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>AWS API Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Hadoop, Spark, Scala, Kafka, MongoDB, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Terraform, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7837b5aefbcb5351</t>
+          <t>https://www.indeed.com/viewjob?jk=8aca26123e673da7</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Engineer (remote)</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Claritev</t>
+          <t>S.S. White Technologies</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, BigQuery, Spark, PySpark, Scala, ETL, ELT, DataOps</t>
+          <t>AWS, ECS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c836f48c3d814cb7</t>
+          <t>https://www.indeed.com/viewjob?jk=dc670920196ab795</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Product Developer Advanced</t>
+          <t>Database Systems Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Tech Army</t>
+          <t>Estuate</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Milpitas, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, ETL, Power BI, Python</t>
+          <t>Databricks, Spark, PySpark, Scala, Oracle, SQL Server, MySQL, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d958ebf75215c9a</t>
+          <t>https://www.indeed.com/viewjob?jk=23d7f5f64249cd00</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Production Engineer</t>
+          <t>Solutions Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Placer.ai</t>
+          <t>Cellular Sales, Verizon Authorized Retailer</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad1335920bcdcf1c</t>
+          <t>https://www.indeed.com/viewjob?jk=f9313901bc5ac9da</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Digital Analytics Engineer - Customer Experience</t>
+          <t>Software Engineer - Core Platform</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Sherwin-Williams</t>
+          <t>Unacast</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Scala, Snowflake, Power BI, Tableau, Git, SQL</t>
+          <t>AWS, RDS, Spark, Scala, Snowflake, MySQL, DynamoDB, NoSQL, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=724311be6474c008</t>
+          <t>https://www.indeed.com/viewjob?jk=868f8c4ef1ebde56</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>MLOps Engineer - Machine Learning Platform</t>
+          <t>Sr. Data Scientist, Programmatic Algorithms</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Impact.Com</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, IAM, GCP, Scala, NoSQL, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Databricks, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Kafka, MLOps</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29ff9b97d0d69a97</t>
+          <t>https://www.indeed.com/viewjob?jk=4e86578384aa4b6f</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Data Scientist, Programmatic Algorithms</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Innovien Solutions</t>
+          <t>Impact.Com</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Databricks, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>RDS, Databricks, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Kafka, MLOps</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3120,671 +3120,6 @@
         </is>
       </c>
       <c r="G77" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=19b0604cffe8cf9d</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Service Cloud Developer</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=14f7aec210bdd6b1</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Data Analytics and AI Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Citrin Cooperman</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Florham Park, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ab24ee357dc36621</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Data Analytics and AI Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Citrin Cooperman</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Philadelphia, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ebeab9493cf52705</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Data Analytics and AI Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Citrin Cooperman</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Braintree, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bd5fb31b5a0e0aed</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Data Analytics and AI Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Citrin Cooperman</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Worcester, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=35945946ef347401</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Data Analytics and AI Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Citrin Cooperman</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=98baf5e0e0e210ab</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Data Analytics and AI Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Citrin Cooperman</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=619ef2ef0698f1fd</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Data Analytics and AI Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Citrin Cooperman</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=16af3b0c4f8842cc</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Django/Python</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>ATG</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>North Little Rock, AR, US USA</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>AWS, S3, Azure, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e959c5c2ece017ba</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Django/Python</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>ATG</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>AWS, S3, Azure, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=df9a48331ce93c56</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Mid Level Software Engineer</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Harvestaff</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Chesterfield, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Oracle, SQL Server, PostgreSQL, MongoDB, Cassandra, NoSQL, Jenkins, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ee62f5b48244cf04</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>American Airlines</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Terraform, Kubernetes, SonarQube</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8aca26123e673da7</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>OpenAM</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>Azure, Scala, Kafka, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fdf8975ebf0eb43f</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Software Developer</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>L&amp;T Technology Services Ltd.</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Novi, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>Azure, Databricks, Hadoop, Spark, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b8bace0705a89432</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Software Developer</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>S.S. White Technologies</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Saint Petersburg, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>AWS, ECS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dc670920196ab795</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Solutions Engineer</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Cellular Sales, Verizon Authorized Retailer</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Knoxville, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, ETL, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f9313901bc5ac9da</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Software Engineer - Core Platform</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Unacast</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Ashburn, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Spark, Scala, Snowflake, MySQL, DynamoDB, NoSQL, GitHub Actions, Git</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=868f8c4ef1ebde56</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Sr. Data Scientist, Programmatic Algorithms</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Impact.Com</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Kafka, MLOps</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4e86578384aa4b6f</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Sr. Data Scientist, Programmatic Algorithms</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Impact.Com</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Kafka, MLOps</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=0db61ba5b16e71bf</t>
         </is>

--- a/results/job_matches_2026-04-28.xlsx
+++ b/results/job_matches_2026-04-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G77"/>
+  <dimension ref="A1:G74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Software Developer</t>
+          <t>Senior Consultant - Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Torq</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>25.7</v>
+        <v>21.5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Redshift, S3, SQS, SNS, API Gateway, ECS, RDS</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, BigQuery, Scala, Kafka</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e7c40f9e99ad12f</t>
+          <t>https://www.indeed.com/viewjob?jk=7c4c907044e720da</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Customer Support Developer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Quilt</t>
+          <t>Airbyte</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Provo, UT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,67 +531,67 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f1b4cd21f275b79</t>
+          <t>https://www.indeed.com/viewjob?jk=ab2390ad9f6c9780</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Full-Stack (DIT)</t>
+          <t>Snowflake Architect - Job ID 831</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NerdWallet</t>
+          <t>Kapitus</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, IAM, RDS, Databricks</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=997500b178b6daa0</t>
+          <t>https://www.indeed.com/viewjob?jk=30116c3087096b0c</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Customer Support Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Airbyte</t>
+          <t>Silverchair</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Kafka, Snowflake, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab2390ad9f6c9780</t>
+          <t>https://www.indeed.com/viewjob?jk=03088aab7fd212d8</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Customer Support Developer</t>
+          <t>Data Engineer - Snowflake</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Airbyte</t>
+          <t>Corebridge</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, Glue, Redshift, RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,42 +636,42 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7fe60e6480b1a64</t>
+          <t>https://www.indeed.com/viewjob?jk=d3afad6ecd5a25a2</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Snowflake Architect - Job ID 831</t>
+          <t>Senior Associate - Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Kapitus</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, IAM, RDS, Databricks</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30116c3087096b0c</t>
+          <t>https://www.indeed.com/viewjob?jk=cadb0e669ca658a7</t>
         </is>
       </c>
     </row>
@@ -713,17 +713,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Associate - Data Engineer</t>
+          <t>Senior PS Sales Solutions Architect</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Databricks, Spark, PySpark</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,129 +741,129 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cadb0e669ca658a7</t>
+          <t>https://www.indeed.com/viewjob?jk=9ed1a2a8d040517b</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior PS Sales Solutions Architect</t>
+          <t>Sr. Consultant SW Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ed1a2a8d040517b</t>
+          <t>https://www.indeed.com/viewjob?jk=f9ca5a09e7cef446</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr. Consultant SW Engineer</t>
+          <t>Software Engineer - Specialist</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9ca5a09e7cef446</t>
+          <t>https://www.indeed.com/viewjob?jk=936f1055bc6513a5</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer (remote)</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Claritev</t>
+          <t>Versant</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, GCP, Hadoop, Spark, Scala, Oracle, Data Modeling</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, GCP, Spark, Scala, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de8ee6455a8ca514</t>
+          <t>https://www.indeed.com/viewjob?jk=f536b07e93637686</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Versant</t>
+          <t>Western Governors University</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, GCP, Spark, Scala, PostgreSQL, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Spark Streaming, ETL, MLOps</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f536b07e93637686</t>
+          <t>https://www.indeed.com/viewjob?jk=02b371541d1ac53b</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Engineer - Specialist</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, NoSQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=936f1055bc6513a5</t>
+          <t>https://www.indeed.com/viewjob?jk=d07a1b512d8f6b8e</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>IT Applications Engineer V - Data Science, Data &amp; AI Engineering, Application Engineering</t>
+          <t>Database Administrator - Mountlake Terrace, WA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Kaiser Permanente</t>
+          <t>Mindful Support Services</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Mountlake Terrace, WA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, ELT, MLflow, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Dimension Tables, ETL, ELT</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6453e30c37711925</t>
+          <t>https://www.indeed.com/viewjob?jk=c7f72c836b506ce1</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Sr. Backend Engineer - Integrations</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, NoSQL, CI/CD, Jenkins, Maven</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d07a1b512d8f6b8e</t>
+          <t>https://www.indeed.com/viewjob?jk=22b8eb7f870c0ec5</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sr. Backend Engineer - Integrations</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Kharon</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, Glue, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22b8eb7f870c0ec5</t>
+          <t>https://www.indeed.com/viewjob?jk=429c2128943540c2</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>IT Applications Engineer V - Data Science, Data &amp; AI Engineering, Application Engineering</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Kharon</t>
+          <t>Kaiser Permanente</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, dbt</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, ELT, MLflow, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=429c2128943540c2</t>
+          <t>https://www.indeed.com/viewjob?jk=6453e30c37711925</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer - Atlanta, GA</t>
+          <t>Senior Data Science Engineer, GenAI Platforms &amp; Data Infrastructure</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Cortland</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Git</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75a9d9f16c1afffa</t>
+          <t>https://www.indeed.com/viewjob?jk=21b925b3e52300cd</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Platform Engineer (Remote / Contract)</t>
+          <t>Senior DevOps Engineer - Atlanta, GA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>VERVE GROUP</t>
+          <t>Cortland</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, GCP, Dataflow, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Git</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca697f45b6290281</t>
+          <t>https://www.indeed.com/viewjob?jk=75a9d9f16c1afffa</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Science Engineer, GenAI Platforms &amp; Data Infrastructure</t>
+          <t>Platform Engineer (Remote / Contract)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>VERVE GROUP</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,17 +1151,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, ECS, RDS, GCP, Dataflow, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21b925b3e52300cd</t>
+          <t>https://www.indeed.com/viewjob?jk=ca697f45b6290281</t>
         </is>
       </c>
     </row>
@@ -1203,17 +1203,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Sr. SDET</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Klaviyo</t>
+          <t>Subway</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, Scala, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c14b5f2f1affd1a2</t>
+          <t>https://www.indeed.com/viewjob?jk=e99b607ba441a3b6</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>SR SDET (Sr Software Engineer in Test &amp; Merchandising Automation)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Aureon</t>
+          <t>Subway</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>West Des Moines, IA, US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, Scala, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f774c4618ca5806</t>
+          <t>https://www.indeed.com/viewjob?jk=ac35b48862d2d754</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Specialty Software Engineer - Capital Markets Reference Data</t>
+          <t>Sr Software Engineer (SQL/Databricks)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>CIBC</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, SQL Server, ETL, Power BI</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0e85b21f1fb3187</t>
+          <t>https://www.indeed.com/viewjob?jk=59821689b0632a0e</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Sr. Automation Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Subway</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Jenkins, Maven, Docker</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, DynamoDB, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e59f80446549413</t>
+          <t>https://www.indeed.com/viewjob?jk=89ac62864e6673e6</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Integration Developer</t>
+          <t>Senior Automation Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>AlayaCare</t>
+          <t>Subway</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, DynamoDB, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e35070e714f42f3c</t>
+          <t>https://www.indeed.com/viewjob?jk=fb7872e2804ae8eb</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Integration Developer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>AlayaCare</t>
+          <t>Klaviyo</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47a751a18a865523</t>
+          <t>https://www.indeed.com/viewjob?jk=c14b5f2f1affd1a2</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Integration Developer</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>AlayaCare</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5b72f3e295f2b38</t>
+          <t>https://www.indeed.com/viewjob?jk=e79ac2cb00b1176b</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>HARVEST GROUP</t>
+          <t>Aureon</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>West Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Scala, Snowflake, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d391d4aaecc47ecd</t>
+          <t>https://www.indeed.com/viewjob?jk=2f774c4618ca5806</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Founding Engineers</t>
+          <t>Senior Specialty Software Engineer - Capital Markets Reference Data</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Career Mentors</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Databricks, GCP, Spark, Kafka, Snowflake, PostgreSQL, dbt, Tableau, MLflow</t>
+          <t>API Gateway, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=004a99e42e1b83ba</t>
+          <t>https://www.indeed.com/viewjob?jk=f0e85b21f1fb3187</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Founding Engineers</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Career Mentors</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Databricks, GCP, Spark, Kafka, Snowflake, PostgreSQL, dbt, Tableau, MLflow</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cbf54fc5208e3a3</t>
+          <t>https://www.indeed.com/viewjob?jk=2e59f80446549413</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Founding Engineers</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Career Mentors</t>
+          <t>HARVEST GROUP</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Databricks, GCP, Spark, Kafka, Snowflake, PostgreSQL, dbt, Tableau, MLflow</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Scala, Snowflake, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3753908732fe77ab</t>
+          <t>https://www.indeed.com/viewjob?jk=d391d4aaecc47ecd</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e30f253b6a8acf18</t>
+          <t>https://www.indeed.com/viewjob?jk=004a99e42e1b83ba</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20194c0f45aa2c81</t>
+          <t>https://www.indeed.com/viewjob?jk=9cbf54fc5208e3a3</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Reliability Engineer</t>
+          <t>Founding Engineers</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Fitch Group</t>
+          <t>Career Mentors</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Docker, Kubernetes, Git</t>
+          <t>AWS, Databricks, GCP, Spark, Kafka, Snowflake, PostgreSQL, dbt, Tableau, MLflow</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb104709126cf2da</t>
+          <t>https://www.indeed.com/viewjob?jk=3753908732fe77ab</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Founding Engineers</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>NRG Energy</t>
+          <t>Career Mentors</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Cloud Storage, Spark, Data Modeling, ETL, ELT</t>
+          <t>AWS, Databricks, GCP, Spark, Kafka, Snowflake, PostgreSQL, dbt, Tableau, MLflow</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,59 +1721,59 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=daf356dec855c3b1</t>
+          <t>https://www.indeed.com/viewjob?jk=e30f253b6a8acf18</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>System Architect IV (ATL)</t>
+          <t>Founding Engineers</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Career Mentors</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Databricks, GCP, Spark, Kafka, Snowflake, PostgreSQL, dbt, Tableau, MLflow</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=562c3953d5d4cf9e</t>
+          <t>https://www.indeed.com/viewjob?jk=20194c0f45aa2c81</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Engineer - Intermediate</t>
+          <t>System Architect IV (ATL)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Maven</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00328cd20addd95f</t>
+          <t>https://www.indeed.com/viewjob?jk=c0679e72962f96d1</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Engineer - Intermediate</t>
+          <t>System Architect IV (ATL)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Maven</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1563bdd8162e56a</t>
+          <t>https://www.indeed.com/viewjob?jk=562c3953d5d4cf9e</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer (remote)</t>
+          <t>Software Engineer - Intermediate</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Claritev</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hive, Impala, Spark, PySpark, Scala</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60d533f19b4463da</t>
+          <t>https://www.indeed.com/viewjob?jk=00328cd20addd95f</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer (remote)</t>
+          <t>Software Engineer - Intermediate</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Claritev</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hive, Impala, Spark, PySpark, Scala</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa65c57599624378</t>
+          <t>https://www.indeed.com/viewjob?jk=f1563bdd8162e56a</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer (remote)</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Claritev</t>
+          <t>Moody's</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,29 +1921,29 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hive, Impala, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Spark, Scala</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9230bee4c19c2afb</t>
+          <t>https://www.indeed.com/viewjob?jk=777c988322e931b7</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Platform &amp; Integrations</t>
+          <t>DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Seismic</t>
+          <t>Global Technology Solutions Inc</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cca2fb47a24092c1</t>
+          <t>https://www.indeed.com/viewjob?jk=252844720ed3e114</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>AI Commercial &amp; ML Ops Engineer</t>
+          <t>Senior Reliability Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>MGM Resorts International</t>
+          <t>Fitch Group</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLflow, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e59ac0d5620a4ae</t>
+          <t>https://www.indeed.com/viewjob?jk=bb104709126cf2da</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sr Software Engineer, Fullstack</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>NRG Energy</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, SQL Server, Data Modeling, CI/CD, GitHub Actions</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Cloud Storage, Spark, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,67 +2036,67 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fb90dbd5192ef62</t>
+          <t>https://www.indeed.com/viewjob?jk=daf356dec855c3b1</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sr. Consultant - Data Engineer</t>
+          <t>Senior Software Engineer - Platform &amp; Integrations</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Insygnum</t>
+          <t>Seismic</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Glue, RDS, Hadoop, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=add721e79e9d7463</t>
+          <t>https://www.indeed.com/viewjob?jk=cca2fb47a24092c1</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>AI Commercial &amp; ML Ops Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Rosen's Diversified, Inc.</t>
+          <t>MGM Resorts International</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Green Bay, WI, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43e06e046a3009ec</t>
+          <t>https://www.indeed.com/viewjob?jk=9e59ac0d5620a4ae</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Sr Software Engineer, Fullstack</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Rosen's Diversified, Inc.</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Eagan, MN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, SQL Server, Data Modeling, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d5ed846b77ab548</t>
+          <t>https://www.indeed.com/viewjob?jk=4fb90dbd5192ef62</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Consultant - Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>WEX Inc.</t>
+          <t>Insygnum</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>Glue, RDS, Hadoop, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51f550253b36df98</t>
+          <t>https://www.indeed.com/viewjob?jk=add721e79e9d7463</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Rosen's Diversified, Inc.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Green Bay, WI, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Docker, Kubernetes, pytest</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71acb476a93daa68</t>
+          <t>https://www.indeed.com/viewjob?jk=43e06e046a3009ec</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Platform</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Redfin</t>
+          <t>Rosen's Diversified, Inc.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Eagan, MN, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d62543661efd20a8</t>
+          <t>https://www.indeed.com/viewjob?jk=0d5ed846b77ab548</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>TM1 Developer IBM Planning Analytics Solution</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t xml:space="preserve">KPRMT Global solutions </t>
+          <t>WEX Inc.</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Delaware, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,104 +2271,104 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, Azure, GCP, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ba25f8dea0287eb</t>
+          <t>https://www.indeed.com/viewjob?jk=51f550253b36df98</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Product Developer Advanced</t>
+          <t>Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Tech Army</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, ETL, Power BI, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Docker, Kubernetes, pytest</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d958ebf75215c9a</t>
+          <t>https://www.indeed.com/viewjob?jk=71acb476a93daa68</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Production Engineer</t>
+          <t>TM1 Developer IBM Planning Analytics Solution</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Placer.ai</t>
+          <t xml:space="preserve">KPRMT Global solutions </t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Delaware, NJ, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad1335920bcdcf1c</t>
+          <t>https://www.indeed.com/viewjob?jk=5ba25f8dea0287eb</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Digital Analytics Engineer - Customer Experience</t>
+          <t>AI and vision learning engineer (In person required)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Sherwin-Williams</t>
+          <t>SEC Industrial</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Peachtree Corners, GA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Scala, Snowflake, Power BI, Tableau, Git, SQL</t>
+          <t>AWS, RDS, Hadoop, Spark, Scala, NoSQL, ETL, Talend, Docker, Python</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=724311be6474c008</t>
+          <t>https://www.indeed.com/viewjob?jk=a87cdb9d826d513d</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>MLOps Engineer - Machine Learning Platform</t>
+          <t>AI/ML Software Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Numa Management Associates</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, IAM, GCP, Scala, NoSQL, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, MLOps, Docker</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29ff9b97d0d69a97</t>
+          <t>https://www.indeed.com/viewjob?jk=3b8199552143ed2c</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Product Developer Advanced</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Innovien Solutions</t>
+          <t>Tech Army</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Databricks, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, ETL, Power BI, Python</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19b0604cffe8cf9d</t>
+          <t>https://www.indeed.com/viewjob?jk=8d958ebf75215c9a</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Analytics and AI Senior Consultant</t>
+          <t>Production Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Citrin Cooperman</t>
+          <t>Placer.ai</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Florham Park, NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
+          <t>RDS, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab24ee357dc36621</t>
+          <t>https://www.indeed.com/viewjob?jk=ad1335920bcdcf1c</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Analytics and AI Senior Consultant</t>
+          <t>Senior Digital Analytics Engineer - Customer Experience</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Citrin Cooperman</t>
+          <t>Sherwin-Williams</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
+          <t>AWS, IAM, RDS, Databricks, Scala, Snowflake, Power BI, Tableau, Git, SQL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebeab9493cf52705</t>
+          <t>https://www.indeed.com/viewjob?jk=724311be6474c008</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Analytics and AI Senior Consultant</t>
+          <t>MLOps Engineer - Machine Learning Platform</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Citrin Cooperman</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Braintree, MA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,17 +2551,17 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
+          <t>AWS, IAM, GCP, Scala, NoSQL, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd5fb31b5a0e0aed</t>
+          <t>https://www.indeed.com/viewjob?jk=29ff9b97d0d69a97</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>Florham Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35945946ef347401</t>
+          <t>https://www.indeed.com/viewjob?jk=ab24ee357dc36621</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98baf5e0e0e210ab</t>
+          <t>https://www.indeed.com/viewjob?jk=ebeab9493cf52705</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Braintree, MA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=619ef2ef0698f1fd</t>
+          <t>https://www.indeed.com/viewjob?jk=bd5fb31b5a0e0aed</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16af3b0c4f8842cc</t>
+          <t>https://www.indeed.com/viewjob?jk=35945946ef347401</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>AI/ML Software Engineer</t>
+          <t>Data Analytics and AI Senior Consultant</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Numa Management Associates</t>
+          <t>Citrin Cooperman</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, MLOps, Docker</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b8199552143ed2c</t>
+          <t>https://www.indeed.com/viewjob?jk=98baf5e0e0e210ab</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer (remote)</t>
+          <t>Data Analytics and AI Senior Consultant</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Claritev</t>
+          <t>Citrin Cooperman</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, BigQuery, Spark, PySpark, Scala, ETL, ELT, DataOps</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c836f48c3d814cb7</t>
+          <t>https://www.indeed.com/viewjob?jk=619ef2ef0698f1fd</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>.Net Developer</t>
+          <t>Data Analytics and AI Senior Consultant</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Cloud and Things</t>
+          <t>Citrin Cooperman</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,17 +2796,17 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, Azure DevOps, Docker, SonarQube, Git</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9e68a2fc7798ac9</t>
+          <t>https://www.indeed.com/viewjob?jk=16af3b0c4f8842cc</t>
         </is>
       </c>
     </row>
@@ -2988,17 +2988,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Solutions Engineer</t>
+          <t>Software Engineer - Core Platform</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Cellular Sales, Verizon Authorized Retailer</t>
+          <t>Unacast</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,122 +3006,17 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, ETL, CI/CD, Docker</t>
+          <t>AWS, RDS, Spark, Scala, Snowflake, MySQL, DynamoDB, NoSQL, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9313901bc5ac9da</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Software Engineer - Core Platform</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Unacast</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Ashburn, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Spark, Scala, Snowflake, MySQL, DynamoDB, NoSQL, GitHub Actions, Git</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=868f8c4ef1ebde56</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Sr. Data Scientist, Programmatic Algorithms</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Impact.Com</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Kafka, MLOps</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4e86578384aa4b6f</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Sr. Data Scientist, Programmatic Algorithms</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Impact.Com</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Kafka, MLOps</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0db61ba5b16e71bf</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-28.xlsx
+++ b/results/job_matches_2026-04-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G74"/>
+  <dimension ref="A1:G62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,17 +503,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Customer Support Developer</t>
+          <t>Database DevOps Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Airbyte</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,17 +521,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, RDS, Hadoop, HDFS, Zookeeper, Scala, Oracle, PostgreSQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab2390ad9f6c9780</t>
+          <t>https://www.indeed.com/viewjob?jk=bdd9d74906a09ef3</t>
         </is>
       </c>
     </row>
@@ -748,17 +748,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr. Consultant SW Engineer</t>
+          <t>Data Reliability Engineer/Software Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Red Hat</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Lowell, MA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>S3, ECS, Databricks, BigQuery, Spark, Scala, Spark Streaming, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,94 +776,94 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9ca5a09e7cef446</t>
+          <t>https://www.indeed.com/viewjob?jk=bed2b2b5d3a2123b</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineer - Specialist</t>
+          <t>Sr. Consultant SW Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=936f1055bc6513a5</t>
+          <t>https://www.indeed.com/viewjob?jk=f9ca5a09e7cef446</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Platform Engineer- 6 Month Assignment</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Versant</t>
+          <t>MAXhealth</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, GCP, Spark, Scala, PostgreSQL, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Cloud Storage, Scala, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f536b07e93637686</t>
+          <t>https://www.indeed.com/viewjob?jk=d635caaec7baf168</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Western Governors University</t>
+          <t>Versant</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Spark Streaming, ETL, MLOps</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, GCP, Spark, Scala, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02b371541d1ac53b</t>
+          <t>https://www.indeed.com/viewjob?jk=f536b07e93637686</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Western Governors University</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, NoSQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Spark Streaming, ETL, MLOps</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d07a1b512d8f6b8e</t>
+          <t>https://www.indeed.com/viewjob?jk=02b371541d1ac53b</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Database Administrator - Mountlake Terrace, WA</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Mindful Support Services</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Mountlake Terrace, WA, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Dimension Tables, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, NoSQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7f72c836b506ce1</t>
+          <t>https://www.indeed.com/viewjob?jk=d07a1b512d8f6b8e</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sr. Backend Engineer - Integrations</t>
+          <t>Database Administrator - Mountlake Terrace, WA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Mindful Support Services</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Mountlake Terrace, WA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Dimension Tables, ETL, ELT</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22b8eb7f870c0ec5</t>
+          <t>https://www.indeed.com/viewjob?jk=c7f72c836b506ce1</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Backend Engineer - Integrations</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Kharon</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,17 +1011,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, dbt</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=429c2128943540c2</t>
+          <t>https://www.indeed.com/viewjob?jk=22b8eb7f870c0ec5</t>
         </is>
       </c>
     </row>
@@ -1168,17 +1168,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. SDET</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Easterseals Southern California</t>
+          <t>Subway</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,24 +1186,24 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Oracle, PostgreSQL</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, Scala, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2241b1872054f42d</t>
+          <t>https://www.indeed.com/viewjob?jk=e99b607ba441a3b6</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sr. SDET</t>
+          <t>SR SDET (Sr Software Engineer in Test &amp; Merchandising Automation)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e99b607ba441a3b6</t>
+          <t>https://www.indeed.com/viewjob?jk=ac35b48862d2d754</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SR SDET (Sr Software Engineer in Test &amp; Merchandising Automation)</t>
+          <t>Sr Software Engineer (SQL/Databricks)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Subway</t>
+          <t>CIBC</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Shelton, CT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, Scala, ELT, CI/CD</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, SQL Server, ETL, Power BI</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac35b48862d2d754</t>
+          <t>https://www.indeed.com/viewjob?jk=59821689b0632a0e</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sr Software Engineer (SQL/Databricks)</t>
+          <t>Sr. Automation Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CIBC</t>
+          <t>Subway</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, SQL Server, ETL, Power BI</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, DynamoDB, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,14 +1301,14 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59821689b0632a0e</t>
+          <t>https://www.indeed.com/viewjob?jk=89ac62864e6673e6</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sr. Automation Engineer</t>
+          <t>Senior Automation Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89ac62864e6673e6</t>
+          <t>https://www.indeed.com/viewjob?jk=fb7872e2804ae8eb</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Automation Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Subway</t>
+          <t>Klaviyo</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Shelton, CT, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, DynamoDB, ELT, CI/CD</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb7872e2804ae8eb</t>
+          <t>https://www.indeed.com/viewjob?jk=c14b5f2f1affd1a2</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Klaviyo</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c14b5f2f1affd1a2</t>
+          <t>https://www.indeed.com/viewjob?jk=e79ac2cb00b1176b</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Aureon</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>West Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e79ac2cb00b1176b</t>
+          <t>https://www.indeed.com/viewjob?jk=2f774c4618ca5806</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Senior Specialty Software Engineer - Capital Markets Reference Data</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Aureon</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>West Des Moines, IA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, ETL, ELT</t>
+          <t>API Gateway, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f774c4618ca5806</t>
+          <t>https://www.indeed.com/viewjob?jk=f0e85b21f1fb3187</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Specialty Software Engineer - Capital Markets Reference Data</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0e85b21f1fb3187</t>
+          <t>https://www.indeed.com/viewjob?jk=2e59f80446549413</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>HARVEST GROUP</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Jenkins, Maven, Docker</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Scala, Snowflake, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e59f80446549413</t>
+          <t>https://www.indeed.com/viewjob?jk=d391d4aaecc47ecd</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Founding Engineers</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>HARVEST GROUP</t>
+          <t>Career Mentors</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Scala, Snowflake, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Databricks, GCP, Spark, Kafka, Snowflake, PostgreSQL, dbt, Tableau, MLflow</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d391d4aaecc47ecd</t>
+          <t>https://www.indeed.com/viewjob?jk=004a99e42e1b83ba</t>
         </is>
       </c>
     </row>
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=004a99e42e1b83ba</t>
+          <t>https://www.indeed.com/viewjob?jk=9cbf54fc5208e3a3</t>
         </is>
       </c>
     </row>
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cbf54fc5208e3a3</t>
+          <t>https://www.indeed.com/viewjob?jk=3753908732fe77ab</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3753908732fe77ab</t>
+          <t>https://www.indeed.com/viewjob?jk=e30f253b6a8acf18</t>
         </is>
       </c>
     </row>
@@ -1721,42 +1721,42 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e30f253b6a8acf18</t>
+          <t>https://www.indeed.com/viewjob?jk=20194c0f45aa2c81</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Founding Engineers</t>
+          <t>System Architect IV (ATL)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Career Mentors</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Databricks, GCP, Spark, Kafka, Snowflake, PostgreSQL, dbt, Tableau, MLflow</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20194c0f45aa2c81</t>
+          <t>https://www.indeed.com/viewjob?jk=c0679e72962f96d1</t>
         </is>
       </c>
     </row>
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0679e72962f96d1</t>
+          <t>https://www.indeed.com/viewjob?jk=562c3953d5d4cf9e</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>System Architect IV (ATL)</t>
+          <t>Asset &amp; Wealth Management-Software Engineering-Associate-Dallas</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Glue, EMR, Redshift, S3, Hadoop, Spark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=562c3953d5d4cf9e</t>
+          <t>https://www.indeed.com/viewjob?jk=ce31ad37d0b4074e</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Engineer - Intermediate</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Moody's</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Maven</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Spark, Scala</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00328cd20addd95f</t>
+          <t>https://www.indeed.com/viewjob?jk=777c988322e931b7</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Engineer - Intermediate</t>
+          <t>DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Global Technology Solutions Inc</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Maven</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1563bdd8162e56a</t>
+          <t>https://www.indeed.com/viewjob?jk=252844720ed3e114</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Reliability Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Moody's</t>
+          <t>Fitch Group</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Spark, Scala</t>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=777c988322e931b7</t>
+          <t>https://www.indeed.com/viewjob?jk=bb104709126cf2da</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>DevSecOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Global Technology Solutions Inc</t>
+          <t>NRG Energy</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Terraform</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Cloud Storage, Spark, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=252844720ed3e114</t>
+          <t>https://www.indeed.com/viewjob?jk=daf356dec855c3b1</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Reliability Engineer</t>
+          <t>Senior Software Engineer - Platform &amp; Integrations</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Fitch Group</t>
+          <t>Seismic</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb104709126cf2da</t>
+          <t>https://www.indeed.com/viewjob?jk=cca2fb47a24092c1</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Commercial &amp; ML Ops Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>NRG Energy</t>
+          <t>MGM Resorts International</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Cloud Storage, Spark, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=daf356dec855c3b1</t>
+          <t>https://www.indeed.com/viewjob?jk=9e59ac0d5620a4ae</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Platform &amp; Integrations</t>
+          <t>Sr Software Engineer, Fullstack</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Seismic</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, SQL Server, Data Modeling, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,67 +2071,67 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cca2fb47a24092c1</t>
+          <t>https://www.indeed.com/viewjob?jk=4fb90dbd5192ef62</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>AI Commercial &amp; ML Ops Engineer</t>
+          <t>Sr. Consultant - Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>MGM Resorts International</t>
+          <t>Insygnum</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLflow, CI/CD</t>
+          <t>Glue, RDS, Hadoop, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e59ac0d5620a4ae</t>
+          <t>https://www.indeed.com/viewjob?jk=add721e79e9d7463</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr Software Engineer, Fullstack</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>Rosen's Diversified, Inc.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Green Bay, WI, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, SQL Server, Data Modeling, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fb90dbd5192ef62</t>
+          <t>https://www.indeed.com/viewjob?jk=43e06e046a3009ec</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sr. Consultant - Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Insygnum</t>
+          <t>Rosen's Diversified, Inc.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Eagan, MN, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Glue, RDS, Hadoop, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=add721e79e9d7463</t>
+          <t>https://www.indeed.com/viewjob?jk=0d5ed846b77ab548</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Rosen's Diversified, Inc.</t>
+          <t>Ansell</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Green Bay, WI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MongoDB, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43e06e046a3009ec</t>
+          <t>https://www.indeed.com/viewjob?jk=ddfd90d1833c2dcd</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Rosen's Diversified, Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Eagan, MN, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Docker, Kubernetes, pytest</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d5ed846b77ab548</t>
+          <t>https://www.indeed.com/viewjob?jk=71acb476a93daa68</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>TM1 Developer IBM Planning Analytics Solution</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>WEX Inc.</t>
+          <t xml:space="preserve">KPRMT Global solutions </t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Delaware, NJ, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,42 +2271,42 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51f550253b36df98</t>
+          <t>https://www.indeed.com/viewjob?jk=5ba25f8dea0287eb</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack</t>
+          <t>AI and vision learning engineer (In person required)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>SEC Industrial</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Peachtree Corners, GA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Docker, Kubernetes, pytest</t>
+          <t>AWS, RDS, Hadoop, Spark, Scala, NoSQL, ETL, Talend, Docker, Python</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,59 +2316,59 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71acb476a93daa68</t>
+          <t>https://www.indeed.com/viewjob?jk=a87cdb9d826d513d</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>TM1 Developer IBM Planning Analytics Solution</t>
+          <t>AI/ML Software Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t xml:space="preserve">KPRMT Global solutions </t>
+          <t>Numa Management Associates</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Delaware, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, MLOps, Docker</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ba25f8dea0287eb</t>
+          <t>https://www.indeed.com/viewjob?jk=3b8199552143ed2c</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>AI and vision learning engineer (In person required)</t>
+          <t>Product Developer Advanced</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>SEC Industrial</t>
+          <t>Tech Army</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Peachtree Corners, GA, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Spark, Scala, NoSQL, ETL, Talend, Docker, Python</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, ETL, Power BI, Python</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a87cdb9d826d513d</t>
+          <t>https://www.indeed.com/viewjob?jk=8d958ebf75215c9a</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>AI/ML Software Engineer</t>
+          <t>Senior Software Engineer - Django/Python</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Numa Management Associates</t>
+          <t>ATG</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>North Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, MLOps, Docker</t>
+          <t>AWS, S3, Azure, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b8199552143ed2c</t>
+          <t>https://www.indeed.com/viewjob?jk=e959c5c2ece017ba</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Product Developer Advanced</t>
+          <t>Mid Level Software Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Tech Army</t>
+          <t>Harvestaff</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Chesterfield, MO, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, ETL, Power BI, Python</t>
+          <t>RDS, Azure, Oracle, SQL Server, PostgreSQL, MongoDB, Cassandra, NoSQL, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d958ebf75215c9a</t>
+          <t>https://www.indeed.com/viewjob?jk=ee62f5b48244cf04</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Production Engineer</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Placer.ai</t>
+          <t>S.S. White Technologies</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, ECS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad1335920bcdcf1c</t>
+          <t>https://www.indeed.com/viewjob?jk=dc670920196ab795</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Digital Analytics Engineer - Customer Experience</t>
+          <t>Database Systems Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Sherwin-Williams</t>
+          <t>Estuate</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Milpitas, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Scala, Snowflake, Power BI, Tableau, Git, SQL</t>
+          <t>Databricks, Spark, PySpark, Scala, Oracle, SQL Server, MySQL, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=724311be6474c008</t>
+          <t>https://www.indeed.com/viewjob?jk=23d7f5f64249cd00</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>MLOps Engineer - Machine Learning Platform</t>
+          <t>Software Engineer - Core Platform</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Unacast</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, IAM, GCP, Scala, NoSQL, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Spark, Scala, Snowflake, MySQL, DynamoDB, NoSQL, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29ff9b97d0d69a97</t>
+          <t>https://www.indeed.com/viewjob?jk=868f8c4ef1ebde56</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Analytics and AI Senior Consultant</t>
+          <t>Software Engineer, Search and Alerts</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Citrin Cooperman</t>
+          <t>Fitch Group</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Florham Park, NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,437 +2586,17 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
+          <t>AWS, Kinesis, S3, Oracle, MongoDB, DynamoDB, NoSQL, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab24ee357dc36621</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Data Analytics and AI Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Citrin Cooperman</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Philadelphia, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ebeab9493cf52705</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Data Analytics and AI Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Citrin Cooperman</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Braintree, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bd5fb31b5a0e0aed</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Data Analytics and AI Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Citrin Cooperman</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Worcester, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=35945946ef347401</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Data Analytics and AI Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Citrin Cooperman</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=98baf5e0e0e210ab</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Data Analytics and AI Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Citrin Cooperman</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=619ef2ef0698f1fd</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Data Analytics and AI Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Citrin Cooperman</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=16af3b0c4f8842cc</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Django/Python</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>ATG</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>North Little Rock, AR, US USA</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>AWS, S3, Azure, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e959c5c2ece017ba</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Mid Level Software Engineer</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Harvestaff</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Chesterfield, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Oracle, SQL Server, PostgreSQL, MongoDB, Cassandra, NoSQL, Jenkins, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ee62f5b48244cf04</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>American Airlines</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Terraform, Kubernetes, SonarQube</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8aca26123e673da7</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Software Developer</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>S.S. White Technologies</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Saint Petersburg, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>AWS, ECS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dc670920196ab795</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Database Systems Engineer</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Estuate</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Milpitas, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>Databricks, Spark, PySpark, Scala, Oracle, SQL Server, MySQL, ETL, ELT, Power BI</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=23d7f5f64249cd00</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Software Engineer - Core Platform</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Unacast</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Ashburn, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Spark, Scala, Snowflake, MySQL, DynamoDB, NoSQL, GitHub Actions, Git</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=868f8c4ef1ebde56</t>
+          <t>https://www.indeed.com/viewjob?jk=8e27c3a57395d5ed</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-28.xlsx
+++ b/results/job_matches_2026-04-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G62"/>
+  <dimension ref="A1:G74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,25 +503,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Database DevOps Engineer</t>
+          <t>Cloud &amp; Digital Platform DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Diality Inc</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>18.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Zookeeper, Scala, Oracle, PostgreSQL, NoSQL, ETL</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,172 +531,172 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdd9d74906a09ef3</t>
+          <t>https://www.indeed.com/viewjob?jk=089debbb9a2ef97f</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Snowflake Architect - Job ID 831</t>
+          <t>Senior Engineer, Data</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kapitus</t>
+          <t>Dutch Bros Coffee</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>18.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, IAM, RDS, Databricks</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Cloud Storage, Hive, Spark, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30116c3087096b0c</t>
+          <t>https://www.indeed.com/viewjob?jk=84a91bd027b544af</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>SENIOR DATA ENGINEER (REMOTE OPPORTUNITY)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Silverchair</t>
+          <t>Hyatt</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16</v>
+        <v>18.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Kafka, Snowflake, Data Modeling, Star Schema</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Spark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03088aab7fd212d8</t>
+          <t>https://www.indeed.com/viewjob?jk=8ebdb111545a743c</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer - Snowflake</t>
+          <t>Database DevOps Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Corebridge</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Hadoop, HDFS, Zookeeper, Scala, Oracle, PostgreSQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3afad6ecd5a25a2</t>
+          <t>https://www.indeed.com/viewjob?jk=bdd9d74906a09ef3</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Associate - Data Engineer</t>
+          <t>Databricks Architect</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Stitch Consulting Services, Inc.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Databricks, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cadb0e669ca658a7</t>
+          <t>https://www.indeed.com/viewjob?jk=1e709ce8d08339ad</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Snowflake Architect - Job ID 831</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Old National Bank</t>
+          <t>Kapitus</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Lake Elmo, MN, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, IAM, RDS, Databricks</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,207 +706,207 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58d405ceae103971</t>
+          <t>https://www.indeed.com/viewjob?jk=30116c3087096b0c</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior PS Sales Solutions Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Silverchair</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Kafka, Snowflake, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ed1a2a8d040517b</t>
+          <t>https://www.indeed.com/viewjob?jk=03088aab7fd212d8</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Reliability Engineer/Software Engineer</t>
+          <t>Data Engineer - Snowflake</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Red Hat</t>
+          <t>Corebridge</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lowell, MA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>S3, ECS, Databricks, BigQuery, Spark, Scala, Spark Streaming, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Glue, Redshift, RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bed2b2b5d3a2123b</t>
+          <t>https://www.indeed.com/viewjob?jk=d3afad6ecd5a25a2</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr. Consultant SW Engineer</t>
+          <t>Senior Associate - Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9ca5a09e7cef446</t>
+          <t>https://www.indeed.com/viewjob?jk=cadb0e669ca658a7</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Platform Engineer- 6 Month Assignment</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>MAXhealth</t>
+          <t>Old National Bank</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Lake Elmo, MN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Cloud Storage, Scala, SQL Server, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d635caaec7baf168</t>
+          <t>https://www.indeed.com/viewjob?jk=58d405ceae103971</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior PS Sales Solutions Architect</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Versant</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.2</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, GCP, Spark, Scala, PostgreSQL, NoSQL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f536b07e93637686</t>
+          <t>https://www.indeed.com/viewjob?jk=9ed1a2a8d040517b</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Data Reliability Engineer/Software Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Western Governors University</t>
+          <t>Red Hat</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Lowell, MA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Spark Streaming, ETL, MLOps</t>
+          <t>S3, ECS, Databricks, BigQuery, Spark, Scala, Spark Streaming, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,67 +916,67 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02b371541d1ac53b</t>
+          <t>https://www.indeed.com/viewjob?jk=bed2b2b5d3a2123b</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Sr. Consultant SW Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, NoSQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d07a1b512d8f6b8e</t>
+          <t>https://www.indeed.com/viewjob?jk=f9ca5a09e7cef446</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Database Administrator - Mountlake Terrace, WA</t>
+          <t>NLM Cloud Engineer I</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Mindful Support Services</t>
+          <t>Lexical Intelligence, LLC</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Mountlake Terrace, WA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Dimension Tables, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, Hadoop, Spark, Scala, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,59 +986,59 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7f72c836b506ce1</t>
+          <t>https://www.indeed.com/viewjob?jk=1f7f43fcc961cf9a</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sr. Backend Engineer - Integrations</t>
+          <t>Data Platform Engineer- 6 Month Assignment</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>MAXhealth</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Cloud Storage, Scala, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22b8eb7f870c0ec5</t>
+          <t>https://www.indeed.com/viewjob?jk=d635caaec7baf168</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>IT Applications Engineer V - Data Science, Data &amp; AI Engineering, Application Engineering</t>
+          <t>NLM Cloud Engineer II</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Kaiser Permanente</t>
+          <t>Lexical Intelligence, LLC</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,77 +1046,77 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, ELT, MLflow, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, Spark, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6453e30c37711925</t>
+          <t>https://www.indeed.com/viewjob?jk=49524b4a45bcb416</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Science Engineer, GenAI Platforms &amp; Data Infrastructure</t>
+          <t>Mid-Level Data Engineer, Global</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21b925b3e52300cd</t>
+          <t>https://www.indeed.com/viewjob?jk=9cd7e80ca3c98167</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer - Atlanta, GA</t>
+          <t>Cloud &amp; Digital Platform Architect</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Cortland</t>
+          <t>Diality Inc</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Git</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, SQS, SNS</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,67 +1126,67 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75a9d9f16c1afffa</t>
+          <t>https://www.indeed.com/viewjob?jk=969f04a102da7944</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Platform Engineer (Remote / Contract)</t>
+          <t>IT Applications Engineer V - Data Science, Data &amp; AI Engineering, Application Engineering</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>VERVE GROUP</t>
+          <t>Kaiser Permanente</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, GCP, Dataflow, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, ELT, MLflow, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca697f45b6290281</t>
+          <t>https://www.indeed.com/viewjob?jk=6453e30c37711925</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr. SDET</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Subway</t>
+          <t>Western Governors University</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Shelton, CT, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, Scala, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Spark Streaming, ETL, MLOps</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,67 +1196,67 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e99b607ba441a3b6</t>
+          <t>https://www.indeed.com/viewjob?jk=02b371541d1ac53b</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SR SDET (Sr Software Engineer in Test &amp; Merchandising Automation)</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Subway</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Shelton, CT, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, Scala, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, NoSQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac35b48862d2d754</t>
+          <t>https://www.indeed.com/viewjob?jk=d07a1b512d8f6b8e</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sr Software Engineer (SQL/Databricks)</t>
+          <t>Database Administrator - Mountlake Terrace, WA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CIBC</t>
+          <t>Mindful Support Services</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Mountlake Terrace, WA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, SQL Server, ETL, Power BI</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Dimension Tables, ETL, ELT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,59 +1266,59 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59821689b0632a0e</t>
+          <t>https://www.indeed.com/viewjob?jk=c7f72c836b506ce1</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sr. Automation Engineer</t>
+          <t>Sr. Backend Engineer - Integrations</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Subway</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Shelton, CT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, DynamoDB, ELT, CI/CD</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89ac62864e6673e6</t>
+          <t>https://www.indeed.com/viewjob?jk=22b8eb7f870c0ec5</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Automation Engineer</t>
+          <t>Senior Data Science Engineer, GenAI Platforms &amp; Data Infrastructure</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Subway</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Shelton, CT, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, DynamoDB, ELT, CI/CD</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb7872e2804ae8eb</t>
+          <t>https://www.indeed.com/viewjob?jk=21b925b3e52300cd</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior DevOps Engineer - Atlanta, GA</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Klaviyo</t>
+          <t>Cortland</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Git</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c14b5f2f1affd1a2</t>
+          <t>https://www.indeed.com/viewjob?jk=75a9d9f16c1afffa</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>Platform Engineer (Remote / Contract)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>VERVE GROUP</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, ECS, RDS, GCP, Dataflow, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e79ac2cb00b1176b</t>
+          <t>https://www.indeed.com/viewjob?jk=ca697f45b6290281</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Sr. SDET</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Aureon</t>
+          <t>Subway</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>West Des Moines, IA, US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, Scala, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f774c4618ca5806</t>
+          <t>https://www.indeed.com/viewjob?jk=e99b607ba441a3b6</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Specialty Software Engineer - Capital Markets Reference Data</t>
+          <t>SR SDET (Sr Software Engineer in Test &amp; Merchandising Automation)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Subway</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, Scala, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0e85b21f1fb3187</t>
+          <t>https://www.indeed.com/viewjob?jk=ac35b48862d2d754</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Aureon</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>West Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Jenkins, Maven, Docker</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e59f80446549413</t>
+          <t>https://www.indeed.com/viewjob?jk=2f774c4618ca5806</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Sr Software Engineer (SQL/Databricks)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>HARVEST GROUP</t>
+          <t>CIBC</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Scala, Snowflake, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, SQL Server, ETL, Power BI</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d391d4aaecc47ecd</t>
+          <t>https://www.indeed.com/viewjob?jk=59821689b0632a0e</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Founding Engineers</t>
+          <t>Sr. Automation Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Career Mentors</t>
+          <t>Subway</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Databricks, GCP, Spark, Kafka, Snowflake, PostgreSQL, dbt, Tableau, MLflow</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, DynamoDB, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=004a99e42e1b83ba</t>
+          <t>https://www.indeed.com/viewjob?jk=89ac62864e6673e6</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Founding Engineers</t>
+          <t>Senior Automation Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Career Mentors</t>
+          <t>Subway</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Databricks, GCP, Spark, Kafka, Snowflake, PostgreSQL, dbt, Tableau, MLflow</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, DynamoDB, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cbf54fc5208e3a3</t>
+          <t>https://www.indeed.com/viewjob?jk=fb7872e2804ae8eb</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Founding Engineers</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Career Mentors</t>
+          <t>Klaviyo</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Databricks, GCP, Spark, Kafka, Snowflake, PostgreSQL, dbt, Tableau, MLflow</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3753908732fe77ab</t>
+          <t>https://www.indeed.com/viewjob?jk=c14b5f2f1affd1a2</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Founding Engineers</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Career Mentors</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Databricks, GCP, Spark, Kafka, Snowflake, PostgreSQL, dbt, Tableau, MLflow</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e30f253b6a8acf18</t>
+          <t>https://www.indeed.com/viewjob?jk=e79ac2cb00b1176b</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Founding Engineers</t>
+          <t>Senior Specialty Software Engineer - Capital Markets Reference Data</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Career Mentors</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,104 +1711,104 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Databricks, GCP, Spark, Kafka, Snowflake, PostgreSQL, dbt, Tableau, MLflow</t>
+          <t>API Gateway, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20194c0f45aa2c81</t>
+          <t>https://www.indeed.com/viewjob?jk=f0e85b21f1fb3187</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>System Architect IV (ATL)</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0679e72962f96d1</t>
+          <t>https://www.indeed.com/viewjob?jk=2e59f80446549413</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>System Architect IV (ATL)</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>HARVEST GROUP</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Scala, Snowflake, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=562c3953d5d4cf9e</t>
+          <t>https://www.indeed.com/viewjob?jk=d391d4aaecc47ecd</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Asset &amp; Wealth Management-Software Engineering-Associate-Dallas</t>
+          <t>System Architect IV (ATL)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, S3, Hadoop, Spark, Scala, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce31ad37d0b4074e</t>
+          <t>https://www.indeed.com/viewjob?jk=c0679e72962f96d1</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>System Architect IV (ATL)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Moody's</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=777c988322e931b7</t>
+          <t>https://www.indeed.com/viewjob?jk=562c3953d5d4cf9e</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>DevSecOps Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Global Technology Solutions Inc</t>
+          <t>Dealpath</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Terraform</t>
+          <t>AWS, S3, IAM, RDS, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=252844720ed3e114</t>
+          <t>https://www.indeed.com/viewjob?jk=645d3d76b515ea5a</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Reliability Engineer</t>
+          <t>Asset &amp; Wealth Management-Software Engineering-Associate-Dallas</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Fitch Group</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Docker, Kubernetes, Git</t>
+          <t>AWS, Glue, EMR, Redshift, S3, Hadoop, Spark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb104709126cf2da</t>
+          <t>https://www.indeed.com/viewjob?jk=ce31ad37d0b4074e</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>NRG Energy</t>
+          <t>Moody's</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,29 +1956,29 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Cloud Storage, Spark, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Spark, Scala</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=daf356dec855c3b1</t>
+          <t>https://www.indeed.com/viewjob?jk=777c988322e931b7</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Platform &amp; Integrations</t>
+          <t>DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Seismic</t>
+          <t>Global Technology Solutions Inc</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cca2fb47a24092c1</t>
+          <t>https://www.indeed.com/viewjob?jk=252844720ed3e114</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>AI Commercial &amp; ML Ops Engineer</t>
+          <t>Senior Reliability Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>MGM Resorts International</t>
+          <t>Fitch Group</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLflow, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e59ac0d5620a4ae</t>
+          <t>https://www.indeed.com/viewjob?jk=bb104709126cf2da</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sr Software Engineer, Fullstack</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>NRG Energy</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, SQL Server, Data Modeling, CI/CD, GitHub Actions</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Cloud Storage, Spark, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fb90dbd5192ef62</t>
+          <t>https://www.indeed.com/viewjob?jk=daf356dec855c3b1</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sr. Consultant - Data Engineer</t>
+          <t>Software Engineer, Finance Applications</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Insygnum</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Francisco Bay Area, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Glue, RDS, Hadoop, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, Oracle, MySQL, DynamoDB, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=add721e79e9d7463</t>
+          <t>https://www.indeed.com/viewjob?jk=5be60fb53ad2487f</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Software Engineer - Platform &amp; Integrations</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Rosen's Diversified, Inc.</t>
+          <t>Seismic</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Green Bay, WI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43e06e046a3009ec</t>
+          <t>https://www.indeed.com/viewjob?jk=cca2fb47a24092c1</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>AI Commercial &amp; ML Ops Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Rosen's Diversified, Inc.</t>
+          <t>MGM Resorts International</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Eagan, MN, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,59 +2176,59 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d5ed846b77ab548</t>
+          <t>https://www.indeed.com/viewjob?jk=9e59ac0d5620a4ae</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Sr Software Engineer, Fullstack</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Ansell</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MongoDB, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, SQL Server, Data Modeling, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddfd90d1833c2dcd</t>
+          <t>https://www.indeed.com/viewjob?jk=4fb90dbd5192ef62</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack</t>
+          <t>Sr. Consultant - Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Insygnum</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Docker, Kubernetes, pytest</t>
+          <t>Glue, RDS, Hadoop, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71acb476a93daa68</t>
+          <t>https://www.indeed.com/viewjob?jk=add721e79e9d7463</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>TM1 Developer IBM Planning Analytics Solution</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t xml:space="preserve">KPRMT Global solutions </t>
+          <t>Rosen's Diversified, Inc.</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Delaware, NJ, US USA</t>
+          <t>Green Bay, WI, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,64 +2271,64 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ba25f8dea0287eb</t>
+          <t>https://www.indeed.com/viewjob?jk=43e06e046a3009ec</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>AI and vision learning engineer (In person required)</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>SEC Industrial</t>
+          <t>Rosen's Diversified, Inc.</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Peachtree Corners, GA, US USA</t>
+          <t>Eagan, MN, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Spark, Scala, NoSQL, ETL, Talend, Docker, Python</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a87cdb9d826d513d</t>
+          <t>https://www.indeed.com/viewjob?jk=0d5ed846b77ab548</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>AI/ML Software Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Numa Management Associates</t>
+          <t>OEConnection</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2337,186 +2337,186 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, MLOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b8199552143ed2c</t>
+          <t>https://www.indeed.com/viewjob?jk=545e32663300e2ec</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Product Developer Advanced</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Tech Army</t>
+          <t>OEConnection</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, ETL, Power BI, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d958ebf75215c9a</t>
+          <t>https://www.indeed.com/viewjob?jk=78c8d1f679e08f02</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Django/Python</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ATG</t>
+          <t>RYZE Claim Solutions</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>North Little Rock, AR, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
+          <t>RDS, Azure, Scala, PostgreSQL, Power BI, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e959c5c2ece017ba</t>
+          <t>https://www.indeed.com/viewjob?jk=75d6a299e37b16a3</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Mid Level Software Engineer</t>
+          <t>Software Sr Developer, Marketing and Communications</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Harvestaff</t>
+          <t>DaVita</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Chesterfield, MO, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Oracle, SQL Server, PostgreSQL, MongoDB, Cassandra, NoSQL, Jenkins, Azure DevOps</t>
+          <t>API Gateway, RDS, GCP, Scala, SQL Server, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee62f5b48244cf04</t>
+          <t>https://www.indeed.com/viewjob?jk=2f4e10eee0c4935f</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Senior Analytics Engineer, Applied AI</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>S.S. White Technologies</t>
+          <t>MDVIP LLC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Snowflake, SQL Server, dbt, Power BI, Python</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc670920196ab795</t>
+          <t>https://www.indeed.com/viewjob?jk=386fc1ac3272e529</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Database Systems Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Estuate</t>
+          <t>Ansell</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Milpitas, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Databricks, Spark, PySpark, Scala, Oracle, SQL Server, MySQL, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MongoDB, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,75 +2526,495 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23d7f5f64249cd00</t>
+          <t>https://www.indeed.com/viewjob?jk=ddfd90d1833c2dcd</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Engineer - Core Platform</t>
+          <t>Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Unacast</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Snowflake, MySQL, DynamoDB, NoSQL, GitHub Actions, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Docker, Kubernetes, pytest</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=868f8c4ef1ebde56</t>
+          <t>https://www.indeed.com/viewjob?jk=71acb476a93daa68</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
+          <t>TM1 Developer IBM Planning Analytics Solution</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KPRMT Global solutions </t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Delaware, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5ba25f8dea0287eb</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>AI and vision learning engineer (In person required)</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>SEC Industrial</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Peachtree Corners, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Hadoop, Spark, Scala, NoSQL, ETL, Talend, Docker, Python</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a87cdb9d826d513d</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>AI/ML Software Engineer</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Numa Management Associates</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, MLOps, Docker</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3b8199552143ed2c</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Data Lake Data Engineer</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>E Source</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, ETL, ELT, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=252a0ed8c082beed</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Software Engineer, Data Infrastructure (Robotics &amp; Cloud)</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Tobor Robot Corporation</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Las Vegas, NV, US USA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>AWS, S3, SQS, IAM, RDS, Blob Storage, PostgreSQL, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b311657af0452f37</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Product Developer Advanced</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Tech Army</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Tallahassee, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, ETL, Power BI, Python</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8d958ebf75215c9a</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Analytics Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Rogue Credit Union</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Medford, OR, US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Dataflow, Spark, PySpark, Scala, Snowflake, Data Modeling, Tableau</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=58c35a1b6ab36700</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>.Net Developer</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Cloud and Things</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Albany, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, Azure DevOps, Docker, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a9e68a2fc7798ac9</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Django/Python</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>ATG</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>North Little Rock, AR, US USA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e959c5c2ece017ba</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Mid Level Software Engineer</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Harvestaff</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Chesterfield, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Oracle, SQL Server, PostgreSQL, MongoDB, Cassandra, NoSQL, Jenkins, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ee62f5b48244cf04</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Software Developer</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>S.S. White Technologies</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Saint Petersburg, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>AWS, ECS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dc670920196ab795</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Database Systems Engineer</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Estuate</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Milpitas, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Databricks, Spark, PySpark, Scala, Oracle, SQL Server, MySQL, ETL, ELT, Power BI</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=23d7f5f64249cd00</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
           <t>Software Engineer, Search and Alerts</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B74" t="inlineStr">
         <is>
           <t>Fitch Group</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="C74" t="inlineStr">
         <is>
           <t>Chicago, IL, US USA</t>
         </is>
       </c>
-      <c r="D62" t="n">
+      <c r="D74" t="n">
         <v>10.4</v>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="E74" t="inlineStr">
         <is>
           <t>AWS, Kinesis, S3, Oracle, MongoDB, DynamoDB, NoSQL, CI/CD, Git, Python</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=8e27c3a57395d5ed</t>
         </is>

--- a/results/job_matches_2026-04-28.xlsx
+++ b/results/job_matches_2026-04-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G74"/>
+  <dimension ref="A1:G68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,25 +678,25 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Snowflake Architect - Job ID 831</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Kapitus</t>
+          <t>Silverchair</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, IAM, RDS, Databricks</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Kafka, Snowflake, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,59 +706,59 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30116c3087096b0c</t>
+          <t>https://www.indeed.com/viewjob?jk=03088aab7fd212d8</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Silverchair</t>
+          <t>American Family Insurance</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Kafka, Snowflake, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03088aab7fd212d8</t>
+          <t>https://www.indeed.com/viewjob?jk=5bdf4aa591683148</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer - Snowflake</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Corebridge</t>
+          <t>Old National Bank</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Lake Elmo, MN, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3afad6ecd5a25a2</t>
+          <t>https://www.indeed.com/viewjob?jk=58d405ceae103971</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Associate - Data Engineer</t>
+          <t>Data Engineer - Snowflake</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Corebridge</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,34 +801,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Databricks, Spark, PySpark</t>
+          <t>AWS, Glue, Redshift, RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cadb0e669ca658a7</t>
+          <t>https://www.indeed.com/viewjob?jk=d3afad6ecd5a25a2</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Associate - Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Old National Bank</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Lake Elmo, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,17 +836,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58d405ceae103971</t>
+          <t>https://www.indeed.com/viewjob?jk=cadb0e669ca658a7</t>
         </is>
       </c>
     </row>
@@ -888,17 +888,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Reliability Engineer/Software Engineer</t>
+          <t>Cloud Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Red Hat</t>
+          <t>SambaNova Systems</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Lowell, MA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>S3, ECS, Databricks, BigQuery, Spark, Scala, Spark Streaming, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bed2b2b5d3a2123b</t>
+          <t>https://www.indeed.com/viewjob?jk=ae25761539c2b2d9</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr. Consultant SW Engineer</t>
+          <t>Data Reliability Engineer/Software Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Red Hat</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Lowell, MA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>S3, ECS, Databricks, BigQuery, Spark, Scala, Spark Streaming, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9ca5a09e7cef446</t>
+          <t>https://www.indeed.com/viewjob?jk=bed2b2b5d3a2123b</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>NLM Cloud Engineer I</t>
+          <t>Sr. Consultant SW Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Lexical Intelligence, LLC</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Hadoop, Spark, Scala, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f7f43fcc961cf9a</t>
+          <t>https://www.indeed.com/viewjob?jk=f9ca5a09e7cef446</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Platform Engineer- 6 Month Assignment</t>
+          <t>NLM Cloud Engineer I</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>MAXhealth</t>
+          <t>Lexical Intelligence, LLC</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,69 +1011,69 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Cloud Storage, Scala, SQL Server, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, Hadoop, Spark, Scala, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d635caaec7baf168</t>
+          <t>https://www.indeed.com/viewjob?jk=1f7f43fcc961cf9a</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>NLM Cloud Engineer II</t>
+          <t>Data Platform Engineer- 6 Month Assignment</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Lexical Intelligence, LLC</t>
+          <t>MAXhealth</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, Spark, PostgreSQL, MySQL, MongoDB</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Cloud Storage, Scala, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49524b4a45bcb416</t>
+          <t>https://www.indeed.com/viewjob?jk=d635caaec7baf168</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Mid-Level Data Engineer, Global</t>
+          <t>NLM Cloud Engineer II</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Lexical Intelligence, LLC</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables, ETL</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, Spark, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cd7e80ca3c98167</t>
+          <t>https://www.indeed.com/viewjob?jk=49524b4a45bcb416</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Cloud &amp; Digital Platform Architect</t>
+          <t>Mid-Level Data Engineer, Global</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Diality Inc</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, SQS, SNS</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=969f04a102da7944</t>
+          <t>https://www.indeed.com/viewjob?jk=9cd7e80ca3c98167</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>IT Applications Engineer V - Data Science, Data &amp; AI Engineering, Application Engineering</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Kaiser Permanente</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, ELT, MLflow, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, NoSQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6453e30c37711925</t>
+          <t>https://www.indeed.com/viewjob?jk=d07a1b512d8f6b8e</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Database Administrator - Mountlake Terrace, WA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Western Governors University</t>
+          <t>Mindful Support Services</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Mountlake Terrace, WA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Spark Streaming, ETL, MLOps</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Dimension Tables, ETL, ELT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02b371541d1ac53b</t>
+          <t>https://www.indeed.com/viewjob?jk=c7f72c836b506ce1</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Western Governors University</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, NoSQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Spark Streaming, ETL, MLOps</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d07a1b512d8f6b8e</t>
+          <t>https://www.indeed.com/viewjob?jk=02b371541d1ac53b</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Database Administrator - Mountlake Terrace, WA</t>
+          <t>IT Applications Engineer V - Data Science, Data &amp; AI Engineering, Application Engineering</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Mindful Support Services</t>
+          <t>Kaiser Permanente</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Mountlake Terrace, WA, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,69 +1256,69 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Dimension Tables, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, ELT, MLflow, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7f72c836b506ce1</t>
+          <t>https://www.indeed.com/viewjob?jk=6453e30c37711925</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sr. Backend Engineer - Integrations</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CLEAR</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, dbt, Tableau, Jenkins</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22b8eb7f870c0ec5</t>
+          <t>https://www.indeed.com/viewjob?jk=ceac9c56e064ddc9</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Science Engineer, GenAI Platforms &amp; Data Infrastructure</t>
+          <t>Senior DevOps Engineer - Atlanta, GA</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Cortland</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Git</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21b925b3e52300cd</t>
+          <t>https://www.indeed.com/viewjob?jk=75a9d9f16c1afffa</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer - Atlanta, GA</t>
+          <t>Platform Engineer (Remote / Contract)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Cortland</t>
+          <t>VERVE GROUP</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Git</t>
+          <t>AWS, ECS, RDS, GCP, Dataflow, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75a9d9f16c1afffa</t>
+          <t>https://www.indeed.com/viewjob?jk=ca697f45b6290281</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Platform Engineer (Remote / Contract)</t>
+          <t>Senior Data Science Engineer, GenAI Platforms &amp; Data Infrastructure</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>VERVE GROUP</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, GCP, Dataflow, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca697f45b6290281</t>
+          <t>https://www.indeed.com/viewjob?jk=21b925b3e52300cd</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sr. SDET</t>
+          <t>Senior Development Engineer (Core Engine)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Subway</t>
+          <t>Office Ally</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Shelton, CT, US USA</t>
+          <t>Concord, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, Scala, ELT, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e99b607ba441a3b6</t>
+          <t>https://www.indeed.com/viewjob?jk=18eeecb282323a96</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SR SDET (Sr Software Engineer in Test &amp; Merchandising Automation)</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Subway</t>
+          <t>Klaviyo</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Shelton, CT, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, Scala, ELT, CI/CD</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac35b48862d2d754</t>
+          <t>https://www.indeed.com/viewjob?jk=c14b5f2f1affd1a2</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Aureon</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>West Des Moines, IA, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, ETL, ELT</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f774c4618ca5806</t>
+          <t>https://www.indeed.com/viewjob?jk=e79ac2cb00b1176b</t>
         </is>
       </c>
     </row>
@@ -1553,17 +1553,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sr. Automation Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Subway</t>
+          <t>Aureon</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Shelton, CT, US USA</t>
+          <t>West Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, DynamoDB, ELT, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89ac62864e6673e6</t>
+          <t>https://www.indeed.com/viewjob?jk=2f774c4618ca5806</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Automation Engineer</t>
+          <t>Senior Specialty Software Engineer - Capital Markets Reference Data</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Subway</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Shelton, CT, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, DynamoDB, ELT, CI/CD</t>
+          <t>API Gateway, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb7872e2804ae8eb</t>
+          <t>https://www.indeed.com/viewjob?jk=f0e85b21f1fb3187</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Klaviyo</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c14b5f2f1affd1a2</t>
+          <t>https://www.indeed.com/viewjob?jk=2e59f80446549413</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>HARVEST GROUP</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Scala, Snowflake, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e79ac2cb00b1176b</t>
+          <t>https://www.indeed.com/viewjob?jk=d391d4aaecc47ecd</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Specialty Software Engineer - Capital Markets Reference Data</t>
+          <t>Senior Technical Support Engineer, Observe by Snowflake</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,104 +1711,104 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Snowflake, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0e85b21f1fb3187</t>
+          <t>https://www.indeed.com/viewjob?jk=b918e60460b92ef4</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Software Engineer III - Big Data &amp; AWS</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Jenkins, Maven, Docker</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Databricks</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e59f80446549413</t>
+          <t>https://www.indeed.com/viewjob?jk=e881c656d4332d30</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>HARVEST GROUP</t>
+          <t>Moody's</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Scala, Snowflake, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Spark, Scala</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d391d4aaecc47ecd</t>
+          <t>https://www.indeed.com/viewjob?jk=3c607892a88eb133</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>System Architect IV (ATL)</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Dealpath</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, S3, IAM, RDS, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0679e72962f96d1</t>
+          <t>https://www.indeed.com/viewjob?jk=645d3d76b515ea5a</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>System Architect IV (ATL)</t>
+          <t>Asset &amp; Wealth Management-Software Engineering-Associate-Dallas</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Glue, EMR, Redshift, S3, Hadoop, Spark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=562c3953d5d4cf9e</t>
+          <t>https://www.indeed.com/viewjob?jk=ce31ad37d0b4074e</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Dealpath</t>
+          <t>Moody's</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, PostgreSQL</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Spark, Scala</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=645d3d76b515ea5a</t>
+          <t>https://www.indeed.com/viewjob?jk=777c988322e931b7</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Asset &amp; Wealth Management-Software Engineering-Associate-Dallas</t>
+          <t>DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Global Technology Solutions Inc</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, S3, Hadoop, Spark, Scala, Snowflake, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce31ad37d0b4074e</t>
+          <t>https://www.indeed.com/viewjob?jk=252844720ed3e114</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Reliability Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Moody's</t>
+          <t>Fitch Group</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Spark, Scala</t>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=777c988322e931b7</t>
+          <t>https://www.indeed.com/viewjob?jk=bb104709126cf2da</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>DevSecOps Engineer</t>
+          <t>System Architect IV (ATL)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Global Technology Solutions Inc</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=252844720ed3e114</t>
+          <t>https://www.indeed.com/viewjob?jk=c0679e72962f96d1</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Reliability Engineer</t>
+          <t>System Architect IV (ATL)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Fitch Group</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb104709126cf2da</t>
+          <t>https://www.indeed.com/viewjob?jk=562c3953d5d4cf9e</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>NRG Energy</t>
+          <t>NetDocuments</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Cloud Storage, Spark, Data Modeling, ETL, ELT</t>
+          <t>AWS, SQS, SNS, RDS, HBase, Scala, Kafka, Snowflake, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=daf356dec855c3b1</t>
+          <t>https://www.indeed.com/viewjob?jk=1610940d9ea365df</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Engineer, Finance Applications</t>
+          <t>Senior Software Engineer - Platform &amp; Integrations</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>Seismic</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, Oracle, MySQL, DynamoDB, Kubernetes, Git</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5be60fb53ad2487f</t>
+          <t>https://www.indeed.com/viewjob?jk=cca2fb47a24092c1</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Platform &amp; Integrations</t>
+          <t>Sr Software Engineer, Fullstack</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Seismic</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, SQL Server, Data Modeling, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cca2fb47a24092c1</t>
+          <t>https://www.indeed.com/viewjob?jk=4fb90dbd5192ef62</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>AI Commercial &amp; ML Ops Engineer</t>
+          <t>Software Engineer, Finance Applications</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>MGM Resorts International</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>San Francisco Bay Area, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,69 +2166,69 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLflow, CI/CD</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, Oracle, MySQL, DynamoDB, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e59ac0d5620a4ae</t>
+          <t>https://www.indeed.com/viewjob?jk=5be60fb53ad2487f</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sr Software Engineer, Fullstack</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>OEConnection</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, SQL Server, Data Modeling, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fb90dbd5192ef62</t>
+          <t>https://www.indeed.com/viewjob?jk=545e32663300e2ec</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sr. Consultant - Data Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Insygnum</t>
+          <t>OEConnection</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Glue, RDS, Hadoop, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=add721e79e9d7463</t>
+          <t>https://www.indeed.com/viewjob?jk=78c8d1f679e08f02</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Sr. Consultant - Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Rosen's Diversified, Inc.</t>
+          <t>Insygnum</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Green Bay, WI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,17 +2271,17 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>Glue, RDS, Hadoop, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43e06e046a3009ec</t>
+          <t>https://www.indeed.com/viewjob?jk=add721e79e9d7463</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Eagan, MN, US USA</t>
+          <t>Green Bay, WI, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d5ed846b77ab548</t>
+          <t>https://www.indeed.com/viewjob?jk=43e06e046a3009ec</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>OEConnection</t>
+          <t>Rosen's Diversified, Inc.</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Eagan, MN, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=545e32663300e2ec</t>
+          <t>https://www.indeed.com/viewjob?jk=0d5ed846b77ab548</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Senior Product Data Analyst - Supply Chain</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>OEConnection</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Spark, PySpark, Scala, Oracle, Power BI</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78c8d1f679e08f02</t>
+          <t>https://www.indeed.com/viewjob?jk=3f3aaa95e1c534da</t>
         </is>
       </c>
     </row>
@@ -2428,17 +2428,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Sr Developer, Marketing and Communications</t>
+          <t>Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>DaVita</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, GCP, Scala, SQL Server, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Docker, Kubernetes, pytest</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f4e10eee0c4935f</t>
+          <t>https://www.indeed.com/viewjob?jk=71acb476a93daa68</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer, Applied AI</t>
+          <t>TM1 Developer IBM Planning Analytics Solution</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>MDVIP LLC</t>
+          <t xml:space="preserve">KPRMT Global solutions </t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Delaware, NJ, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Snowflake, SQL Server, dbt, Power BI, Python</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=386fc1ac3272e529</t>
+          <t>https://www.indeed.com/viewjob?jk=5ba25f8dea0287eb</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior Analytics Engineer, Applied AI</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Ansell</t>
+          <t>MDVIP LLC</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MongoDB, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Snowflake, SQL Server, dbt, Power BI, Python</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddfd90d1833c2dcd</t>
+          <t>https://www.indeed.com/viewjob?jk=386fc1ac3272e529</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack</t>
+          <t>Data Lake Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>E Source</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Docker, Kubernetes, pytest</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, ETL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71acb476a93daa68</t>
+          <t>https://www.indeed.com/viewjob?jk=252a0ed8c082beed</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>TM1 Developer IBM Planning Analytics Solution</t>
+          <t>Software Engineer, Data Infrastructure (Robotics &amp; Cloud)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t xml:space="preserve">KPRMT Global solutions </t>
+          <t>Tobor Robot Corporation</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Delaware, NJ, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, S3, SQS, IAM, RDS, Blob Storage, PostgreSQL, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ba25f8dea0287eb</t>
+          <t>https://www.indeed.com/viewjob?jk=b311657af0452f37</t>
         </is>
       </c>
     </row>
@@ -2638,17 +2638,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>AI/ML Software Engineer</t>
+          <t>Analytics Data Engineer II</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Numa Management Associates</t>
+          <t>Rogue Credit Union</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Medford, OR, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, MLOps, Docker</t>
+          <t>RDS, Azure, Databricks, Dataflow, Spark, PySpark, Scala, Snowflake, Data Modeling, Tableau</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b8199552143ed2c</t>
+          <t>https://www.indeed.com/viewjob?jk=58c35a1b6ab36700</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Lake Data Engineer</t>
+          <t>Senior Software Engineer - Django/Python</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>E Source</t>
+          <t>ATG</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>North Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, ETL, ELT, CI/CD, Terraform</t>
+          <t>AWS, S3, Azure, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=252a0ed8c082beed</t>
+          <t>https://www.indeed.com/viewjob?jk=e959c5c2ece017ba</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Infrastructure (Robotics &amp; Cloud)</t>
+          <t>Mid Level Software Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Tobor Robot Corporation</t>
+          <t>Harvestaff</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Chesterfield, MO, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, IAM, RDS, Blob Storage, PostgreSQL, MLOps, CI/CD, Terraform</t>
+          <t>RDS, Azure, Oracle, SQL Server, PostgreSQL, MongoDB, Cassandra, NoSQL, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b311657af0452f37</t>
+          <t>https://www.indeed.com/viewjob?jk=ee62f5b48244cf04</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Product Developer Advanced</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Tech Army</t>
+          <t>M&amp;T Bank</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, ETL, Power BI, Python</t>
+          <t>RDS, Hadoop, Hive, Spark, Snowflake, SQL Server, ETL, Airflow, Apache Airflow, Git</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d958ebf75215c9a</t>
+          <t>https://www.indeed.com/viewjob?jk=c0cc7c1bb617e5ca</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Analytics Data Engineer II</t>
+          <t>Database Systems Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Rogue Credit Union</t>
+          <t>Estuate</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Medford, OR, US USA</t>
+          <t>Milpitas, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Dataflow, Spark, PySpark, Scala, Snowflake, Data Modeling, Tableau</t>
+          <t>Databricks, Spark, PySpark, Scala, Oracle, SQL Server, MySQL, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,217 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58c35a1b6ab36700</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>.Net Developer</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Cloud and Things</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Albany, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, Azure DevOps, Docker, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a9e68a2fc7798ac9</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Django/Python</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>ATG</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>North Little Rock, AR, US USA</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>AWS, S3, Azure, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e959c5c2ece017ba</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Mid Level Software Engineer</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Harvestaff</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Chesterfield, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Oracle, SQL Server, PostgreSQL, MongoDB, Cassandra, NoSQL, Jenkins, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ee62f5b48244cf04</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Software Developer</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>S.S. White Technologies</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Saint Petersburg, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>AWS, ECS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dc670920196ab795</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Database Systems Engineer</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Estuate</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Milpitas, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>Databricks, Spark, PySpark, Scala, Oracle, SQL Server, MySQL, ETL, ELT, Power BI</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=23d7f5f64249cd00</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Software Engineer, Search and Alerts</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Fitch Group</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>AWS, Kinesis, S3, Oracle, MongoDB, DynamoDB, NoSQL, CI/CD, Git, Python</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8e27c3a57395d5ed</t>
         </is>
       </c>
     </row>
